--- a/DAQTool-Template.xlsx
+++ b/DAQTool-Template.xlsx
@@ -781,11 +781,11 @@
         <v/>
       </c>
       <c r="AL2">
-        <f>IF(AE2="","",HYPERLINK(AE2,"before"))</f>
+        <f>IF(AE2="","",HYPERLINK(IFERROR(LEFT(AE2,FIND(";",AE2)-1),AE2),"before"))</f>
         <v/>
       </c>
       <c r="AM2">
-        <f>IF(AF2="","",HYPERLINK(AF2,"after"))</f>
+        <f>IF(AF2="","",HYPERLINK(IFERROR(LEFT(AF2,FIND(";",AF2)-1),AF2),"after"))</f>
         <v/>
       </c>
     </row>
@@ -817,11 +817,11 @@
         <v/>
       </c>
       <c r="AL3">
-        <f>IF(AE3="","",HYPERLINK(AE3,"before"))</f>
+        <f>IF(AE3="","",HYPERLINK(IFERROR(LEFT(AE3,FIND(";",AE3)-1),AE3),"before"))</f>
         <v/>
       </c>
       <c r="AM3">
-        <f>IF(AF3="","",HYPERLINK(AF3,"after"))</f>
+        <f>IF(AF3="","",HYPERLINK(IFERROR(LEFT(AF3,FIND(";",AF3)-1),AF3),"after"))</f>
         <v/>
       </c>
     </row>
@@ -853,11 +853,11 @@
         <v/>
       </c>
       <c r="AL4">
-        <f>IF(AE4="","",HYPERLINK(AE4,"before"))</f>
+        <f>IF(AE4="","",HYPERLINK(IFERROR(LEFT(AE4,FIND(";",AE4)-1),AE4),"before"))</f>
         <v/>
       </c>
       <c r="AM4">
-        <f>IF(AF4="","",HYPERLINK(AF4,"after"))</f>
+        <f>IF(AF4="","",HYPERLINK(IFERROR(LEFT(AF4,FIND(";",AF4)-1),AF4),"after"))</f>
         <v/>
       </c>
     </row>
@@ -889,11 +889,11 @@
         <v/>
       </c>
       <c r="AL5">
-        <f>IF(AE5="","",HYPERLINK(AE5,"before"))</f>
+        <f>IF(AE5="","",HYPERLINK(IFERROR(LEFT(AE5,FIND(";",AE5)-1),AE5),"before"))</f>
         <v/>
       </c>
       <c r="AM5">
-        <f>IF(AF5="","",HYPERLINK(AF5,"after"))</f>
+        <f>IF(AF5="","",HYPERLINK(IFERROR(LEFT(AF5,FIND(";",AF5)-1),AF5),"after"))</f>
         <v/>
       </c>
     </row>
@@ -925,11 +925,11 @@
         <v/>
       </c>
       <c r="AL6">
-        <f>IF(AE6="","",HYPERLINK(AE6,"before"))</f>
+        <f>IF(AE6="","",HYPERLINK(IFERROR(LEFT(AE6,FIND(";",AE6)-1),AE6),"before"))</f>
         <v/>
       </c>
       <c r="AM6">
-        <f>IF(AF6="","",HYPERLINK(AF6,"after"))</f>
+        <f>IF(AF6="","",HYPERLINK(IFERROR(LEFT(AF6,FIND(";",AF6)-1),AF6),"after"))</f>
         <v/>
       </c>
     </row>
@@ -961,11 +961,11 @@
         <v/>
       </c>
       <c r="AL7">
-        <f>IF(AE7="","",HYPERLINK(AE7,"before"))</f>
+        <f>IF(AE7="","",HYPERLINK(IFERROR(LEFT(AE7,FIND(";",AE7)-1),AE7),"before"))</f>
         <v/>
       </c>
       <c r="AM7">
-        <f>IF(AF7="","",HYPERLINK(AF7,"after"))</f>
+        <f>IF(AF7="","",HYPERLINK(IFERROR(LEFT(AF7,FIND(";",AF7)-1),AF7),"after"))</f>
         <v/>
       </c>
     </row>
@@ -997,11 +997,11 @@
         <v/>
       </c>
       <c r="AL8">
-        <f>IF(AE8="","",HYPERLINK(AE8,"before"))</f>
+        <f>IF(AE8="","",HYPERLINK(IFERROR(LEFT(AE8,FIND(";",AE8)-1),AE8),"before"))</f>
         <v/>
       </c>
       <c r="AM8">
-        <f>IF(AF8="","",HYPERLINK(AF8,"after"))</f>
+        <f>IF(AF8="","",HYPERLINK(IFERROR(LEFT(AF8,FIND(";",AF8)-1),AF8),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1033,11 +1033,11 @@
         <v/>
       </c>
       <c r="AL9">
-        <f>IF(AE9="","",HYPERLINK(AE9,"before"))</f>
+        <f>IF(AE9="","",HYPERLINK(IFERROR(LEFT(AE9,FIND(";",AE9)-1),AE9),"before"))</f>
         <v/>
       </c>
       <c r="AM9">
-        <f>IF(AF9="","",HYPERLINK(AF9,"after"))</f>
+        <f>IF(AF9="","",HYPERLINK(IFERROR(LEFT(AF9,FIND(";",AF9)-1),AF9),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1069,11 +1069,11 @@
         <v/>
       </c>
       <c r="AL10">
-        <f>IF(AE10="","",HYPERLINK(AE10,"before"))</f>
+        <f>IF(AE10="","",HYPERLINK(IFERROR(LEFT(AE10,FIND(";",AE10)-1),AE10),"before"))</f>
         <v/>
       </c>
       <c r="AM10">
-        <f>IF(AF10="","",HYPERLINK(AF10,"after"))</f>
+        <f>IF(AF10="","",HYPERLINK(IFERROR(LEFT(AF10,FIND(";",AF10)-1),AF10),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1105,11 +1105,11 @@
         <v/>
       </c>
       <c r="AL11">
-        <f>IF(AE11="","",HYPERLINK(AE11,"before"))</f>
+        <f>IF(AE11="","",HYPERLINK(IFERROR(LEFT(AE11,FIND(";",AE11)-1),AE11),"before"))</f>
         <v/>
       </c>
       <c r="AM11">
-        <f>IF(AF11="","",HYPERLINK(AF11,"after"))</f>
+        <f>IF(AF11="","",HYPERLINK(IFERROR(LEFT(AF11,FIND(";",AF11)-1),AF11),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1141,11 +1141,11 @@
         <v/>
       </c>
       <c r="AL12">
-        <f>IF(AE12="","",HYPERLINK(AE12,"before"))</f>
+        <f>IF(AE12="","",HYPERLINK(IFERROR(LEFT(AE12,FIND(";",AE12)-1),AE12),"before"))</f>
         <v/>
       </c>
       <c r="AM12">
-        <f>IF(AF12="","",HYPERLINK(AF12,"after"))</f>
+        <f>IF(AF12="","",HYPERLINK(IFERROR(LEFT(AF12,FIND(";",AF12)-1),AF12),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1177,11 +1177,11 @@
         <v/>
       </c>
       <c r="AL13">
-        <f>IF(AE13="","",HYPERLINK(AE13,"before"))</f>
+        <f>IF(AE13="","",HYPERLINK(IFERROR(LEFT(AE13,FIND(";",AE13)-1),AE13),"before"))</f>
         <v/>
       </c>
       <c r="AM13">
-        <f>IF(AF13="","",HYPERLINK(AF13,"after"))</f>
+        <f>IF(AF13="","",HYPERLINK(IFERROR(LEFT(AF13,FIND(";",AF13)-1),AF13),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1213,11 +1213,11 @@
         <v/>
       </c>
       <c r="AL14">
-        <f>IF(AE14="","",HYPERLINK(AE14,"before"))</f>
+        <f>IF(AE14="","",HYPERLINK(IFERROR(LEFT(AE14,FIND(";",AE14)-1),AE14),"before"))</f>
         <v/>
       </c>
       <c r="AM14">
-        <f>IF(AF14="","",HYPERLINK(AF14,"after"))</f>
+        <f>IF(AF14="","",HYPERLINK(IFERROR(LEFT(AF14,FIND(";",AF14)-1),AF14),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1249,11 +1249,11 @@
         <v/>
       </c>
       <c r="AL15">
-        <f>IF(AE15="","",HYPERLINK(AE15,"before"))</f>
+        <f>IF(AE15="","",HYPERLINK(IFERROR(LEFT(AE15,FIND(";",AE15)-1),AE15),"before"))</f>
         <v/>
       </c>
       <c r="AM15">
-        <f>IF(AF15="","",HYPERLINK(AF15,"after"))</f>
+        <f>IF(AF15="","",HYPERLINK(IFERROR(LEFT(AF15,FIND(";",AF15)-1),AF15),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1285,11 +1285,11 @@
         <v/>
       </c>
       <c r="AL16">
-        <f>IF(AE16="","",HYPERLINK(AE16,"before"))</f>
+        <f>IF(AE16="","",HYPERLINK(IFERROR(LEFT(AE16,FIND(";",AE16)-1),AE16),"before"))</f>
         <v/>
       </c>
       <c r="AM16">
-        <f>IF(AF16="","",HYPERLINK(AF16,"after"))</f>
+        <f>IF(AF16="","",HYPERLINK(IFERROR(LEFT(AF16,FIND(";",AF16)-1),AF16),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1321,11 +1321,11 @@
         <v/>
       </c>
       <c r="AL17">
-        <f>IF(AE17="","",HYPERLINK(AE17,"before"))</f>
+        <f>IF(AE17="","",HYPERLINK(IFERROR(LEFT(AE17,FIND(";",AE17)-1),AE17),"before"))</f>
         <v/>
       </c>
       <c r="AM17">
-        <f>IF(AF17="","",HYPERLINK(AF17,"after"))</f>
+        <f>IF(AF17="","",HYPERLINK(IFERROR(LEFT(AF17,FIND(";",AF17)-1),AF17),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1357,11 +1357,11 @@
         <v/>
       </c>
       <c r="AL18">
-        <f>IF(AE18="","",HYPERLINK(AE18,"before"))</f>
+        <f>IF(AE18="","",HYPERLINK(IFERROR(LEFT(AE18,FIND(";",AE18)-1),AE18),"before"))</f>
         <v/>
       </c>
       <c r="AM18">
-        <f>IF(AF18="","",HYPERLINK(AF18,"after"))</f>
+        <f>IF(AF18="","",HYPERLINK(IFERROR(LEFT(AF18,FIND(";",AF18)-1),AF18),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1393,11 +1393,11 @@
         <v/>
       </c>
       <c r="AL19">
-        <f>IF(AE19="","",HYPERLINK(AE19,"before"))</f>
+        <f>IF(AE19="","",HYPERLINK(IFERROR(LEFT(AE19,FIND(";",AE19)-1),AE19),"before"))</f>
         <v/>
       </c>
       <c r="AM19">
-        <f>IF(AF19="","",HYPERLINK(AF19,"after"))</f>
+        <f>IF(AF19="","",HYPERLINK(IFERROR(LEFT(AF19,FIND(";",AF19)-1),AF19),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1429,11 +1429,11 @@
         <v/>
       </c>
       <c r="AL20">
-        <f>IF(AE20="","",HYPERLINK(AE20,"before"))</f>
+        <f>IF(AE20="","",HYPERLINK(IFERROR(LEFT(AE20,FIND(";",AE20)-1),AE20),"before"))</f>
         <v/>
       </c>
       <c r="AM20">
-        <f>IF(AF20="","",HYPERLINK(AF20,"after"))</f>
+        <f>IF(AF20="","",HYPERLINK(IFERROR(LEFT(AF20,FIND(";",AF20)-1),AF20),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1465,11 +1465,11 @@
         <v/>
       </c>
       <c r="AL21">
-        <f>IF(AE21="","",HYPERLINK(AE21,"before"))</f>
+        <f>IF(AE21="","",HYPERLINK(IFERROR(LEFT(AE21,FIND(";",AE21)-1),AE21),"before"))</f>
         <v/>
       </c>
       <c r="AM21">
-        <f>IF(AF21="","",HYPERLINK(AF21,"after"))</f>
+        <f>IF(AF21="","",HYPERLINK(IFERROR(LEFT(AF21,FIND(";",AF21)-1),AF21),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1501,11 +1501,11 @@
         <v/>
       </c>
       <c r="AL22">
-        <f>IF(AE22="","",HYPERLINK(AE22,"before"))</f>
+        <f>IF(AE22="","",HYPERLINK(IFERROR(LEFT(AE22,FIND(";",AE22)-1),AE22),"before"))</f>
         <v/>
       </c>
       <c r="AM22">
-        <f>IF(AF22="","",HYPERLINK(AF22,"after"))</f>
+        <f>IF(AF22="","",HYPERLINK(IFERROR(LEFT(AF22,FIND(";",AF22)-1),AF22),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1537,11 +1537,11 @@
         <v/>
       </c>
       <c r="AL23">
-        <f>IF(AE23="","",HYPERLINK(AE23,"before"))</f>
+        <f>IF(AE23="","",HYPERLINK(IFERROR(LEFT(AE23,FIND(";",AE23)-1),AE23),"before"))</f>
         <v/>
       </c>
       <c r="AM23">
-        <f>IF(AF23="","",HYPERLINK(AF23,"after"))</f>
+        <f>IF(AF23="","",HYPERLINK(IFERROR(LEFT(AF23,FIND(";",AF23)-1),AF23),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1573,11 +1573,11 @@
         <v/>
       </c>
       <c r="AL24">
-        <f>IF(AE24="","",HYPERLINK(AE24,"before"))</f>
+        <f>IF(AE24="","",HYPERLINK(IFERROR(LEFT(AE24,FIND(";",AE24)-1),AE24),"before"))</f>
         <v/>
       </c>
       <c r="AM24">
-        <f>IF(AF24="","",HYPERLINK(AF24,"after"))</f>
+        <f>IF(AF24="","",HYPERLINK(IFERROR(LEFT(AF24,FIND(";",AF24)-1),AF24),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1609,11 +1609,11 @@
         <v/>
       </c>
       <c r="AL25">
-        <f>IF(AE25="","",HYPERLINK(AE25,"before"))</f>
+        <f>IF(AE25="","",HYPERLINK(IFERROR(LEFT(AE25,FIND(";",AE25)-1),AE25),"before"))</f>
         <v/>
       </c>
       <c r="AM25">
-        <f>IF(AF25="","",HYPERLINK(AF25,"after"))</f>
+        <f>IF(AF25="","",HYPERLINK(IFERROR(LEFT(AF25,FIND(";",AF25)-1),AF25),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1645,11 +1645,11 @@
         <v/>
       </c>
       <c r="AL26">
-        <f>IF(AE26="","",HYPERLINK(AE26,"before"))</f>
+        <f>IF(AE26="","",HYPERLINK(IFERROR(LEFT(AE26,FIND(";",AE26)-1),AE26),"before"))</f>
         <v/>
       </c>
       <c r="AM26">
-        <f>IF(AF26="","",HYPERLINK(AF26,"after"))</f>
+        <f>IF(AF26="","",HYPERLINK(IFERROR(LEFT(AF26,FIND(";",AF26)-1),AF26),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1681,11 +1681,11 @@
         <v/>
       </c>
       <c r="AL27">
-        <f>IF(AE27="","",HYPERLINK(AE27,"before"))</f>
+        <f>IF(AE27="","",HYPERLINK(IFERROR(LEFT(AE27,FIND(";",AE27)-1),AE27),"before"))</f>
         <v/>
       </c>
       <c r="AM27">
-        <f>IF(AF27="","",HYPERLINK(AF27,"after"))</f>
+        <f>IF(AF27="","",HYPERLINK(IFERROR(LEFT(AF27,FIND(";",AF27)-1),AF27),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1717,11 +1717,11 @@
         <v/>
       </c>
       <c r="AL28">
-        <f>IF(AE28="","",HYPERLINK(AE28,"before"))</f>
+        <f>IF(AE28="","",HYPERLINK(IFERROR(LEFT(AE28,FIND(";",AE28)-1),AE28),"before"))</f>
         <v/>
       </c>
       <c r="AM28">
-        <f>IF(AF28="","",HYPERLINK(AF28,"after"))</f>
+        <f>IF(AF28="","",HYPERLINK(IFERROR(LEFT(AF28,FIND(";",AF28)-1),AF28),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1753,11 +1753,11 @@
         <v/>
       </c>
       <c r="AL29">
-        <f>IF(AE29="","",HYPERLINK(AE29,"before"))</f>
+        <f>IF(AE29="","",HYPERLINK(IFERROR(LEFT(AE29,FIND(";",AE29)-1),AE29),"before"))</f>
         <v/>
       </c>
       <c r="AM29">
-        <f>IF(AF29="","",HYPERLINK(AF29,"after"))</f>
+        <f>IF(AF29="","",HYPERLINK(IFERROR(LEFT(AF29,FIND(";",AF29)-1),AF29),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1789,11 +1789,11 @@
         <v/>
       </c>
       <c r="AL30">
-        <f>IF(AE30="","",HYPERLINK(AE30,"before"))</f>
+        <f>IF(AE30="","",HYPERLINK(IFERROR(LEFT(AE30,FIND(";",AE30)-1),AE30),"before"))</f>
         <v/>
       </c>
       <c r="AM30">
-        <f>IF(AF30="","",HYPERLINK(AF30,"after"))</f>
+        <f>IF(AF30="","",HYPERLINK(IFERROR(LEFT(AF30,FIND(";",AF30)-1),AF30),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1825,11 +1825,11 @@
         <v/>
       </c>
       <c r="AL31">
-        <f>IF(AE31="","",HYPERLINK(AE31,"before"))</f>
+        <f>IF(AE31="","",HYPERLINK(IFERROR(LEFT(AE31,FIND(";",AE31)-1),AE31),"before"))</f>
         <v/>
       </c>
       <c r="AM31">
-        <f>IF(AF31="","",HYPERLINK(AF31,"after"))</f>
+        <f>IF(AF31="","",HYPERLINK(IFERROR(LEFT(AF31,FIND(";",AF31)-1),AF31),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1861,11 +1861,11 @@
         <v/>
       </c>
       <c r="AL32">
-        <f>IF(AE32="","",HYPERLINK(AE32,"before"))</f>
+        <f>IF(AE32="","",HYPERLINK(IFERROR(LEFT(AE32,FIND(";",AE32)-1),AE32),"before"))</f>
         <v/>
       </c>
       <c r="AM32">
-        <f>IF(AF32="","",HYPERLINK(AF32,"after"))</f>
+        <f>IF(AF32="","",HYPERLINK(IFERROR(LEFT(AF32,FIND(";",AF32)-1),AF32),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1897,11 +1897,11 @@
         <v/>
       </c>
       <c r="AL33">
-        <f>IF(AE33="","",HYPERLINK(AE33,"before"))</f>
+        <f>IF(AE33="","",HYPERLINK(IFERROR(LEFT(AE33,FIND(";",AE33)-1),AE33),"before"))</f>
         <v/>
       </c>
       <c r="AM33">
-        <f>IF(AF33="","",HYPERLINK(AF33,"after"))</f>
+        <f>IF(AF33="","",HYPERLINK(IFERROR(LEFT(AF33,FIND(";",AF33)-1),AF33),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1933,11 +1933,11 @@
         <v/>
       </c>
       <c r="AL34">
-        <f>IF(AE34="","",HYPERLINK(AE34,"before"))</f>
+        <f>IF(AE34="","",HYPERLINK(IFERROR(LEFT(AE34,FIND(";",AE34)-1),AE34),"before"))</f>
         <v/>
       </c>
       <c r="AM34">
-        <f>IF(AF34="","",HYPERLINK(AF34,"after"))</f>
+        <f>IF(AF34="","",HYPERLINK(IFERROR(LEFT(AF34,FIND(";",AF34)-1),AF34),"after"))</f>
         <v/>
       </c>
     </row>
@@ -1969,11 +1969,11 @@
         <v/>
       </c>
       <c r="AL35">
-        <f>IF(AE35="","",HYPERLINK(AE35,"before"))</f>
+        <f>IF(AE35="","",HYPERLINK(IFERROR(LEFT(AE35,FIND(";",AE35)-1),AE35),"before"))</f>
         <v/>
       </c>
       <c r="AM35">
-        <f>IF(AF35="","",HYPERLINK(AF35,"after"))</f>
+        <f>IF(AF35="","",HYPERLINK(IFERROR(LEFT(AF35,FIND(";",AF35)-1),AF35),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2005,11 +2005,11 @@
         <v/>
       </c>
       <c r="AL36">
-        <f>IF(AE36="","",HYPERLINK(AE36,"before"))</f>
+        <f>IF(AE36="","",HYPERLINK(IFERROR(LEFT(AE36,FIND(";",AE36)-1),AE36),"before"))</f>
         <v/>
       </c>
       <c r="AM36">
-        <f>IF(AF36="","",HYPERLINK(AF36,"after"))</f>
+        <f>IF(AF36="","",HYPERLINK(IFERROR(LEFT(AF36,FIND(";",AF36)-1),AF36),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2041,11 +2041,11 @@
         <v/>
       </c>
       <c r="AL37">
-        <f>IF(AE37="","",HYPERLINK(AE37,"before"))</f>
+        <f>IF(AE37="","",HYPERLINK(IFERROR(LEFT(AE37,FIND(";",AE37)-1),AE37),"before"))</f>
         <v/>
       </c>
       <c r="AM37">
-        <f>IF(AF37="","",HYPERLINK(AF37,"after"))</f>
+        <f>IF(AF37="","",HYPERLINK(IFERROR(LEFT(AF37,FIND(";",AF37)-1),AF37),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2077,11 +2077,11 @@
         <v/>
       </c>
       <c r="AL38">
-        <f>IF(AE38="","",HYPERLINK(AE38,"before"))</f>
+        <f>IF(AE38="","",HYPERLINK(IFERROR(LEFT(AE38,FIND(";",AE38)-1),AE38),"before"))</f>
         <v/>
       </c>
       <c r="AM38">
-        <f>IF(AF38="","",HYPERLINK(AF38,"after"))</f>
+        <f>IF(AF38="","",HYPERLINK(IFERROR(LEFT(AF38,FIND(";",AF38)-1),AF38),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2113,11 +2113,11 @@
         <v/>
       </c>
       <c r="AL39">
-        <f>IF(AE39="","",HYPERLINK(AE39,"before"))</f>
+        <f>IF(AE39="","",HYPERLINK(IFERROR(LEFT(AE39,FIND(";",AE39)-1),AE39),"before"))</f>
         <v/>
       </c>
       <c r="AM39">
-        <f>IF(AF39="","",HYPERLINK(AF39,"after"))</f>
+        <f>IF(AF39="","",HYPERLINK(IFERROR(LEFT(AF39,FIND(";",AF39)-1),AF39),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2149,11 +2149,11 @@
         <v/>
       </c>
       <c r="AL40">
-        <f>IF(AE40="","",HYPERLINK(AE40,"before"))</f>
+        <f>IF(AE40="","",HYPERLINK(IFERROR(LEFT(AE40,FIND(";",AE40)-1),AE40),"before"))</f>
         <v/>
       </c>
       <c r="AM40">
-        <f>IF(AF40="","",HYPERLINK(AF40,"after"))</f>
+        <f>IF(AF40="","",HYPERLINK(IFERROR(LEFT(AF40,FIND(";",AF40)-1),AF40),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2185,11 +2185,11 @@
         <v/>
       </c>
       <c r="AL41">
-        <f>IF(AE41="","",HYPERLINK(AE41,"before"))</f>
+        <f>IF(AE41="","",HYPERLINK(IFERROR(LEFT(AE41,FIND(";",AE41)-1),AE41),"before"))</f>
         <v/>
       </c>
       <c r="AM41">
-        <f>IF(AF41="","",HYPERLINK(AF41,"after"))</f>
+        <f>IF(AF41="","",HYPERLINK(IFERROR(LEFT(AF41,FIND(";",AF41)-1),AF41),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2221,11 +2221,11 @@
         <v/>
       </c>
       <c r="AL42">
-        <f>IF(AE42="","",HYPERLINK(AE42,"before"))</f>
+        <f>IF(AE42="","",HYPERLINK(IFERROR(LEFT(AE42,FIND(";",AE42)-1),AE42),"before"))</f>
         <v/>
       </c>
       <c r="AM42">
-        <f>IF(AF42="","",HYPERLINK(AF42,"after"))</f>
+        <f>IF(AF42="","",HYPERLINK(IFERROR(LEFT(AF42,FIND(";",AF42)-1),AF42),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2257,11 +2257,11 @@
         <v/>
       </c>
       <c r="AL43">
-        <f>IF(AE43="","",HYPERLINK(AE43,"before"))</f>
+        <f>IF(AE43="","",HYPERLINK(IFERROR(LEFT(AE43,FIND(";",AE43)-1),AE43),"before"))</f>
         <v/>
       </c>
       <c r="AM43">
-        <f>IF(AF43="","",HYPERLINK(AF43,"after"))</f>
+        <f>IF(AF43="","",HYPERLINK(IFERROR(LEFT(AF43,FIND(";",AF43)-1),AF43),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2293,11 +2293,11 @@
         <v/>
       </c>
       <c r="AL44">
-        <f>IF(AE44="","",HYPERLINK(AE44,"before"))</f>
+        <f>IF(AE44="","",HYPERLINK(IFERROR(LEFT(AE44,FIND(";",AE44)-1),AE44),"before"))</f>
         <v/>
       </c>
       <c r="AM44">
-        <f>IF(AF44="","",HYPERLINK(AF44,"after"))</f>
+        <f>IF(AF44="","",HYPERLINK(IFERROR(LEFT(AF44,FIND(";",AF44)-1),AF44),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2329,11 +2329,11 @@
         <v/>
       </c>
       <c r="AL45">
-        <f>IF(AE45="","",HYPERLINK(AE45,"before"))</f>
+        <f>IF(AE45="","",HYPERLINK(IFERROR(LEFT(AE45,FIND(";",AE45)-1),AE45),"before"))</f>
         <v/>
       </c>
       <c r="AM45">
-        <f>IF(AF45="","",HYPERLINK(AF45,"after"))</f>
+        <f>IF(AF45="","",HYPERLINK(IFERROR(LEFT(AF45,FIND(";",AF45)-1),AF45),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2365,11 +2365,11 @@
         <v/>
       </c>
       <c r="AL46">
-        <f>IF(AE46="","",HYPERLINK(AE46,"before"))</f>
+        <f>IF(AE46="","",HYPERLINK(IFERROR(LEFT(AE46,FIND(";",AE46)-1),AE46),"before"))</f>
         <v/>
       </c>
       <c r="AM46">
-        <f>IF(AF46="","",HYPERLINK(AF46,"after"))</f>
+        <f>IF(AF46="","",HYPERLINK(IFERROR(LEFT(AF46,FIND(";",AF46)-1),AF46),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2401,11 +2401,11 @@
         <v/>
       </c>
       <c r="AL47">
-        <f>IF(AE47="","",HYPERLINK(AE47,"before"))</f>
+        <f>IF(AE47="","",HYPERLINK(IFERROR(LEFT(AE47,FIND(";",AE47)-1),AE47),"before"))</f>
         <v/>
       </c>
       <c r="AM47">
-        <f>IF(AF47="","",HYPERLINK(AF47,"after"))</f>
+        <f>IF(AF47="","",HYPERLINK(IFERROR(LEFT(AF47,FIND(";",AF47)-1),AF47),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2437,11 +2437,11 @@
         <v/>
       </c>
       <c r="AL48">
-        <f>IF(AE48="","",HYPERLINK(AE48,"before"))</f>
+        <f>IF(AE48="","",HYPERLINK(IFERROR(LEFT(AE48,FIND(";",AE48)-1),AE48),"before"))</f>
         <v/>
       </c>
       <c r="AM48">
-        <f>IF(AF48="","",HYPERLINK(AF48,"after"))</f>
+        <f>IF(AF48="","",HYPERLINK(IFERROR(LEFT(AF48,FIND(";",AF48)-1),AF48),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2473,11 +2473,11 @@
         <v/>
       </c>
       <c r="AL49">
-        <f>IF(AE49="","",HYPERLINK(AE49,"before"))</f>
+        <f>IF(AE49="","",HYPERLINK(IFERROR(LEFT(AE49,FIND(";",AE49)-1),AE49),"before"))</f>
         <v/>
       </c>
       <c r="AM49">
-        <f>IF(AF49="","",HYPERLINK(AF49,"after"))</f>
+        <f>IF(AF49="","",HYPERLINK(IFERROR(LEFT(AF49,FIND(";",AF49)-1),AF49),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2509,11 +2509,11 @@
         <v/>
       </c>
       <c r="AL50">
-        <f>IF(AE50="","",HYPERLINK(AE50,"before"))</f>
+        <f>IF(AE50="","",HYPERLINK(IFERROR(LEFT(AE50,FIND(";",AE50)-1),AE50),"before"))</f>
         <v/>
       </c>
       <c r="AM50">
-        <f>IF(AF50="","",HYPERLINK(AF50,"after"))</f>
+        <f>IF(AF50="","",HYPERLINK(IFERROR(LEFT(AF50,FIND(";",AF50)-1),AF50),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2545,11 +2545,11 @@
         <v/>
       </c>
       <c r="AL51">
-        <f>IF(AE51="","",HYPERLINK(AE51,"before"))</f>
+        <f>IF(AE51="","",HYPERLINK(IFERROR(LEFT(AE51,FIND(";",AE51)-1),AE51),"before"))</f>
         <v/>
       </c>
       <c r="AM51">
-        <f>IF(AF51="","",HYPERLINK(AF51,"after"))</f>
+        <f>IF(AF51="","",HYPERLINK(IFERROR(LEFT(AF51,FIND(";",AF51)-1),AF51),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2581,11 +2581,11 @@
         <v/>
       </c>
       <c r="AL52">
-        <f>IF(AE52="","",HYPERLINK(AE52,"before"))</f>
+        <f>IF(AE52="","",HYPERLINK(IFERROR(LEFT(AE52,FIND(";",AE52)-1),AE52),"before"))</f>
         <v/>
       </c>
       <c r="AM52">
-        <f>IF(AF52="","",HYPERLINK(AF52,"after"))</f>
+        <f>IF(AF52="","",HYPERLINK(IFERROR(LEFT(AF52,FIND(";",AF52)-1),AF52),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2617,11 +2617,11 @@
         <v/>
       </c>
       <c r="AL53">
-        <f>IF(AE53="","",HYPERLINK(AE53,"before"))</f>
+        <f>IF(AE53="","",HYPERLINK(IFERROR(LEFT(AE53,FIND(";",AE53)-1),AE53),"before"))</f>
         <v/>
       </c>
       <c r="AM53">
-        <f>IF(AF53="","",HYPERLINK(AF53,"after"))</f>
+        <f>IF(AF53="","",HYPERLINK(IFERROR(LEFT(AF53,FIND(";",AF53)-1),AF53),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2653,11 +2653,11 @@
         <v/>
       </c>
       <c r="AL54">
-        <f>IF(AE54="","",HYPERLINK(AE54,"before"))</f>
+        <f>IF(AE54="","",HYPERLINK(IFERROR(LEFT(AE54,FIND(";",AE54)-1),AE54),"before"))</f>
         <v/>
       </c>
       <c r="AM54">
-        <f>IF(AF54="","",HYPERLINK(AF54,"after"))</f>
+        <f>IF(AF54="","",HYPERLINK(IFERROR(LEFT(AF54,FIND(";",AF54)-1),AF54),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2689,11 +2689,11 @@
         <v/>
       </c>
       <c r="AL55">
-        <f>IF(AE55="","",HYPERLINK(AE55,"before"))</f>
+        <f>IF(AE55="","",HYPERLINK(IFERROR(LEFT(AE55,FIND(";",AE55)-1),AE55),"before"))</f>
         <v/>
       </c>
       <c r="AM55">
-        <f>IF(AF55="","",HYPERLINK(AF55,"after"))</f>
+        <f>IF(AF55="","",HYPERLINK(IFERROR(LEFT(AF55,FIND(";",AF55)-1),AF55),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2725,11 +2725,11 @@
         <v/>
       </c>
       <c r="AL56">
-        <f>IF(AE56="","",HYPERLINK(AE56,"before"))</f>
+        <f>IF(AE56="","",HYPERLINK(IFERROR(LEFT(AE56,FIND(";",AE56)-1),AE56),"before"))</f>
         <v/>
       </c>
       <c r="AM56">
-        <f>IF(AF56="","",HYPERLINK(AF56,"after"))</f>
+        <f>IF(AF56="","",HYPERLINK(IFERROR(LEFT(AF56,FIND(";",AF56)-1),AF56),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2761,11 +2761,11 @@
         <v/>
       </c>
       <c r="AL57">
-        <f>IF(AE57="","",HYPERLINK(AE57,"before"))</f>
+        <f>IF(AE57="","",HYPERLINK(IFERROR(LEFT(AE57,FIND(";",AE57)-1),AE57),"before"))</f>
         <v/>
       </c>
       <c r="AM57">
-        <f>IF(AF57="","",HYPERLINK(AF57,"after"))</f>
+        <f>IF(AF57="","",HYPERLINK(IFERROR(LEFT(AF57,FIND(";",AF57)-1),AF57),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2797,11 +2797,11 @@
         <v/>
       </c>
       <c r="AL58">
-        <f>IF(AE58="","",HYPERLINK(AE58,"before"))</f>
+        <f>IF(AE58="","",HYPERLINK(IFERROR(LEFT(AE58,FIND(";",AE58)-1),AE58),"before"))</f>
         <v/>
       </c>
       <c r="AM58">
-        <f>IF(AF58="","",HYPERLINK(AF58,"after"))</f>
+        <f>IF(AF58="","",HYPERLINK(IFERROR(LEFT(AF58,FIND(";",AF58)-1),AF58),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2833,11 +2833,11 @@
         <v/>
       </c>
       <c r="AL59">
-        <f>IF(AE59="","",HYPERLINK(AE59,"before"))</f>
+        <f>IF(AE59="","",HYPERLINK(IFERROR(LEFT(AE59,FIND(";",AE59)-1),AE59),"before"))</f>
         <v/>
       </c>
       <c r="AM59">
-        <f>IF(AF59="","",HYPERLINK(AF59,"after"))</f>
+        <f>IF(AF59="","",HYPERLINK(IFERROR(LEFT(AF59,FIND(";",AF59)-1),AF59),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2869,11 +2869,11 @@
         <v/>
       </c>
       <c r="AL60">
-        <f>IF(AE60="","",HYPERLINK(AE60,"before"))</f>
+        <f>IF(AE60="","",HYPERLINK(IFERROR(LEFT(AE60,FIND(";",AE60)-1),AE60),"before"))</f>
         <v/>
       </c>
       <c r="AM60">
-        <f>IF(AF60="","",HYPERLINK(AF60,"after"))</f>
+        <f>IF(AF60="","",HYPERLINK(IFERROR(LEFT(AF60,FIND(";",AF60)-1),AF60),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2905,11 +2905,11 @@
         <v/>
       </c>
       <c r="AL61">
-        <f>IF(AE61="","",HYPERLINK(AE61,"before"))</f>
+        <f>IF(AE61="","",HYPERLINK(IFERROR(LEFT(AE61,FIND(";",AE61)-1),AE61),"before"))</f>
         <v/>
       </c>
       <c r="AM61">
-        <f>IF(AF61="","",HYPERLINK(AF61,"after"))</f>
+        <f>IF(AF61="","",HYPERLINK(IFERROR(LEFT(AF61,FIND(";",AF61)-1),AF61),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2941,11 +2941,11 @@
         <v/>
       </c>
       <c r="AL62">
-        <f>IF(AE62="","",HYPERLINK(AE62,"before"))</f>
+        <f>IF(AE62="","",HYPERLINK(IFERROR(LEFT(AE62,FIND(";",AE62)-1),AE62),"before"))</f>
         <v/>
       </c>
       <c r="AM62">
-        <f>IF(AF62="","",HYPERLINK(AF62,"after"))</f>
+        <f>IF(AF62="","",HYPERLINK(IFERROR(LEFT(AF62,FIND(";",AF62)-1),AF62),"after"))</f>
         <v/>
       </c>
     </row>
@@ -2977,11 +2977,11 @@
         <v/>
       </c>
       <c r="AL63">
-        <f>IF(AE63="","",HYPERLINK(AE63,"before"))</f>
+        <f>IF(AE63="","",HYPERLINK(IFERROR(LEFT(AE63,FIND(";",AE63)-1),AE63),"before"))</f>
         <v/>
       </c>
       <c r="AM63">
-        <f>IF(AF63="","",HYPERLINK(AF63,"after"))</f>
+        <f>IF(AF63="","",HYPERLINK(IFERROR(LEFT(AF63,FIND(";",AF63)-1),AF63),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3013,11 +3013,11 @@
         <v/>
       </c>
       <c r="AL64">
-        <f>IF(AE64="","",HYPERLINK(AE64,"before"))</f>
+        <f>IF(AE64="","",HYPERLINK(IFERROR(LEFT(AE64,FIND(";",AE64)-1),AE64),"before"))</f>
         <v/>
       </c>
       <c r="AM64">
-        <f>IF(AF64="","",HYPERLINK(AF64,"after"))</f>
+        <f>IF(AF64="","",HYPERLINK(IFERROR(LEFT(AF64,FIND(";",AF64)-1),AF64),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3049,11 +3049,11 @@
         <v/>
       </c>
       <c r="AL65">
-        <f>IF(AE65="","",HYPERLINK(AE65,"before"))</f>
+        <f>IF(AE65="","",HYPERLINK(IFERROR(LEFT(AE65,FIND(";",AE65)-1),AE65),"before"))</f>
         <v/>
       </c>
       <c r="AM65">
-        <f>IF(AF65="","",HYPERLINK(AF65,"after"))</f>
+        <f>IF(AF65="","",HYPERLINK(IFERROR(LEFT(AF65,FIND(";",AF65)-1),AF65),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3085,11 +3085,11 @@
         <v/>
       </c>
       <c r="AL66">
-        <f>IF(AE66="","",HYPERLINK(AE66,"before"))</f>
+        <f>IF(AE66="","",HYPERLINK(IFERROR(LEFT(AE66,FIND(";",AE66)-1),AE66),"before"))</f>
         <v/>
       </c>
       <c r="AM66">
-        <f>IF(AF66="","",HYPERLINK(AF66,"after"))</f>
+        <f>IF(AF66="","",HYPERLINK(IFERROR(LEFT(AF66,FIND(";",AF66)-1),AF66),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3121,11 +3121,11 @@
         <v/>
       </c>
       <c r="AL67">
-        <f>IF(AE67="","",HYPERLINK(AE67,"before"))</f>
+        <f>IF(AE67="","",HYPERLINK(IFERROR(LEFT(AE67,FIND(";",AE67)-1),AE67),"before"))</f>
         <v/>
       </c>
       <c r="AM67">
-        <f>IF(AF67="","",HYPERLINK(AF67,"after"))</f>
+        <f>IF(AF67="","",HYPERLINK(IFERROR(LEFT(AF67,FIND(";",AF67)-1),AF67),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3157,11 +3157,11 @@
         <v/>
       </c>
       <c r="AL68">
-        <f>IF(AE68="","",HYPERLINK(AE68,"before"))</f>
+        <f>IF(AE68="","",HYPERLINK(IFERROR(LEFT(AE68,FIND(";",AE68)-1),AE68),"before"))</f>
         <v/>
       </c>
       <c r="AM68">
-        <f>IF(AF68="","",HYPERLINK(AF68,"after"))</f>
+        <f>IF(AF68="","",HYPERLINK(IFERROR(LEFT(AF68,FIND(";",AF68)-1),AF68),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3193,11 +3193,11 @@
         <v/>
       </c>
       <c r="AL69">
-        <f>IF(AE69="","",HYPERLINK(AE69,"before"))</f>
+        <f>IF(AE69="","",HYPERLINK(IFERROR(LEFT(AE69,FIND(";",AE69)-1),AE69),"before"))</f>
         <v/>
       </c>
       <c r="AM69">
-        <f>IF(AF69="","",HYPERLINK(AF69,"after"))</f>
+        <f>IF(AF69="","",HYPERLINK(IFERROR(LEFT(AF69,FIND(";",AF69)-1),AF69),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3229,11 +3229,11 @@
         <v/>
       </c>
       <c r="AL70">
-        <f>IF(AE70="","",HYPERLINK(AE70,"before"))</f>
+        <f>IF(AE70="","",HYPERLINK(IFERROR(LEFT(AE70,FIND(";",AE70)-1),AE70),"before"))</f>
         <v/>
       </c>
       <c r="AM70">
-        <f>IF(AF70="","",HYPERLINK(AF70,"after"))</f>
+        <f>IF(AF70="","",HYPERLINK(IFERROR(LEFT(AF70,FIND(";",AF70)-1),AF70),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3265,11 +3265,11 @@
         <v/>
       </c>
       <c r="AL71">
-        <f>IF(AE71="","",HYPERLINK(AE71,"before"))</f>
+        <f>IF(AE71="","",HYPERLINK(IFERROR(LEFT(AE71,FIND(";",AE71)-1),AE71),"before"))</f>
         <v/>
       </c>
       <c r="AM71">
-        <f>IF(AF71="","",HYPERLINK(AF71,"after"))</f>
+        <f>IF(AF71="","",HYPERLINK(IFERROR(LEFT(AF71,FIND(";",AF71)-1),AF71),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3301,11 +3301,11 @@
         <v/>
       </c>
       <c r="AL72">
-        <f>IF(AE72="","",HYPERLINK(AE72,"before"))</f>
+        <f>IF(AE72="","",HYPERLINK(IFERROR(LEFT(AE72,FIND(";",AE72)-1),AE72),"before"))</f>
         <v/>
       </c>
       <c r="AM72">
-        <f>IF(AF72="","",HYPERLINK(AF72,"after"))</f>
+        <f>IF(AF72="","",HYPERLINK(IFERROR(LEFT(AF72,FIND(";",AF72)-1),AF72),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3337,11 +3337,11 @@
         <v/>
       </c>
       <c r="AL73">
-        <f>IF(AE73="","",HYPERLINK(AE73,"before"))</f>
+        <f>IF(AE73="","",HYPERLINK(IFERROR(LEFT(AE73,FIND(";",AE73)-1),AE73),"before"))</f>
         <v/>
       </c>
       <c r="AM73">
-        <f>IF(AF73="","",HYPERLINK(AF73,"after"))</f>
+        <f>IF(AF73="","",HYPERLINK(IFERROR(LEFT(AF73,FIND(";",AF73)-1),AF73),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3373,11 +3373,11 @@
         <v/>
       </c>
       <c r="AL74">
-        <f>IF(AE74="","",HYPERLINK(AE74,"before"))</f>
+        <f>IF(AE74="","",HYPERLINK(IFERROR(LEFT(AE74,FIND(";",AE74)-1),AE74),"before"))</f>
         <v/>
       </c>
       <c r="AM74">
-        <f>IF(AF74="","",HYPERLINK(AF74,"after"))</f>
+        <f>IF(AF74="","",HYPERLINK(IFERROR(LEFT(AF74,FIND(";",AF74)-1),AF74),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3409,11 +3409,11 @@
         <v/>
       </c>
       <c r="AL75">
-        <f>IF(AE75="","",HYPERLINK(AE75,"before"))</f>
+        <f>IF(AE75="","",HYPERLINK(IFERROR(LEFT(AE75,FIND(";",AE75)-1),AE75),"before"))</f>
         <v/>
       </c>
       <c r="AM75">
-        <f>IF(AF75="","",HYPERLINK(AF75,"after"))</f>
+        <f>IF(AF75="","",HYPERLINK(IFERROR(LEFT(AF75,FIND(";",AF75)-1),AF75),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3445,11 +3445,11 @@
         <v/>
       </c>
       <c r="AL76">
-        <f>IF(AE76="","",HYPERLINK(AE76,"before"))</f>
+        <f>IF(AE76="","",HYPERLINK(IFERROR(LEFT(AE76,FIND(";",AE76)-1),AE76),"before"))</f>
         <v/>
       </c>
       <c r="AM76">
-        <f>IF(AF76="","",HYPERLINK(AF76,"after"))</f>
+        <f>IF(AF76="","",HYPERLINK(IFERROR(LEFT(AF76,FIND(";",AF76)-1),AF76),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3481,11 +3481,11 @@
         <v/>
       </c>
       <c r="AL77">
-        <f>IF(AE77="","",HYPERLINK(AE77,"before"))</f>
+        <f>IF(AE77="","",HYPERLINK(IFERROR(LEFT(AE77,FIND(";",AE77)-1),AE77),"before"))</f>
         <v/>
       </c>
       <c r="AM77">
-        <f>IF(AF77="","",HYPERLINK(AF77,"after"))</f>
+        <f>IF(AF77="","",HYPERLINK(IFERROR(LEFT(AF77,FIND(";",AF77)-1),AF77),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3517,11 +3517,11 @@
         <v/>
       </c>
       <c r="AL78">
-        <f>IF(AE78="","",HYPERLINK(AE78,"before"))</f>
+        <f>IF(AE78="","",HYPERLINK(IFERROR(LEFT(AE78,FIND(";",AE78)-1),AE78),"before"))</f>
         <v/>
       </c>
       <c r="AM78">
-        <f>IF(AF78="","",HYPERLINK(AF78,"after"))</f>
+        <f>IF(AF78="","",HYPERLINK(IFERROR(LEFT(AF78,FIND(";",AF78)-1),AF78),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3553,11 +3553,11 @@
         <v/>
       </c>
       <c r="AL79">
-        <f>IF(AE79="","",HYPERLINK(AE79,"before"))</f>
+        <f>IF(AE79="","",HYPERLINK(IFERROR(LEFT(AE79,FIND(";",AE79)-1),AE79),"before"))</f>
         <v/>
       </c>
       <c r="AM79">
-        <f>IF(AF79="","",HYPERLINK(AF79,"after"))</f>
+        <f>IF(AF79="","",HYPERLINK(IFERROR(LEFT(AF79,FIND(";",AF79)-1),AF79),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3589,11 +3589,11 @@
         <v/>
       </c>
       <c r="AL80">
-        <f>IF(AE80="","",HYPERLINK(AE80,"before"))</f>
+        <f>IF(AE80="","",HYPERLINK(IFERROR(LEFT(AE80,FIND(";",AE80)-1),AE80),"before"))</f>
         <v/>
       </c>
       <c r="AM80">
-        <f>IF(AF80="","",HYPERLINK(AF80,"after"))</f>
+        <f>IF(AF80="","",HYPERLINK(IFERROR(LEFT(AF80,FIND(";",AF80)-1),AF80),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3625,11 +3625,11 @@
         <v/>
       </c>
       <c r="AL81">
-        <f>IF(AE81="","",HYPERLINK(AE81,"before"))</f>
+        <f>IF(AE81="","",HYPERLINK(IFERROR(LEFT(AE81,FIND(";",AE81)-1),AE81),"before"))</f>
         <v/>
       </c>
       <c r="AM81">
-        <f>IF(AF81="","",HYPERLINK(AF81,"after"))</f>
+        <f>IF(AF81="","",HYPERLINK(IFERROR(LEFT(AF81,FIND(";",AF81)-1),AF81),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3661,11 +3661,11 @@
         <v/>
       </c>
       <c r="AL82">
-        <f>IF(AE82="","",HYPERLINK(AE82,"before"))</f>
+        <f>IF(AE82="","",HYPERLINK(IFERROR(LEFT(AE82,FIND(";",AE82)-1),AE82),"before"))</f>
         <v/>
       </c>
       <c r="AM82">
-        <f>IF(AF82="","",HYPERLINK(AF82,"after"))</f>
+        <f>IF(AF82="","",HYPERLINK(IFERROR(LEFT(AF82,FIND(";",AF82)-1),AF82),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3697,11 +3697,11 @@
         <v/>
       </c>
       <c r="AL83">
-        <f>IF(AE83="","",HYPERLINK(AE83,"before"))</f>
+        <f>IF(AE83="","",HYPERLINK(IFERROR(LEFT(AE83,FIND(";",AE83)-1),AE83),"before"))</f>
         <v/>
       </c>
       <c r="AM83">
-        <f>IF(AF83="","",HYPERLINK(AF83,"after"))</f>
+        <f>IF(AF83="","",HYPERLINK(IFERROR(LEFT(AF83,FIND(";",AF83)-1),AF83),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3733,11 +3733,11 @@
         <v/>
       </c>
       <c r="AL84">
-        <f>IF(AE84="","",HYPERLINK(AE84,"before"))</f>
+        <f>IF(AE84="","",HYPERLINK(IFERROR(LEFT(AE84,FIND(";",AE84)-1),AE84),"before"))</f>
         <v/>
       </c>
       <c r="AM84">
-        <f>IF(AF84="","",HYPERLINK(AF84,"after"))</f>
+        <f>IF(AF84="","",HYPERLINK(IFERROR(LEFT(AF84,FIND(";",AF84)-1),AF84),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3769,11 +3769,11 @@
         <v/>
       </c>
       <c r="AL85">
-        <f>IF(AE85="","",HYPERLINK(AE85,"before"))</f>
+        <f>IF(AE85="","",HYPERLINK(IFERROR(LEFT(AE85,FIND(";",AE85)-1),AE85),"before"))</f>
         <v/>
       </c>
       <c r="AM85">
-        <f>IF(AF85="","",HYPERLINK(AF85,"after"))</f>
+        <f>IF(AF85="","",HYPERLINK(IFERROR(LEFT(AF85,FIND(";",AF85)-1),AF85),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3805,11 +3805,11 @@
         <v/>
       </c>
       <c r="AL86">
-        <f>IF(AE86="","",HYPERLINK(AE86,"before"))</f>
+        <f>IF(AE86="","",HYPERLINK(IFERROR(LEFT(AE86,FIND(";",AE86)-1),AE86),"before"))</f>
         <v/>
       </c>
       <c r="AM86">
-        <f>IF(AF86="","",HYPERLINK(AF86,"after"))</f>
+        <f>IF(AF86="","",HYPERLINK(IFERROR(LEFT(AF86,FIND(";",AF86)-1),AF86),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3841,11 +3841,11 @@
         <v/>
       </c>
       <c r="AL87">
-        <f>IF(AE87="","",HYPERLINK(AE87,"before"))</f>
+        <f>IF(AE87="","",HYPERLINK(IFERROR(LEFT(AE87,FIND(";",AE87)-1),AE87),"before"))</f>
         <v/>
       </c>
       <c r="AM87">
-        <f>IF(AF87="","",HYPERLINK(AF87,"after"))</f>
+        <f>IF(AF87="","",HYPERLINK(IFERROR(LEFT(AF87,FIND(";",AF87)-1),AF87),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3877,11 +3877,11 @@
         <v/>
       </c>
       <c r="AL88">
-        <f>IF(AE88="","",HYPERLINK(AE88,"before"))</f>
+        <f>IF(AE88="","",HYPERLINK(IFERROR(LEFT(AE88,FIND(";",AE88)-1),AE88),"before"))</f>
         <v/>
       </c>
       <c r="AM88">
-        <f>IF(AF88="","",HYPERLINK(AF88,"after"))</f>
+        <f>IF(AF88="","",HYPERLINK(IFERROR(LEFT(AF88,FIND(";",AF88)-1),AF88),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3913,11 +3913,11 @@
         <v/>
       </c>
       <c r="AL89">
-        <f>IF(AE89="","",HYPERLINK(AE89,"before"))</f>
+        <f>IF(AE89="","",HYPERLINK(IFERROR(LEFT(AE89,FIND(";",AE89)-1),AE89),"before"))</f>
         <v/>
       </c>
       <c r="AM89">
-        <f>IF(AF89="","",HYPERLINK(AF89,"after"))</f>
+        <f>IF(AF89="","",HYPERLINK(IFERROR(LEFT(AF89,FIND(";",AF89)-1),AF89),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3949,11 +3949,11 @@
         <v/>
       </c>
       <c r="AL90">
-        <f>IF(AE90="","",HYPERLINK(AE90,"before"))</f>
+        <f>IF(AE90="","",HYPERLINK(IFERROR(LEFT(AE90,FIND(";",AE90)-1),AE90),"before"))</f>
         <v/>
       </c>
       <c r="AM90">
-        <f>IF(AF90="","",HYPERLINK(AF90,"after"))</f>
+        <f>IF(AF90="","",HYPERLINK(IFERROR(LEFT(AF90,FIND(";",AF90)-1),AF90),"after"))</f>
         <v/>
       </c>
     </row>
@@ -3985,11 +3985,11 @@
         <v/>
       </c>
       <c r="AL91">
-        <f>IF(AE91="","",HYPERLINK(AE91,"before"))</f>
+        <f>IF(AE91="","",HYPERLINK(IFERROR(LEFT(AE91,FIND(";",AE91)-1),AE91),"before"))</f>
         <v/>
       </c>
       <c r="AM91">
-        <f>IF(AF91="","",HYPERLINK(AF91,"after"))</f>
+        <f>IF(AF91="","",HYPERLINK(IFERROR(LEFT(AF91,FIND(";",AF91)-1),AF91),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4021,11 +4021,11 @@
         <v/>
       </c>
       <c r="AL92">
-        <f>IF(AE92="","",HYPERLINK(AE92,"before"))</f>
+        <f>IF(AE92="","",HYPERLINK(IFERROR(LEFT(AE92,FIND(";",AE92)-1),AE92),"before"))</f>
         <v/>
       </c>
       <c r="AM92">
-        <f>IF(AF92="","",HYPERLINK(AF92,"after"))</f>
+        <f>IF(AF92="","",HYPERLINK(IFERROR(LEFT(AF92,FIND(";",AF92)-1),AF92),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4057,11 +4057,11 @@
         <v/>
       </c>
       <c r="AL93">
-        <f>IF(AE93="","",HYPERLINK(AE93,"before"))</f>
+        <f>IF(AE93="","",HYPERLINK(IFERROR(LEFT(AE93,FIND(";",AE93)-1),AE93),"before"))</f>
         <v/>
       </c>
       <c r="AM93">
-        <f>IF(AF93="","",HYPERLINK(AF93,"after"))</f>
+        <f>IF(AF93="","",HYPERLINK(IFERROR(LEFT(AF93,FIND(";",AF93)-1),AF93),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4093,11 +4093,11 @@
         <v/>
       </c>
       <c r="AL94">
-        <f>IF(AE94="","",HYPERLINK(AE94,"before"))</f>
+        <f>IF(AE94="","",HYPERLINK(IFERROR(LEFT(AE94,FIND(";",AE94)-1),AE94),"before"))</f>
         <v/>
       </c>
       <c r="AM94">
-        <f>IF(AF94="","",HYPERLINK(AF94,"after"))</f>
+        <f>IF(AF94="","",HYPERLINK(IFERROR(LEFT(AF94,FIND(";",AF94)-1),AF94),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4129,11 +4129,11 @@
         <v/>
       </c>
       <c r="AL95">
-        <f>IF(AE95="","",HYPERLINK(AE95,"before"))</f>
+        <f>IF(AE95="","",HYPERLINK(IFERROR(LEFT(AE95,FIND(";",AE95)-1),AE95),"before"))</f>
         <v/>
       </c>
       <c r="AM95">
-        <f>IF(AF95="","",HYPERLINK(AF95,"after"))</f>
+        <f>IF(AF95="","",HYPERLINK(IFERROR(LEFT(AF95,FIND(";",AF95)-1),AF95),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4165,11 +4165,11 @@
         <v/>
       </c>
       <c r="AL96">
-        <f>IF(AE96="","",HYPERLINK(AE96,"before"))</f>
+        <f>IF(AE96="","",HYPERLINK(IFERROR(LEFT(AE96,FIND(";",AE96)-1),AE96),"before"))</f>
         <v/>
       </c>
       <c r="AM96">
-        <f>IF(AF96="","",HYPERLINK(AF96,"after"))</f>
+        <f>IF(AF96="","",HYPERLINK(IFERROR(LEFT(AF96,FIND(";",AF96)-1),AF96),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4201,11 +4201,11 @@
         <v/>
       </c>
       <c r="AL97">
-        <f>IF(AE97="","",HYPERLINK(AE97,"before"))</f>
+        <f>IF(AE97="","",HYPERLINK(IFERROR(LEFT(AE97,FIND(";",AE97)-1),AE97),"before"))</f>
         <v/>
       </c>
       <c r="AM97">
-        <f>IF(AF97="","",HYPERLINK(AF97,"after"))</f>
+        <f>IF(AF97="","",HYPERLINK(IFERROR(LEFT(AF97,FIND(";",AF97)-1),AF97),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4237,11 +4237,11 @@
         <v/>
       </c>
       <c r="AL98">
-        <f>IF(AE98="","",HYPERLINK(AE98,"before"))</f>
+        <f>IF(AE98="","",HYPERLINK(IFERROR(LEFT(AE98,FIND(";",AE98)-1),AE98),"before"))</f>
         <v/>
       </c>
       <c r="AM98">
-        <f>IF(AF98="","",HYPERLINK(AF98,"after"))</f>
+        <f>IF(AF98="","",HYPERLINK(IFERROR(LEFT(AF98,FIND(";",AF98)-1),AF98),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4273,11 +4273,11 @@
         <v/>
       </c>
       <c r="AL99">
-        <f>IF(AE99="","",HYPERLINK(AE99,"before"))</f>
+        <f>IF(AE99="","",HYPERLINK(IFERROR(LEFT(AE99,FIND(";",AE99)-1),AE99),"before"))</f>
         <v/>
       </c>
       <c r="AM99">
-        <f>IF(AF99="","",HYPERLINK(AF99,"after"))</f>
+        <f>IF(AF99="","",HYPERLINK(IFERROR(LEFT(AF99,FIND(";",AF99)-1),AF99),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4309,11 +4309,11 @@
         <v/>
       </c>
       <c r="AL100">
-        <f>IF(AE100="","",HYPERLINK(AE100,"before"))</f>
+        <f>IF(AE100="","",HYPERLINK(IFERROR(LEFT(AE100,FIND(";",AE100)-1),AE100),"before"))</f>
         <v/>
       </c>
       <c r="AM100">
-        <f>IF(AF100="","",HYPERLINK(AF100,"after"))</f>
+        <f>IF(AF100="","",HYPERLINK(IFERROR(LEFT(AF100,FIND(";",AF100)-1),AF100),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4345,11 +4345,11 @@
         <v/>
       </c>
       <c r="AL101">
-        <f>IF(AE101="","",HYPERLINK(AE101,"before"))</f>
+        <f>IF(AE101="","",HYPERLINK(IFERROR(LEFT(AE101,FIND(";",AE101)-1),AE101),"before"))</f>
         <v/>
       </c>
       <c r="AM101">
-        <f>IF(AF101="","",HYPERLINK(AF101,"after"))</f>
+        <f>IF(AF101="","",HYPERLINK(IFERROR(LEFT(AF101,FIND(";",AF101)-1),AF101),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4381,11 +4381,11 @@
         <v/>
       </c>
       <c r="AL102">
-        <f>IF(AE102="","",HYPERLINK(AE102,"before"))</f>
+        <f>IF(AE102="","",HYPERLINK(IFERROR(LEFT(AE102,FIND(";",AE102)-1),AE102),"before"))</f>
         <v/>
       </c>
       <c r="AM102">
-        <f>IF(AF102="","",HYPERLINK(AF102,"after"))</f>
+        <f>IF(AF102="","",HYPERLINK(IFERROR(LEFT(AF102,FIND(";",AF102)-1),AF102),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4417,11 +4417,11 @@
         <v/>
       </c>
       <c r="AL103">
-        <f>IF(AE103="","",HYPERLINK(AE103,"before"))</f>
+        <f>IF(AE103="","",HYPERLINK(IFERROR(LEFT(AE103,FIND(";",AE103)-1),AE103),"before"))</f>
         <v/>
       </c>
       <c r="AM103">
-        <f>IF(AF103="","",HYPERLINK(AF103,"after"))</f>
+        <f>IF(AF103="","",HYPERLINK(IFERROR(LEFT(AF103,FIND(";",AF103)-1),AF103),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4453,11 +4453,11 @@
         <v/>
       </c>
       <c r="AL104">
-        <f>IF(AE104="","",HYPERLINK(AE104,"before"))</f>
+        <f>IF(AE104="","",HYPERLINK(IFERROR(LEFT(AE104,FIND(";",AE104)-1),AE104),"before"))</f>
         <v/>
       </c>
       <c r="AM104">
-        <f>IF(AF104="","",HYPERLINK(AF104,"after"))</f>
+        <f>IF(AF104="","",HYPERLINK(IFERROR(LEFT(AF104,FIND(";",AF104)-1),AF104),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4489,11 +4489,11 @@
         <v/>
       </c>
       <c r="AL105">
-        <f>IF(AE105="","",HYPERLINK(AE105,"before"))</f>
+        <f>IF(AE105="","",HYPERLINK(IFERROR(LEFT(AE105,FIND(";",AE105)-1),AE105),"before"))</f>
         <v/>
       </c>
       <c r="AM105">
-        <f>IF(AF105="","",HYPERLINK(AF105,"after"))</f>
+        <f>IF(AF105="","",HYPERLINK(IFERROR(LEFT(AF105,FIND(";",AF105)-1),AF105),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4525,11 +4525,11 @@
         <v/>
       </c>
       <c r="AL106">
-        <f>IF(AE106="","",HYPERLINK(AE106,"before"))</f>
+        <f>IF(AE106="","",HYPERLINK(IFERROR(LEFT(AE106,FIND(";",AE106)-1),AE106),"before"))</f>
         <v/>
       </c>
       <c r="AM106">
-        <f>IF(AF106="","",HYPERLINK(AF106,"after"))</f>
+        <f>IF(AF106="","",HYPERLINK(IFERROR(LEFT(AF106,FIND(";",AF106)-1),AF106),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4561,11 +4561,11 @@
         <v/>
       </c>
       <c r="AL107">
-        <f>IF(AE107="","",HYPERLINK(AE107,"before"))</f>
+        <f>IF(AE107="","",HYPERLINK(IFERROR(LEFT(AE107,FIND(";",AE107)-1),AE107),"before"))</f>
         <v/>
       </c>
       <c r="AM107">
-        <f>IF(AF107="","",HYPERLINK(AF107,"after"))</f>
+        <f>IF(AF107="","",HYPERLINK(IFERROR(LEFT(AF107,FIND(";",AF107)-1),AF107),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4597,11 +4597,11 @@
         <v/>
       </c>
       <c r="AL108">
-        <f>IF(AE108="","",HYPERLINK(AE108,"before"))</f>
+        <f>IF(AE108="","",HYPERLINK(IFERROR(LEFT(AE108,FIND(";",AE108)-1),AE108),"before"))</f>
         <v/>
       </c>
       <c r="AM108">
-        <f>IF(AF108="","",HYPERLINK(AF108,"after"))</f>
+        <f>IF(AF108="","",HYPERLINK(IFERROR(LEFT(AF108,FIND(";",AF108)-1),AF108),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4633,11 +4633,11 @@
         <v/>
       </c>
       <c r="AL109">
-        <f>IF(AE109="","",HYPERLINK(AE109,"before"))</f>
+        <f>IF(AE109="","",HYPERLINK(IFERROR(LEFT(AE109,FIND(";",AE109)-1),AE109),"before"))</f>
         <v/>
       </c>
       <c r="AM109">
-        <f>IF(AF109="","",HYPERLINK(AF109,"after"))</f>
+        <f>IF(AF109="","",HYPERLINK(IFERROR(LEFT(AF109,FIND(";",AF109)-1),AF109),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4669,11 +4669,11 @@
         <v/>
       </c>
       <c r="AL110">
-        <f>IF(AE110="","",HYPERLINK(AE110,"before"))</f>
+        <f>IF(AE110="","",HYPERLINK(IFERROR(LEFT(AE110,FIND(";",AE110)-1),AE110),"before"))</f>
         <v/>
       </c>
       <c r="AM110">
-        <f>IF(AF110="","",HYPERLINK(AF110,"after"))</f>
+        <f>IF(AF110="","",HYPERLINK(IFERROR(LEFT(AF110,FIND(";",AF110)-1),AF110),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4705,11 +4705,11 @@
         <v/>
       </c>
       <c r="AL111">
-        <f>IF(AE111="","",HYPERLINK(AE111,"before"))</f>
+        <f>IF(AE111="","",HYPERLINK(IFERROR(LEFT(AE111,FIND(";",AE111)-1),AE111),"before"))</f>
         <v/>
       </c>
       <c r="AM111">
-        <f>IF(AF111="","",HYPERLINK(AF111,"after"))</f>
+        <f>IF(AF111="","",HYPERLINK(IFERROR(LEFT(AF111,FIND(";",AF111)-1),AF111),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4741,11 +4741,11 @@
         <v/>
       </c>
       <c r="AL112">
-        <f>IF(AE112="","",HYPERLINK(AE112,"before"))</f>
+        <f>IF(AE112="","",HYPERLINK(IFERROR(LEFT(AE112,FIND(";",AE112)-1),AE112),"before"))</f>
         <v/>
       </c>
       <c r="AM112">
-        <f>IF(AF112="","",HYPERLINK(AF112,"after"))</f>
+        <f>IF(AF112="","",HYPERLINK(IFERROR(LEFT(AF112,FIND(";",AF112)-1),AF112),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4777,11 +4777,11 @@
         <v/>
       </c>
       <c r="AL113">
-        <f>IF(AE113="","",HYPERLINK(AE113,"before"))</f>
+        <f>IF(AE113="","",HYPERLINK(IFERROR(LEFT(AE113,FIND(";",AE113)-1),AE113),"before"))</f>
         <v/>
       </c>
       <c r="AM113">
-        <f>IF(AF113="","",HYPERLINK(AF113,"after"))</f>
+        <f>IF(AF113="","",HYPERLINK(IFERROR(LEFT(AF113,FIND(";",AF113)-1),AF113),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4813,11 +4813,11 @@
         <v/>
       </c>
       <c r="AL114">
-        <f>IF(AE114="","",HYPERLINK(AE114,"before"))</f>
+        <f>IF(AE114="","",HYPERLINK(IFERROR(LEFT(AE114,FIND(";",AE114)-1),AE114),"before"))</f>
         <v/>
       </c>
       <c r="AM114">
-        <f>IF(AF114="","",HYPERLINK(AF114,"after"))</f>
+        <f>IF(AF114="","",HYPERLINK(IFERROR(LEFT(AF114,FIND(";",AF114)-1),AF114),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4849,11 +4849,11 @@
         <v/>
       </c>
       <c r="AL115">
-        <f>IF(AE115="","",HYPERLINK(AE115,"before"))</f>
+        <f>IF(AE115="","",HYPERLINK(IFERROR(LEFT(AE115,FIND(";",AE115)-1),AE115),"before"))</f>
         <v/>
       </c>
       <c r="AM115">
-        <f>IF(AF115="","",HYPERLINK(AF115,"after"))</f>
+        <f>IF(AF115="","",HYPERLINK(IFERROR(LEFT(AF115,FIND(";",AF115)-1),AF115),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4885,11 +4885,11 @@
         <v/>
       </c>
       <c r="AL116">
-        <f>IF(AE116="","",HYPERLINK(AE116,"before"))</f>
+        <f>IF(AE116="","",HYPERLINK(IFERROR(LEFT(AE116,FIND(";",AE116)-1),AE116),"before"))</f>
         <v/>
       </c>
       <c r="AM116">
-        <f>IF(AF116="","",HYPERLINK(AF116,"after"))</f>
+        <f>IF(AF116="","",HYPERLINK(IFERROR(LEFT(AF116,FIND(";",AF116)-1),AF116),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4921,11 +4921,11 @@
         <v/>
       </c>
       <c r="AL117">
-        <f>IF(AE117="","",HYPERLINK(AE117,"before"))</f>
+        <f>IF(AE117="","",HYPERLINK(IFERROR(LEFT(AE117,FIND(";",AE117)-1),AE117),"before"))</f>
         <v/>
       </c>
       <c r="AM117">
-        <f>IF(AF117="","",HYPERLINK(AF117,"after"))</f>
+        <f>IF(AF117="","",HYPERLINK(IFERROR(LEFT(AF117,FIND(";",AF117)-1),AF117),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4957,11 +4957,11 @@
         <v/>
       </c>
       <c r="AL118">
-        <f>IF(AE118="","",HYPERLINK(AE118,"before"))</f>
+        <f>IF(AE118="","",HYPERLINK(IFERROR(LEFT(AE118,FIND(";",AE118)-1),AE118),"before"))</f>
         <v/>
       </c>
       <c r="AM118">
-        <f>IF(AF118="","",HYPERLINK(AF118,"after"))</f>
+        <f>IF(AF118="","",HYPERLINK(IFERROR(LEFT(AF118,FIND(";",AF118)-1),AF118),"after"))</f>
         <v/>
       </c>
     </row>
@@ -4993,11 +4993,11 @@
         <v/>
       </c>
       <c r="AL119">
-        <f>IF(AE119="","",HYPERLINK(AE119,"before"))</f>
+        <f>IF(AE119="","",HYPERLINK(IFERROR(LEFT(AE119,FIND(";",AE119)-1),AE119),"before"))</f>
         <v/>
       </c>
       <c r="AM119">
-        <f>IF(AF119="","",HYPERLINK(AF119,"after"))</f>
+        <f>IF(AF119="","",HYPERLINK(IFERROR(LEFT(AF119,FIND(";",AF119)-1),AF119),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5029,11 +5029,11 @@
         <v/>
       </c>
       <c r="AL120">
-        <f>IF(AE120="","",HYPERLINK(AE120,"before"))</f>
+        <f>IF(AE120="","",HYPERLINK(IFERROR(LEFT(AE120,FIND(";",AE120)-1),AE120),"before"))</f>
         <v/>
       </c>
       <c r="AM120">
-        <f>IF(AF120="","",HYPERLINK(AF120,"after"))</f>
+        <f>IF(AF120="","",HYPERLINK(IFERROR(LEFT(AF120,FIND(";",AF120)-1),AF120),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5065,11 +5065,11 @@
         <v/>
       </c>
       <c r="AL121">
-        <f>IF(AE121="","",HYPERLINK(AE121,"before"))</f>
+        <f>IF(AE121="","",HYPERLINK(IFERROR(LEFT(AE121,FIND(";",AE121)-1),AE121),"before"))</f>
         <v/>
       </c>
       <c r="AM121">
-        <f>IF(AF121="","",HYPERLINK(AF121,"after"))</f>
+        <f>IF(AF121="","",HYPERLINK(IFERROR(LEFT(AF121,FIND(";",AF121)-1),AF121),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5101,11 +5101,11 @@
         <v/>
       </c>
       <c r="AL122">
-        <f>IF(AE122="","",HYPERLINK(AE122,"before"))</f>
+        <f>IF(AE122="","",HYPERLINK(IFERROR(LEFT(AE122,FIND(";",AE122)-1),AE122),"before"))</f>
         <v/>
       </c>
       <c r="AM122">
-        <f>IF(AF122="","",HYPERLINK(AF122,"after"))</f>
+        <f>IF(AF122="","",HYPERLINK(IFERROR(LEFT(AF122,FIND(";",AF122)-1),AF122),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5137,11 +5137,11 @@
         <v/>
       </c>
       <c r="AL123">
-        <f>IF(AE123="","",HYPERLINK(AE123,"before"))</f>
+        <f>IF(AE123="","",HYPERLINK(IFERROR(LEFT(AE123,FIND(";",AE123)-1),AE123),"before"))</f>
         <v/>
       </c>
       <c r="AM123">
-        <f>IF(AF123="","",HYPERLINK(AF123,"after"))</f>
+        <f>IF(AF123="","",HYPERLINK(IFERROR(LEFT(AF123,FIND(";",AF123)-1),AF123),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5173,11 +5173,11 @@
         <v/>
       </c>
       <c r="AL124">
-        <f>IF(AE124="","",HYPERLINK(AE124,"before"))</f>
+        <f>IF(AE124="","",HYPERLINK(IFERROR(LEFT(AE124,FIND(";",AE124)-1),AE124),"before"))</f>
         <v/>
       </c>
       <c r="AM124">
-        <f>IF(AF124="","",HYPERLINK(AF124,"after"))</f>
+        <f>IF(AF124="","",HYPERLINK(IFERROR(LEFT(AF124,FIND(";",AF124)-1),AF124),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5209,11 +5209,11 @@
         <v/>
       </c>
       <c r="AL125">
-        <f>IF(AE125="","",HYPERLINK(AE125,"before"))</f>
+        <f>IF(AE125="","",HYPERLINK(IFERROR(LEFT(AE125,FIND(";",AE125)-1),AE125),"before"))</f>
         <v/>
       </c>
       <c r="AM125">
-        <f>IF(AF125="","",HYPERLINK(AF125,"after"))</f>
+        <f>IF(AF125="","",HYPERLINK(IFERROR(LEFT(AF125,FIND(";",AF125)-1),AF125),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5245,11 +5245,11 @@
         <v/>
       </c>
       <c r="AL126">
-        <f>IF(AE126="","",HYPERLINK(AE126,"before"))</f>
+        <f>IF(AE126="","",HYPERLINK(IFERROR(LEFT(AE126,FIND(";",AE126)-1),AE126),"before"))</f>
         <v/>
       </c>
       <c r="AM126">
-        <f>IF(AF126="","",HYPERLINK(AF126,"after"))</f>
+        <f>IF(AF126="","",HYPERLINK(IFERROR(LEFT(AF126,FIND(";",AF126)-1),AF126),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5281,11 +5281,11 @@
         <v/>
       </c>
       <c r="AL127">
-        <f>IF(AE127="","",HYPERLINK(AE127,"before"))</f>
+        <f>IF(AE127="","",HYPERLINK(IFERROR(LEFT(AE127,FIND(";",AE127)-1),AE127),"before"))</f>
         <v/>
       </c>
       <c r="AM127">
-        <f>IF(AF127="","",HYPERLINK(AF127,"after"))</f>
+        <f>IF(AF127="","",HYPERLINK(IFERROR(LEFT(AF127,FIND(";",AF127)-1),AF127),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5317,11 +5317,11 @@
         <v/>
       </c>
       <c r="AL128">
-        <f>IF(AE128="","",HYPERLINK(AE128,"before"))</f>
+        <f>IF(AE128="","",HYPERLINK(IFERROR(LEFT(AE128,FIND(";",AE128)-1),AE128),"before"))</f>
         <v/>
       </c>
       <c r="AM128">
-        <f>IF(AF128="","",HYPERLINK(AF128,"after"))</f>
+        <f>IF(AF128="","",HYPERLINK(IFERROR(LEFT(AF128,FIND(";",AF128)-1),AF128),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5353,11 +5353,11 @@
         <v/>
       </c>
       <c r="AL129">
-        <f>IF(AE129="","",HYPERLINK(AE129,"before"))</f>
+        <f>IF(AE129="","",HYPERLINK(IFERROR(LEFT(AE129,FIND(";",AE129)-1),AE129),"before"))</f>
         <v/>
       </c>
       <c r="AM129">
-        <f>IF(AF129="","",HYPERLINK(AF129,"after"))</f>
+        <f>IF(AF129="","",HYPERLINK(IFERROR(LEFT(AF129,FIND(";",AF129)-1),AF129),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5389,11 +5389,11 @@
         <v/>
       </c>
       <c r="AL130">
-        <f>IF(AE130="","",HYPERLINK(AE130,"before"))</f>
+        <f>IF(AE130="","",HYPERLINK(IFERROR(LEFT(AE130,FIND(";",AE130)-1),AE130),"before"))</f>
         <v/>
       </c>
       <c r="AM130">
-        <f>IF(AF130="","",HYPERLINK(AF130,"after"))</f>
+        <f>IF(AF130="","",HYPERLINK(IFERROR(LEFT(AF130,FIND(";",AF130)-1),AF130),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5425,11 +5425,11 @@
         <v/>
       </c>
       <c r="AL131">
-        <f>IF(AE131="","",HYPERLINK(AE131,"before"))</f>
+        <f>IF(AE131="","",HYPERLINK(IFERROR(LEFT(AE131,FIND(";",AE131)-1),AE131),"before"))</f>
         <v/>
       </c>
       <c r="AM131">
-        <f>IF(AF131="","",HYPERLINK(AF131,"after"))</f>
+        <f>IF(AF131="","",HYPERLINK(IFERROR(LEFT(AF131,FIND(";",AF131)-1),AF131),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5461,11 +5461,11 @@
         <v/>
       </c>
       <c r="AL132">
-        <f>IF(AE132="","",HYPERLINK(AE132,"before"))</f>
+        <f>IF(AE132="","",HYPERLINK(IFERROR(LEFT(AE132,FIND(";",AE132)-1),AE132),"before"))</f>
         <v/>
       </c>
       <c r="AM132">
-        <f>IF(AF132="","",HYPERLINK(AF132,"after"))</f>
+        <f>IF(AF132="","",HYPERLINK(IFERROR(LEFT(AF132,FIND(";",AF132)-1),AF132),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5497,11 +5497,11 @@
         <v/>
       </c>
       <c r="AL133">
-        <f>IF(AE133="","",HYPERLINK(AE133,"before"))</f>
+        <f>IF(AE133="","",HYPERLINK(IFERROR(LEFT(AE133,FIND(";",AE133)-1),AE133),"before"))</f>
         <v/>
       </c>
       <c r="AM133">
-        <f>IF(AF133="","",HYPERLINK(AF133,"after"))</f>
+        <f>IF(AF133="","",HYPERLINK(IFERROR(LEFT(AF133,FIND(";",AF133)-1),AF133),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5533,11 +5533,11 @@
         <v/>
       </c>
       <c r="AL134">
-        <f>IF(AE134="","",HYPERLINK(AE134,"before"))</f>
+        <f>IF(AE134="","",HYPERLINK(IFERROR(LEFT(AE134,FIND(";",AE134)-1),AE134),"before"))</f>
         <v/>
       </c>
       <c r="AM134">
-        <f>IF(AF134="","",HYPERLINK(AF134,"after"))</f>
+        <f>IF(AF134="","",HYPERLINK(IFERROR(LEFT(AF134,FIND(";",AF134)-1),AF134),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5569,11 +5569,11 @@
         <v/>
       </c>
       <c r="AL135">
-        <f>IF(AE135="","",HYPERLINK(AE135,"before"))</f>
+        <f>IF(AE135="","",HYPERLINK(IFERROR(LEFT(AE135,FIND(";",AE135)-1),AE135),"before"))</f>
         <v/>
       </c>
       <c r="AM135">
-        <f>IF(AF135="","",HYPERLINK(AF135,"after"))</f>
+        <f>IF(AF135="","",HYPERLINK(IFERROR(LEFT(AF135,FIND(";",AF135)-1),AF135),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5605,11 +5605,11 @@
         <v/>
       </c>
       <c r="AL136">
-        <f>IF(AE136="","",HYPERLINK(AE136,"before"))</f>
+        <f>IF(AE136="","",HYPERLINK(IFERROR(LEFT(AE136,FIND(";",AE136)-1),AE136),"before"))</f>
         <v/>
       </c>
       <c r="AM136">
-        <f>IF(AF136="","",HYPERLINK(AF136,"after"))</f>
+        <f>IF(AF136="","",HYPERLINK(IFERROR(LEFT(AF136,FIND(";",AF136)-1),AF136),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5641,11 +5641,11 @@
         <v/>
       </c>
       <c r="AL137">
-        <f>IF(AE137="","",HYPERLINK(AE137,"before"))</f>
+        <f>IF(AE137="","",HYPERLINK(IFERROR(LEFT(AE137,FIND(";",AE137)-1),AE137),"before"))</f>
         <v/>
       </c>
       <c r="AM137">
-        <f>IF(AF137="","",HYPERLINK(AF137,"after"))</f>
+        <f>IF(AF137="","",HYPERLINK(IFERROR(LEFT(AF137,FIND(";",AF137)-1),AF137),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5677,11 +5677,11 @@
         <v/>
       </c>
       <c r="AL138">
-        <f>IF(AE138="","",HYPERLINK(AE138,"before"))</f>
+        <f>IF(AE138="","",HYPERLINK(IFERROR(LEFT(AE138,FIND(";",AE138)-1),AE138),"before"))</f>
         <v/>
       </c>
       <c r="AM138">
-        <f>IF(AF138="","",HYPERLINK(AF138,"after"))</f>
+        <f>IF(AF138="","",HYPERLINK(IFERROR(LEFT(AF138,FIND(";",AF138)-1),AF138),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5713,11 +5713,11 @@
         <v/>
       </c>
       <c r="AL139">
-        <f>IF(AE139="","",HYPERLINK(AE139,"before"))</f>
+        <f>IF(AE139="","",HYPERLINK(IFERROR(LEFT(AE139,FIND(";",AE139)-1),AE139),"before"))</f>
         <v/>
       </c>
       <c r="AM139">
-        <f>IF(AF139="","",HYPERLINK(AF139,"after"))</f>
+        <f>IF(AF139="","",HYPERLINK(IFERROR(LEFT(AF139,FIND(";",AF139)-1),AF139),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5749,11 +5749,11 @@
         <v/>
       </c>
       <c r="AL140">
-        <f>IF(AE140="","",HYPERLINK(AE140,"before"))</f>
+        <f>IF(AE140="","",HYPERLINK(IFERROR(LEFT(AE140,FIND(";",AE140)-1),AE140),"before"))</f>
         <v/>
       </c>
       <c r="AM140">
-        <f>IF(AF140="","",HYPERLINK(AF140,"after"))</f>
+        <f>IF(AF140="","",HYPERLINK(IFERROR(LEFT(AF140,FIND(";",AF140)-1),AF140),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5785,11 +5785,11 @@
         <v/>
       </c>
       <c r="AL141">
-        <f>IF(AE141="","",HYPERLINK(AE141,"before"))</f>
+        <f>IF(AE141="","",HYPERLINK(IFERROR(LEFT(AE141,FIND(";",AE141)-1),AE141),"before"))</f>
         <v/>
       </c>
       <c r="AM141">
-        <f>IF(AF141="","",HYPERLINK(AF141,"after"))</f>
+        <f>IF(AF141="","",HYPERLINK(IFERROR(LEFT(AF141,FIND(";",AF141)-1),AF141),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5821,11 +5821,11 @@
         <v/>
       </c>
       <c r="AL142">
-        <f>IF(AE142="","",HYPERLINK(AE142,"before"))</f>
+        <f>IF(AE142="","",HYPERLINK(IFERROR(LEFT(AE142,FIND(";",AE142)-1),AE142),"before"))</f>
         <v/>
       </c>
       <c r="AM142">
-        <f>IF(AF142="","",HYPERLINK(AF142,"after"))</f>
+        <f>IF(AF142="","",HYPERLINK(IFERROR(LEFT(AF142,FIND(";",AF142)-1),AF142),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5857,11 +5857,11 @@
         <v/>
       </c>
       <c r="AL143">
-        <f>IF(AE143="","",HYPERLINK(AE143,"before"))</f>
+        <f>IF(AE143="","",HYPERLINK(IFERROR(LEFT(AE143,FIND(";",AE143)-1),AE143),"before"))</f>
         <v/>
       </c>
       <c r="AM143">
-        <f>IF(AF143="","",HYPERLINK(AF143,"after"))</f>
+        <f>IF(AF143="","",HYPERLINK(IFERROR(LEFT(AF143,FIND(";",AF143)-1),AF143),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5893,11 +5893,11 @@
         <v/>
       </c>
       <c r="AL144">
-        <f>IF(AE144="","",HYPERLINK(AE144,"before"))</f>
+        <f>IF(AE144="","",HYPERLINK(IFERROR(LEFT(AE144,FIND(";",AE144)-1),AE144),"before"))</f>
         <v/>
       </c>
       <c r="AM144">
-        <f>IF(AF144="","",HYPERLINK(AF144,"after"))</f>
+        <f>IF(AF144="","",HYPERLINK(IFERROR(LEFT(AF144,FIND(";",AF144)-1),AF144),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5929,11 +5929,11 @@
         <v/>
       </c>
       <c r="AL145">
-        <f>IF(AE145="","",HYPERLINK(AE145,"before"))</f>
+        <f>IF(AE145="","",HYPERLINK(IFERROR(LEFT(AE145,FIND(";",AE145)-1),AE145),"before"))</f>
         <v/>
       </c>
       <c r="AM145">
-        <f>IF(AF145="","",HYPERLINK(AF145,"after"))</f>
+        <f>IF(AF145="","",HYPERLINK(IFERROR(LEFT(AF145,FIND(";",AF145)-1),AF145),"after"))</f>
         <v/>
       </c>
     </row>
@@ -5965,11 +5965,11 @@
         <v/>
       </c>
       <c r="AL146">
-        <f>IF(AE146="","",HYPERLINK(AE146,"before"))</f>
+        <f>IF(AE146="","",HYPERLINK(IFERROR(LEFT(AE146,FIND(";",AE146)-1),AE146),"before"))</f>
         <v/>
       </c>
       <c r="AM146">
-        <f>IF(AF146="","",HYPERLINK(AF146,"after"))</f>
+        <f>IF(AF146="","",HYPERLINK(IFERROR(LEFT(AF146,FIND(";",AF146)-1),AF146),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6001,11 +6001,11 @@
         <v/>
       </c>
       <c r="AL147">
-        <f>IF(AE147="","",HYPERLINK(AE147,"before"))</f>
+        <f>IF(AE147="","",HYPERLINK(IFERROR(LEFT(AE147,FIND(";",AE147)-1),AE147),"before"))</f>
         <v/>
       </c>
       <c r="AM147">
-        <f>IF(AF147="","",HYPERLINK(AF147,"after"))</f>
+        <f>IF(AF147="","",HYPERLINK(IFERROR(LEFT(AF147,FIND(";",AF147)-1),AF147),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6037,11 +6037,11 @@
         <v/>
       </c>
       <c r="AL148">
-        <f>IF(AE148="","",HYPERLINK(AE148,"before"))</f>
+        <f>IF(AE148="","",HYPERLINK(IFERROR(LEFT(AE148,FIND(";",AE148)-1),AE148),"before"))</f>
         <v/>
       </c>
       <c r="AM148">
-        <f>IF(AF148="","",HYPERLINK(AF148,"after"))</f>
+        <f>IF(AF148="","",HYPERLINK(IFERROR(LEFT(AF148,FIND(";",AF148)-1),AF148),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6073,11 +6073,11 @@
         <v/>
       </c>
       <c r="AL149">
-        <f>IF(AE149="","",HYPERLINK(AE149,"before"))</f>
+        <f>IF(AE149="","",HYPERLINK(IFERROR(LEFT(AE149,FIND(";",AE149)-1),AE149),"before"))</f>
         <v/>
       </c>
       <c r="AM149">
-        <f>IF(AF149="","",HYPERLINK(AF149,"after"))</f>
+        <f>IF(AF149="","",HYPERLINK(IFERROR(LEFT(AF149,FIND(";",AF149)-1),AF149),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6109,11 +6109,11 @@
         <v/>
       </c>
       <c r="AL150">
-        <f>IF(AE150="","",HYPERLINK(AE150,"before"))</f>
+        <f>IF(AE150="","",HYPERLINK(IFERROR(LEFT(AE150,FIND(";",AE150)-1),AE150),"before"))</f>
         <v/>
       </c>
       <c r="AM150">
-        <f>IF(AF150="","",HYPERLINK(AF150,"after"))</f>
+        <f>IF(AF150="","",HYPERLINK(IFERROR(LEFT(AF150,FIND(";",AF150)-1),AF150),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6145,11 +6145,11 @@
         <v/>
       </c>
       <c r="AL151">
-        <f>IF(AE151="","",HYPERLINK(AE151,"before"))</f>
+        <f>IF(AE151="","",HYPERLINK(IFERROR(LEFT(AE151,FIND(";",AE151)-1),AE151),"before"))</f>
         <v/>
       </c>
       <c r="AM151">
-        <f>IF(AF151="","",HYPERLINK(AF151,"after"))</f>
+        <f>IF(AF151="","",HYPERLINK(IFERROR(LEFT(AF151,FIND(";",AF151)-1),AF151),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6181,11 +6181,11 @@
         <v/>
       </c>
       <c r="AL152">
-        <f>IF(AE152="","",HYPERLINK(AE152,"before"))</f>
+        <f>IF(AE152="","",HYPERLINK(IFERROR(LEFT(AE152,FIND(";",AE152)-1),AE152),"before"))</f>
         <v/>
       </c>
       <c r="AM152">
-        <f>IF(AF152="","",HYPERLINK(AF152,"after"))</f>
+        <f>IF(AF152="","",HYPERLINK(IFERROR(LEFT(AF152,FIND(";",AF152)-1),AF152),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6217,11 +6217,11 @@
         <v/>
       </c>
       <c r="AL153">
-        <f>IF(AE153="","",HYPERLINK(AE153,"before"))</f>
+        <f>IF(AE153="","",HYPERLINK(IFERROR(LEFT(AE153,FIND(";",AE153)-1),AE153),"before"))</f>
         <v/>
       </c>
       <c r="AM153">
-        <f>IF(AF153="","",HYPERLINK(AF153,"after"))</f>
+        <f>IF(AF153="","",HYPERLINK(IFERROR(LEFT(AF153,FIND(";",AF153)-1),AF153),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6253,11 +6253,11 @@
         <v/>
       </c>
       <c r="AL154">
-        <f>IF(AE154="","",HYPERLINK(AE154,"before"))</f>
+        <f>IF(AE154="","",HYPERLINK(IFERROR(LEFT(AE154,FIND(";",AE154)-1),AE154),"before"))</f>
         <v/>
       </c>
       <c r="AM154">
-        <f>IF(AF154="","",HYPERLINK(AF154,"after"))</f>
+        <f>IF(AF154="","",HYPERLINK(IFERROR(LEFT(AF154,FIND(";",AF154)-1),AF154),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6289,11 +6289,11 @@
         <v/>
       </c>
       <c r="AL155">
-        <f>IF(AE155="","",HYPERLINK(AE155,"before"))</f>
+        <f>IF(AE155="","",HYPERLINK(IFERROR(LEFT(AE155,FIND(";",AE155)-1),AE155),"before"))</f>
         <v/>
       </c>
       <c r="AM155">
-        <f>IF(AF155="","",HYPERLINK(AF155,"after"))</f>
+        <f>IF(AF155="","",HYPERLINK(IFERROR(LEFT(AF155,FIND(";",AF155)-1),AF155),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6325,11 +6325,11 @@
         <v/>
       </c>
       <c r="AL156">
-        <f>IF(AE156="","",HYPERLINK(AE156,"before"))</f>
+        <f>IF(AE156="","",HYPERLINK(IFERROR(LEFT(AE156,FIND(";",AE156)-1),AE156),"before"))</f>
         <v/>
       </c>
       <c r="AM156">
-        <f>IF(AF156="","",HYPERLINK(AF156,"after"))</f>
+        <f>IF(AF156="","",HYPERLINK(IFERROR(LEFT(AF156,FIND(";",AF156)-1),AF156),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6361,11 +6361,11 @@
         <v/>
       </c>
       <c r="AL157">
-        <f>IF(AE157="","",HYPERLINK(AE157,"before"))</f>
+        <f>IF(AE157="","",HYPERLINK(IFERROR(LEFT(AE157,FIND(";",AE157)-1),AE157),"before"))</f>
         <v/>
       </c>
       <c r="AM157">
-        <f>IF(AF157="","",HYPERLINK(AF157,"after"))</f>
+        <f>IF(AF157="","",HYPERLINK(IFERROR(LEFT(AF157,FIND(";",AF157)-1),AF157),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6397,11 +6397,11 @@
         <v/>
       </c>
       <c r="AL158">
-        <f>IF(AE158="","",HYPERLINK(AE158,"before"))</f>
+        <f>IF(AE158="","",HYPERLINK(IFERROR(LEFT(AE158,FIND(";",AE158)-1),AE158),"before"))</f>
         <v/>
       </c>
       <c r="AM158">
-        <f>IF(AF158="","",HYPERLINK(AF158,"after"))</f>
+        <f>IF(AF158="","",HYPERLINK(IFERROR(LEFT(AF158,FIND(";",AF158)-1),AF158),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6433,11 +6433,11 @@
         <v/>
       </c>
       <c r="AL159">
-        <f>IF(AE159="","",HYPERLINK(AE159,"before"))</f>
+        <f>IF(AE159="","",HYPERLINK(IFERROR(LEFT(AE159,FIND(";",AE159)-1),AE159),"before"))</f>
         <v/>
       </c>
       <c r="AM159">
-        <f>IF(AF159="","",HYPERLINK(AF159,"after"))</f>
+        <f>IF(AF159="","",HYPERLINK(IFERROR(LEFT(AF159,FIND(";",AF159)-1),AF159),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6469,11 +6469,11 @@
         <v/>
       </c>
       <c r="AL160">
-        <f>IF(AE160="","",HYPERLINK(AE160,"before"))</f>
+        <f>IF(AE160="","",HYPERLINK(IFERROR(LEFT(AE160,FIND(";",AE160)-1),AE160),"before"))</f>
         <v/>
       </c>
       <c r="AM160">
-        <f>IF(AF160="","",HYPERLINK(AF160,"after"))</f>
+        <f>IF(AF160="","",HYPERLINK(IFERROR(LEFT(AF160,FIND(";",AF160)-1),AF160),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6505,11 +6505,11 @@
         <v/>
       </c>
       <c r="AL161">
-        <f>IF(AE161="","",HYPERLINK(AE161,"before"))</f>
+        <f>IF(AE161="","",HYPERLINK(IFERROR(LEFT(AE161,FIND(";",AE161)-1),AE161),"before"))</f>
         <v/>
       </c>
       <c r="AM161">
-        <f>IF(AF161="","",HYPERLINK(AF161,"after"))</f>
+        <f>IF(AF161="","",HYPERLINK(IFERROR(LEFT(AF161,FIND(";",AF161)-1),AF161),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6541,11 +6541,11 @@
         <v/>
       </c>
       <c r="AL162">
-        <f>IF(AE162="","",HYPERLINK(AE162,"before"))</f>
+        <f>IF(AE162="","",HYPERLINK(IFERROR(LEFT(AE162,FIND(";",AE162)-1),AE162),"before"))</f>
         <v/>
       </c>
       <c r="AM162">
-        <f>IF(AF162="","",HYPERLINK(AF162,"after"))</f>
+        <f>IF(AF162="","",HYPERLINK(IFERROR(LEFT(AF162,FIND(";",AF162)-1),AF162),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6577,11 +6577,11 @@
         <v/>
       </c>
       <c r="AL163">
-        <f>IF(AE163="","",HYPERLINK(AE163,"before"))</f>
+        <f>IF(AE163="","",HYPERLINK(IFERROR(LEFT(AE163,FIND(";",AE163)-1),AE163),"before"))</f>
         <v/>
       </c>
       <c r="AM163">
-        <f>IF(AF163="","",HYPERLINK(AF163,"after"))</f>
+        <f>IF(AF163="","",HYPERLINK(IFERROR(LEFT(AF163,FIND(";",AF163)-1),AF163),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6613,11 +6613,11 @@
         <v/>
       </c>
       <c r="AL164">
-        <f>IF(AE164="","",HYPERLINK(AE164,"before"))</f>
+        <f>IF(AE164="","",HYPERLINK(IFERROR(LEFT(AE164,FIND(";",AE164)-1),AE164),"before"))</f>
         <v/>
       </c>
       <c r="AM164">
-        <f>IF(AF164="","",HYPERLINK(AF164,"after"))</f>
+        <f>IF(AF164="","",HYPERLINK(IFERROR(LEFT(AF164,FIND(";",AF164)-1),AF164),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6649,11 +6649,11 @@
         <v/>
       </c>
       <c r="AL165">
-        <f>IF(AE165="","",HYPERLINK(AE165,"before"))</f>
+        <f>IF(AE165="","",HYPERLINK(IFERROR(LEFT(AE165,FIND(";",AE165)-1),AE165),"before"))</f>
         <v/>
       </c>
       <c r="AM165">
-        <f>IF(AF165="","",HYPERLINK(AF165,"after"))</f>
+        <f>IF(AF165="","",HYPERLINK(IFERROR(LEFT(AF165,FIND(";",AF165)-1),AF165),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6685,11 +6685,11 @@
         <v/>
       </c>
       <c r="AL166">
-        <f>IF(AE166="","",HYPERLINK(AE166,"before"))</f>
+        <f>IF(AE166="","",HYPERLINK(IFERROR(LEFT(AE166,FIND(";",AE166)-1),AE166),"before"))</f>
         <v/>
       </c>
       <c r="AM166">
-        <f>IF(AF166="","",HYPERLINK(AF166,"after"))</f>
+        <f>IF(AF166="","",HYPERLINK(IFERROR(LEFT(AF166,FIND(";",AF166)-1),AF166),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6721,11 +6721,11 @@
         <v/>
       </c>
       <c r="AL167">
-        <f>IF(AE167="","",HYPERLINK(AE167,"before"))</f>
+        <f>IF(AE167="","",HYPERLINK(IFERROR(LEFT(AE167,FIND(";",AE167)-1),AE167),"before"))</f>
         <v/>
       </c>
       <c r="AM167">
-        <f>IF(AF167="","",HYPERLINK(AF167,"after"))</f>
+        <f>IF(AF167="","",HYPERLINK(IFERROR(LEFT(AF167,FIND(";",AF167)-1),AF167),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6757,11 +6757,11 @@
         <v/>
       </c>
       <c r="AL168">
-        <f>IF(AE168="","",HYPERLINK(AE168,"before"))</f>
+        <f>IF(AE168="","",HYPERLINK(IFERROR(LEFT(AE168,FIND(";",AE168)-1),AE168),"before"))</f>
         <v/>
       </c>
       <c r="AM168">
-        <f>IF(AF168="","",HYPERLINK(AF168,"after"))</f>
+        <f>IF(AF168="","",HYPERLINK(IFERROR(LEFT(AF168,FIND(";",AF168)-1),AF168),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6793,11 +6793,11 @@
         <v/>
       </c>
       <c r="AL169">
-        <f>IF(AE169="","",HYPERLINK(AE169,"before"))</f>
+        <f>IF(AE169="","",HYPERLINK(IFERROR(LEFT(AE169,FIND(";",AE169)-1),AE169),"before"))</f>
         <v/>
       </c>
       <c r="AM169">
-        <f>IF(AF169="","",HYPERLINK(AF169,"after"))</f>
+        <f>IF(AF169="","",HYPERLINK(IFERROR(LEFT(AF169,FIND(";",AF169)-1),AF169),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6829,11 +6829,11 @@
         <v/>
       </c>
       <c r="AL170">
-        <f>IF(AE170="","",HYPERLINK(AE170,"before"))</f>
+        <f>IF(AE170="","",HYPERLINK(IFERROR(LEFT(AE170,FIND(";",AE170)-1),AE170),"before"))</f>
         <v/>
       </c>
       <c r="AM170">
-        <f>IF(AF170="","",HYPERLINK(AF170,"after"))</f>
+        <f>IF(AF170="","",HYPERLINK(IFERROR(LEFT(AF170,FIND(";",AF170)-1),AF170),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6865,11 +6865,11 @@
         <v/>
       </c>
       <c r="AL171">
-        <f>IF(AE171="","",HYPERLINK(AE171,"before"))</f>
+        <f>IF(AE171="","",HYPERLINK(IFERROR(LEFT(AE171,FIND(";",AE171)-1),AE171),"before"))</f>
         <v/>
       </c>
       <c r="AM171">
-        <f>IF(AF171="","",HYPERLINK(AF171,"after"))</f>
+        <f>IF(AF171="","",HYPERLINK(IFERROR(LEFT(AF171,FIND(";",AF171)-1),AF171),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6901,11 +6901,11 @@
         <v/>
       </c>
       <c r="AL172">
-        <f>IF(AE172="","",HYPERLINK(AE172,"before"))</f>
+        <f>IF(AE172="","",HYPERLINK(IFERROR(LEFT(AE172,FIND(";",AE172)-1),AE172),"before"))</f>
         <v/>
       </c>
       <c r="AM172">
-        <f>IF(AF172="","",HYPERLINK(AF172,"after"))</f>
+        <f>IF(AF172="","",HYPERLINK(IFERROR(LEFT(AF172,FIND(";",AF172)-1),AF172),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6937,11 +6937,11 @@
         <v/>
       </c>
       <c r="AL173">
-        <f>IF(AE173="","",HYPERLINK(AE173,"before"))</f>
+        <f>IF(AE173="","",HYPERLINK(IFERROR(LEFT(AE173,FIND(";",AE173)-1),AE173),"before"))</f>
         <v/>
       </c>
       <c r="AM173">
-        <f>IF(AF173="","",HYPERLINK(AF173,"after"))</f>
+        <f>IF(AF173="","",HYPERLINK(IFERROR(LEFT(AF173,FIND(";",AF173)-1),AF173),"after"))</f>
         <v/>
       </c>
     </row>
@@ -6973,11 +6973,11 @@
         <v/>
       </c>
       <c r="AL174">
-        <f>IF(AE174="","",HYPERLINK(AE174,"before"))</f>
+        <f>IF(AE174="","",HYPERLINK(IFERROR(LEFT(AE174,FIND(";",AE174)-1),AE174),"before"))</f>
         <v/>
       </c>
       <c r="AM174">
-        <f>IF(AF174="","",HYPERLINK(AF174,"after"))</f>
+        <f>IF(AF174="","",HYPERLINK(IFERROR(LEFT(AF174,FIND(";",AF174)-1),AF174),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7009,11 +7009,11 @@
         <v/>
       </c>
       <c r="AL175">
-        <f>IF(AE175="","",HYPERLINK(AE175,"before"))</f>
+        <f>IF(AE175="","",HYPERLINK(IFERROR(LEFT(AE175,FIND(";",AE175)-1),AE175),"before"))</f>
         <v/>
       </c>
       <c r="AM175">
-        <f>IF(AF175="","",HYPERLINK(AF175,"after"))</f>
+        <f>IF(AF175="","",HYPERLINK(IFERROR(LEFT(AF175,FIND(";",AF175)-1),AF175),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7045,11 +7045,11 @@
         <v/>
       </c>
       <c r="AL176">
-        <f>IF(AE176="","",HYPERLINK(AE176,"before"))</f>
+        <f>IF(AE176="","",HYPERLINK(IFERROR(LEFT(AE176,FIND(";",AE176)-1),AE176),"before"))</f>
         <v/>
       </c>
       <c r="AM176">
-        <f>IF(AF176="","",HYPERLINK(AF176,"after"))</f>
+        <f>IF(AF176="","",HYPERLINK(IFERROR(LEFT(AF176,FIND(";",AF176)-1),AF176),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7081,11 +7081,11 @@
         <v/>
       </c>
       <c r="AL177">
-        <f>IF(AE177="","",HYPERLINK(AE177,"before"))</f>
+        <f>IF(AE177="","",HYPERLINK(IFERROR(LEFT(AE177,FIND(";",AE177)-1),AE177),"before"))</f>
         <v/>
       </c>
       <c r="AM177">
-        <f>IF(AF177="","",HYPERLINK(AF177,"after"))</f>
+        <f>IF(AF177="","",HYPERLINK(IFERROR(LEFT(AF177,FIND(";",AF177)-1),AF177),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7117,11 +7117,11 @@
         <v/>
       </c>
       <c r="AL178">
-        <f>IF(AE178="","",HYPERLINK(AE178,"before"))</f>
+        <f>IF(AE178="","",HYPERLINK(IFERROR(LEFT(AE178,FIND(";",AE178)-1),AE178),"before"))</f>
         <v/>
       </c>
       <c r="AM178">
-        <f>IF(AF178="","",HYPERLINK(AF178,"after"))</f>
+        <f>IF(AF178="","",HYPERLINK(IFERROR(LEFT(AF178,FIND(";",AF178)-1),AF178),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7153,11 +7153,11 @@
         <v/>
       </c>
       <c r="AL179">
-        <f>IF(AE179="","",HYPERLINK(AE179,"before"))</f>
+        <f>IF(AE179="","",HYPERLINK(IFERROR(LEFT(AE179,FIND(";",AE179)-1),AE179),"before"))</f>
         <v/>
       </c>
       <c r="AM179">
-        <f>IF(AF179="","",HYPERLINK(AF179,"after"))</f>
+        <f>IF(AF179="","",HYPERLINK(IFERROR(LEFT(AF179,FIND(";",AF179)-1),AF179),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7189,11 +7189,11 @@
         <v/>
       </c>
       <c r="AL180">
-        <f>IF(AE180="","",HYPERLINK(AE180,"before"))</f>
+        <f>IF(AE180="","",HYPERLINK(IFERROR(LEFT(AE180,FIND(";",AE180)-1),AE180),"before"))</f>
         <v/>
       </c>
       <c r="AM180">
-        <f>IF(AF180="","",HYPERLINK(AF180,"after"))</f>
+        <f>IF(AF180="","",HYPERLINK(IFERROR(LEFT(AF180,FIND(";",AF180)-1),AF180),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7225,11 +7225,11 @@
         <v/>
       </c>
       <c r="AL181">
-        <f>IF(AE181="","",HYPERLINK(AE181,"before"))</f>
+        <f>IF(AE181="","",HYPERLINK(IFERROR(LEFT(AE181,FIND(";",AE181)-1),AE181),"before"))</f>
         <v/>
       </c>
       <c r="AM181">
-        <f>IF(AF181="","",HYPERLINK(AF181,"after"))</f>
+        <f>IF(AF181="","",HYPERLINK(IFERROR(LEFT(AF181,FIND(";",AF181)-1),AF181),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7261,11 +7261,11 @@
         <v/>
       </c>
       <c r="AL182">
-        <f>IF(AE182="","",HYPERLINK(AE182,"before"))</f>
+        <f>IF(AE182="","",HYPERLINK(IFERROR(LEFT(AE182,FIND(";",AE182)-1),AE182),"before"))</f>
         <v/>
       </c>
       <c r="AM182">
-        <f>IF(AF182="","",HYPERLINK(AF182,"after"))</f>
+        <f>IF(AF182="","",HYPERLINK(IFERROR(LEFT(AF182,FIND(";",AF182)-1),AF182),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7297,11 +7297,11 @@
         <v/>
       </c>
       <c r="AL183">
-        <f>IF(AE183="","",HYPERLINK(AE183,"before"))</f>
+        <f>IF(AE183="","",HYPERLINK(IFERROR(LEFT(AE183,FIND(";",AE183)-1),AE183),"before"))</f>
         <v/>
       </c>
       <c r="AM183">
-        <f>IF(AF183="","",HYPERLINK(AF183,"after"))</f>
+        <f>IF(AF183="","",HYPERLINK(IFERROR(LEFT(AF183,FIND(";",AF183)-1),AF183),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7333,11 +7333,11 @@
         <v/>
       </c>
       <c r="AL184">
-        <f>IF(AE184="","",HYPERLINK(AE184,"before"))</f>
+        <f>IF(AE184="","",HYPERLINK(IFERROR(LEFT(AE184,FIND(";",AE184)-1),AE184),"before"))</f>
         <v/>
       </c>
       <c r="AM184">
-        <f>IF(AF184="","",HYPERLINK(AF184,"after"))</f>
+        <f>IF(AF184="","",HYPERLINK(IFERROR(LEFT(AF184,FIND(";",AF184)-1),AF184),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7369,11 +7369,11 @@
         <v/>
       </c>
       <c r="AL185">
-        <f>IF(AE185="","",HYPERLINK(AE185,"before"))</f>
+        <f>IF(AE185="","",HYPERLINK(IFERROR(LEFT(AE185,FIND(";",AE185)-1),AE185),"before"))</f>
         <v/>
       </c>
       <c r="AM185">
-        <f>IF(AF185="","",HYPERLINK(AF185,"after"))</f>
+        <f>IF(AF185="","",HYPERLINK(IFERROR(LEFT(AF185,FIND(";",AF185)-1),AF185),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7405,11 +7405,11 @@
         <v/>
       </c>
       <c r="AL186">
-        <f>IF(AE186="","",HYPERLINK(AE186,"before"))</f>
+        <f>IF(AE186="","",HYPERLINK(IFERROR(LEFT(AE186,FIND(";",AE186)-1),AE186),"before"))</f>
         <v/>
       </c>
       <c r="AM186">
-        <f>IF(AF186="","",HYPERLINK(AF186,"after"))</f>
+        <f>IF(AF186="","",HYPERLINK(IFERROR(LEFT(AF186,FIND(";",AF186)-1),AF186),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7441,11 +7441,11 @@
         <v/>
       </c>
       <c r="AL187">
-        <f>IF(AE187="","",HYPERLINK(AE187,"before"))</f>
+        <f>IF(AE187="","",HYPERLINK(IFERROR(LEFT(AE187,FIND(";",AE187)-1),AE187),"before"))</f>
         <v/>
       </c>
       <c r="AM187">
-        <f>IF(AF187="","",HYPERLINK(AF187,"after"))</f>
+        <f>IF(AF187="","",HYPERLINK(IFERROR(LEFT(AF187,FIND(";",AF187)-1),AF187),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7477,11 +7477,11 @@
         <v/>
       </c>
       <c r="AL188">
-        <f>IF(AE188="","",HYPERLINK(AE188,"before"))</f>
+        <f>IF(AE188="","",HYPERLINK(IFERROR(LEFT(AE188,FIND(";",AE188)-1),AE188),"before"))</f>
         <v/>
       </c>
       <c r="AM188">
-        <f>IF(AF188="","",HYPERLINK(AF188,"after"))</f>
+        <f>IF(AF188="","",HYPERLINK(IFERROR(LEFT(AF188,FIND(";",AF188)-1),AF188),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7513,11 +7513,11 @@
         <v/>
       </c>
       <c r="AL189">
-        <f>IF(AE189="","",HYPERLINK(AE189,"before"))</f>
+        <f>IF(AE189="","",HYPERLINK(IFERROR(LEFT(AE189,FIND(";",AE189)-1),AE189),"before"))</f>
         <v/>
       </c>
       <c r="AM189">
-        <f>IF(AF189="","",HYPERLINK(AF189,"after"))</f>
+        <f>IF(AF189="","",HYPERLINK(IFERROR(LEFT(AF189,FIND(";",AF189)-1),AF189),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7549,11 +7549,11 @@
         <v/>
       </c>
       <c r="AL190">
-        <f>IF(AE190="","",HYPERLINK(AE190,"before"))</f>
+        <f>IF(AE190="","",HYPERLINK(IFERROR(LEFT(AE190,FIND(";",AE190)-1),AE190),"before"))</f>
         <v/>
       </c>
       <c r="AM190">
-        <f>IF(AF190="","",HYPERLINK(AF190,"after"))</f>
+        <f>IF(AF190="","",HYPERLINK(IFERROR(LEFT(AF190,FIND(";",AF190)-1),AF190),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7585,11 +7585,11 @@
         <v/>
       </c>
       <c r="AL191">
-        <f>IF(AE191="","",HYPERLINK(AE191,"before"))</f>
+        <f>IF(AE191="","",HYPERLINK(IFERROR(LEFT(AE191,FIND(";",AE191)-1),AE191),"before"))</f>
         <v/>
       </c>
       <c r="AM191">
-        <f>IF(AF191="","",HYPERLINK(AF191,"after"))</f>
+        <f>IF(AF191="","",HYPERLINK(IFERROR(LEFT(AF191,FIND(";",AF191)-1),AF191),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7621,11 +7621,11 @@
         <v/>
       </c>
       <c r="AL192">
-        <f>IF(AE192="","",HYPERLINK(AE192,"before"))</f>
+        <f>IF(AE192="","",HYPERLINK(IFERROR(LEFT(AE192,FIND(";",AE192)-1),AE192),"before"))</f>
         <v/>
       </c>
       <c r="AM192">
-        <f>IF(AF192="","",HYPERLINK(AF192,"after"))</f>
+        <f>IF(AF192="","",HYPERLINK(IFERROR(LEFT(AF192,FIND(";",AF192)-1),AF192),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7657,11 +7657,11 @@
         <v/>
       </c>
       <c r="AL193">
-        <f>IF(AE193="","",HYPERLINK(AE193,"before"))</f>
+        <f>IF(AE193="","",HYPERLINK(IFERROR(LEFT(AE193,FIND(";",AE193)-1),AE193),"before"))</f>
         <v/>
       </c>
       <c r="AM193">
-        <f>IF(AF193="","",HYPERLINK(AF193,"after"))</f>
+        <f>IF(AF193="","",HYPERLINK(IFERROR(LEFT(AF193,FIND(";",AF193)-1),AF193),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7693,11 +7693,11 @@
         <v/>
       </c>
       <c r="AL194">
-        <f>IF(AE194="","",HYPERLINK(AE194,"before"))</f>
+        <f>IF(AE194="","",HYPERLINK(IFERROR(LEFT(AE194,FIND(";",AE194)-1),AE194),"before"))</f>
         <v/>
       </c>
       <c r="AM194">
-        <f>IF(AF194="","",HYPERLINK(AF194,"after"))</f>
+        <f>IF(AF194="","",HYPERLINK(IFERROR(LEFT(AF194,FIND(";",AF194)-1),AF194),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7729,11 +7729,11 @@
         <v/>
       </c>
       <c r="AL195">
-        <f>IF(AE195="","",HYPERLINK(AE195,"before"))</f>
+        <f>IF(AE195="","",HYPERLINK(IFERROR(LEFT(AE195,FIND(";",AE195)-1),AE195),"before"))</f>
         <v/>
       </c>
       <c r="AM195">
-        <f>IF(AF195="","",HYPERLINK(AF195,"after"))</f>
+        <f>IF(AF195="","",HYPERLINK(IFERROR(LEFT(AF195,FIND(";",AF195)-1),AF195),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7765,11 +7765,11 @@
         <v/>
       </c>
       <c r="AL196">
-        <f>IF(AE196="","",HYPERLINK(AE196,"before"))</f>
+        <f>IF(AE196="","",HYPERLINK(IFERROR(LEFT(AE196,FIND(";",AE196)-1),AE196),"before"))</f>
         <v/>
       </c>
       <c r="AM196">
-        <f>IF(AF196="","",HYPERLINK(AF196,"after"))</f>
+        <f>IF(AF196="","",HYPERLINK(IFERROR(LEFT(AF196,FIND(";",AF196)-1),AF196),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7801,11 +7801,11 @@
         <v/>
       </c>
       <c r="AL197">
-        <f>IF(AE197="","",HYPERLINK(AE197,"before"))</f>
+        <f>IF(AE197="","",HYPERLINK(IFERROR(LEFT(AE197,FIND(";",AE197)-1),AE197),"before"))</f>
         <v/>
       </c>
       <c r="AM197">
-        <f>IF(AF197="","",HYPERLINK(AF197,"after"))</f>
+        <f>IF(AF197="","",HYPERLINK(IFERROR(LEFT(AF197,FIND(";",AF197)-1),AF197),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7837,11 +7837,11 @@
         <v/>
       </c>
       <c r="AL198">
-        <f>IF(AE198="","",HYPERLINK(AE198,"before"))</f>
+        <f>IF(AE198="","",HYPERLINK(IFERROR(LEFT(AE198,FIND(";",AE198)-1),AE198),"before"))</f>
         <v/>
       </c>
       <c r="AM198">
-        <f>IF(AF198="","",HYPERLINK(AF198,"after"))</f>
+        <f>IF(AF198="","",HYPERLINK(IFERROR(LEFT(AF198,FIND(";",AF198)-1),AF198),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7873,11 +7873,11 @@
         <v/>
       </c>
       <c r="AL199">
-        <f>IF(AE199="","",HYPERLINK(AE199,"before"))</f>
+        <f>IF(AE199="","",HYPERLINK(IFERROR(LEFT(AE199,FIND(";",AE199)-1),AE199),"before"))</f>
         <v/>
       </c>
       <c r="AM199">
-        <f>IF(AF199="","",HYPERLINK(AF199,"after"))</f>
+        <f>IF(AF199="","",HYPERLINK(IFERROR(LEFT(AF199,FIND(";",AF199)-1),AF199),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7909,11 +7909,11 @@
         <v/>
       </c>
       <c r="AL200">
-        <f>IF(AE200="","",HYPERLINK(AE200,"before"))</f>
+        <f>IF(AE200="","",HYPERLINK(IFERROR(LEFT(AE200,FIND(";",AE200)-1),AE200),"before"))</f>
         <v/>
       </c>
       <c r="AM200">
-        <f>IF(AF200="","",HYPERLINK(AF200,"after"))</f>
+        <f>IF(AF200="","",HYPERLINK(IFERROR(LEFT(AF200,FIND(";",AF200)-1),AF200),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7945,11 +7945,11 @@
         <v/>
       </c>
       <c r="AL201">
-        <f>IF(AE201="","",HYPERLINK(AE201,"before"))</f>
+        <f>IF(AE201="","",HYPERLINK(IFERROR(LEFT(AE201,FIND(";",AE201)-1),AE201),"before"))</f>
         <v/>
       </c>
       <c r="AM201">
-        <f>IF(AF201="","",HYPERLINK(AF201,"after"))</f>
+        <f>IF(AF201="","",HYPERLINK(IFERROR(LEFT(AF201,FIND(";",AF201)-1),AF201),"after"))</f>
         <v/>
       </c>
     </row>
@@ -7981,11 +7981,11 @@
         <v/>
       </c>
       <c r="AL202">
-        <f>IF(AE202="","",HYPERLINK(AE202,"before"))</f>
+        <f>IF(AE202="","",HYPERLINK(IFERROR(LEFT(AE202,FIND(";",AE202)-1),AE202),"before"))</f>
         <v/>
       </c>
       <c r="AM202">
-        <f>IF(AF202="","",HYPERLINK(AF202,"after"))</f>
+        <f>IF(AF202="","",HYPERLINK(IFERROR(LEFT(AF202,FIND(";",AF202)-1),AF202),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8017,11 +8017,11 @@
         <v/>
       </c>
       <c r="AL203">
-        <f>IF(AE203="","",HYPERLINK(AE203,"before"))</f>
+        <f>IF(AE203="","",HYPERLINK(IFERROR(LEFT(AE203,FIND(";",AE203)-1),AE203),"before"))</f>
         <v/>
       </c>
       <c r="AM203">
-        <f>IF(AF203="","",HYPERLINK(AF203,"after"))</f>
+        <f>IF(AF203="","",HYPERLINK(IFERROR(LEFT(AF203,FIND(";",AF203)-1),AF203),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8053,11 +8053,11 @@
         <v/>
       </c>
       <c r="AL204">
-        <f>IF(AE204="","",HYPERLINK(AE204,"before"))</f>
+        <f>IF(AE204="","",HYPERLINK(IFERROR(LEFT(AE204,FIND(";",AE204)-1),AE204),"before"))</f>
         <v/>
       </c>
       <c r="AM204">
-        <f>IF(AF204="","",HYPERLINK(AF204,"after"))</f>
+        <f>IF(AF204="","",HYPERLINK(IFERROR(LEFT(AF204,FIND(";",AF204)-1),AF204),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8089,11 +8089,11 @@
         <v/>
       </c>
       <c r="AL205">
-        <f>IF(AE205="","",HYPERLINK(AE205,"before"))</f>
+        <f>IF(AE205="","",HYPERLINK(IFERROR(LEFT(AE205,FIND(";",AE205)-1),AE205),"before"))</f>
         <v/>
       </c>
       <c r="AM205">
-        <f>IF(AF205="","",HYPERLINK(AF205,"after"))</f>
+        <f>IF(AF205="","",HYPERLINK(IFERROR(LEFT(AF205,FIND(";",AF205)-1),AF205),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8125,11 +8125,11 @@
         <v/>
       </c>
       <c r="AL206">
-        <f>IF(AE206="","",HYPERLINK(AE206,"before"))</f>
+        <f>IF(AE206="","",HYPERLINK(IFERROR(LEFT(AE206,FIND(";",AE206)-1),AE206),"before"))</f>
         <v/>
       </c>
       <c r="AM206">
-        <f>IF(AF206="","",HYPERLINK(AF206,"after"))</f>
+        <f>IF(AF206="","",HYPERLINK(IFERROR(LEFT(AF206,FIND(";",AF206)-1),AF206),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8161,11 +8161,11 @@
         <v/>
       </c>
       <c r="AL207">
-        <f>IF(AE207="","",HYPERLINK(AE207,"before"))</f>
+        <f>IF(AE207="","",HYPERLINK(IFERROR(LEFT(AE207,FIND(";",AE207)-1),AE207),"before"))</f>
         <v/>
       </c>
       <c r="AM207">
-        <f>IF(AF207="","",HYPERLINK(AF207,"after"))</f>
+        <f>IF(AF207="","",HYPERLINK(IFERROR(LEFT(AF207,FIND(";",AF207)-1),AF207),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8197,11 +8197,11 @@
         <v/>
       </c>
       <c r="AL208">
-        <f>IF(AE208="","",HYPERLINK(AE208,"before"))</f>
+        <f>IF(AE208="","",HYPERLINK(IFERROR(LEFT(AE208,FIND(";",AE208)-1),AE208),"before"))</f>
         <v/>
       </c>
       <c r="AM208">
-        <f>IF(AF208="","",HYPERLINK(AF208,"after"))</f>
+        <f>IF(AF208="","",HYPERLINK(IFERROR(LEFT(AF208,FIND(";",AF208)-1),AF208),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8233,11 +8233,11 @@
         <v/>
       </c>
       <c r="AL209">
-        <f>IF(AE209="","",HYPERLINK(AE209,"before"))</f>
+        <f>IF(AE209="","",HYPERLINK(IFERROR(LEFT(AE209,FIND(";",AE209)-1),AE209),"before"))</f>
         <v/>
       </c>
       <c r="AM209">
-        <f>IF(AF209="","",HYPERLINK(AF209,"after"))</f>
+        <f>IF(AF209="","",HYPERLINK(IFERROR(LEFT(AF209,FIND(";",AF209)-1),AF209),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8269,11 +8269,11 @@
         <v/>
       </c>
       <c r="AL210">
-        <f>IF(AE210="","",HYPERLINK(AE210,"before"))</f>
+        <f>IF(AE210="","",HYPERLINK(IFERROR(LEFT(AE210,FIND(";",AE210)-1),AE210),"before"))</f>
         <v/>
       </c>
       <c r="AM210">
-        <f>IF(AF210="","",HYPERLINK(AF210,"after"))</f>
+        <f>IF(AF210="","",HYPERLINK(IFERROR(LEFT(AF210,FIND(";",AF210)-1),AF210),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8305,11 +8305,11 @@
         <v/>
       </c>
       <c r="AL211">
-        <f>IF(AE211="","",HYPERLINK(AE211,"before"))</f>
+        <f>IF(AE211="","",HYPERLINK(IFERROR(LEFT(AE211,FIND(";",AE211)-1),AE211),"before"))</f>
         <v/>
       </c>
       <c r="AM211">
-        <f>IF(AF211="","",HYPERLINK(AF211,"after"))</f>
+        <f>IF(AF211="","",HYPERLINK(IFERROR(LEFT(AF211,FIND(";",AF211)-1),AF211),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8341,11 +8341,11 @@
         <v/>
       </c>
       <c r="AL212">
-        <f>IF(AE212="","",HYPERLINK(AE212,"before"))</f>
+        <f>IF(AE212="","",HYPERLINK(IFERROR(LEFT(AE212,FIND(";",AE212)-1),AE212),"before"))</f>
         <v/>
       </c>
       <c r="AM212">
-        <f>IF(AF212="","",HYPERLINK(AF212,"after"))</f>
+        <f>IF(AF212="","",HYPERLINK(IFERROR(LEFT(AF212,FIND(";",AF212)-1),AF212),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8377,11 +8377,11 @@
         <v/>
       </c>
       <c r="AL213">
-        <f>IF(AE213="","",HYPERLINK(AE213,"before"))</f>
+        <f>IF(AE213="","",HYPERLINK(IFERROR(LEFT(AE213,FIND(";",AE213)-1),AE213),"before"))</f>
         <v/>
       </c>
       <c r="AM213">
-        <f>IF(AF213="","",HYPERLINK(AF213,"after"))</f>
+        <f>IF(AF213="","",HYPERLINK(IFERROR(LEFT(AF213,FIND(";",AF213)-1),AF213),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8413,11 +8413,11 @@
         <v/>
       </c>
       <c r="AL214">
-        <f>IF(AE214="","",HYPERLINK(AE214,"before"))</f>
+        <f>IF(AE214="","",HYPERLINK(IFERROR(LEFT(AE214,FIND(";",AE214)-1),AE214),"before"))</f>
         <v/>
       </c>
       <c r="AM214">
-        <f>IF(AF214="","",HYPERLINK(AF214,"after"))</f>
+        <f>IF(AF214="","",HYPERLINK(IFERROR(LEFT(AF214,FIND(";",AF214)-1),AF214),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8449,11 +8449,11 @@
         <v/>
       </c>
       <c r="AL215">
-        <f>IF(AE215="","",HYPERLINK(AE215,"before"))</f>
+        <f>IF(AE215="","",HYPERLINK(IFERROR(LEFT(AE215,FIND(";",AE215)-1),AE215),"before"))</f>
         <v/>
       </c>
       <c r="AM215">
-        <f>IF(AF215="","",HYPERLINK(AF215,"after"))</f>
+        <f>IF(AF215="","",HYPERLINK(IFERROR(LEFT(AF215,FIND(";",AF215)-1),AF215),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8485,11 +8485,11 @@
         <v/>
       </c>
       <c r="AL216">
-        <f>IF(AE216="","",HYPERLINK(AE216,"before"))</f>
+        <f>IF(AE216="","",HYPERLINK(IFERROR(LEFT(AE216,FIND(";",AE216)-1),AE216),"before"))</f>
         <v/>
       </c>
       <c r="AM216">
-        <f>IF(AF216="","",HYPERLINK(AF216,"after"))</f>
+        <f>IF(AF216="","",HYPERLINK(IFERROR(LEFT(AF216,FIND(";",AF216)-1),AF216),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8521,11 +8521,11 @@
         <v/>
       </c>
       <c r="AL217">
-        <f>IF(AE217="","",HYPERLINK(AE217,"before"))</f>
+        <f>IF(AE217="","",HYPERLINK(IFERROR(LEFT(AE217,FIND(";",AE217)-1),AE217),"before"))</f>
         <v/>
       </c>
       <c r="AM217">
-        <f>IF(AF217="","",HYPERLINK(AF217,"after"))</f>
+        <f>IF(AF217="","",HYPERLINK(IFERROR(LEFT(AF217,FIND(";",AF217)-1),AF217),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8557,11 +8557,11 @@
         <v/>
       </c>
       <c r="AL218">
-        <f>IF(AE218="","",HYPERLINK(AE218,"before"))</f>
+        <f>IF(AE218="","",HYPERLINK(IFERROR(LEFT(AE218,FIND(";",AE218)-1),AE218),"before"))</f>
         <v/>
       </c>
       <c r="AM218">
-        <f>IF(AF218="","",HYPERLINK(AF218,"after"))</f>
+        <f>IF(AF218="","",HYPERLINK(IFERROR(LEFT(AF218,FIND(";",AF218)-1),AF218),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8593,11 +8593,11 @@
         <v/>
       </c>
       <c r="AL219">
-        <f>IF(AE219="","",HYPERLINK(AE219,"before"))</f>
+        <f>IF(AE219="","",HYPERLINK(IFERROR(LEFT(AE219,FIND(";",AE219)-1),AE219),"before"))</f>
         <v/>
       </c>
       <c r="AM219">
-        <f>IF(AF219="","",HYPERLINK(AF219,"after"))</f>
+        <f>IF(AF219="","",HYPERLINK(IFERROR(LEFT(AF219,FIND(";",AF219)-1),AF219),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8629,11 +8629,11 @@
         <v/>
       </c>
       <c r="AL220">
-        <f>IF(AE220="","",HYPERLINK(AE220,"before"))</f>
+        <f>IF(AE220="","",HYPERLINK(IFERROR(LEFT(AE220,FIND(";",AE220)-1),AE220),"before"))</f>
         <v/>
       </c>
       <c r="AM220">
-        <f>IF(AF220="","",HYPERLINK(AF220,"after"))</f>
+        <f>IF(AF220="","",HYPERLINK(IFERROR(LEFT(AF220,FIND(";",AF220)-1),AF220),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8665,11 +8665,11 @@
         <v/>
       </c>
       <c r="AL221">
-        <f>IF(AE221="","",HYPERLINK(AE221,"before"))</f>
+        <f>IF(AE221="","",HYPERLINK(IFERROR(LEFT(AE221,FIND(";",AE221)-1),AE221),"before"))</f>
         <v/>
       </c>
       <c r="AM221">
-        <f>IF(AF221="","",HYPERLINK(AF221,"after"))</f>
+        <f>IF(AF221="","",HYPERLINK(IFERROR(LEFT(AF221,FIND(";",AF221)-1),AF221),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8701,11 +8701,11 @@
         <v/>
       </c>
       <c r="AL222">
-        <f>IF(AE222="","",HYPERLINK(AE222,"before"))</f>
+        <f>IF(AE222="","",HYPERLINK(IFERROR(LEFT(AE222,FIND(";",AE222)-1),AE222),"before"))</f>
         <v/>
       </c>
       <c r="AM222">
-        <f>IF(AF222="","",HYPERLINK(AF222,"after"))</f>
+        <f>IF(AF222="","",HYPERLINK(IFERROR(LEFT(AF222,FIND(";",AF222)-1),AF222),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8737,11 +8737,11 @@
         <v/>
       </c>
       <c r="AL223">
-        <f>IF(AE223="","",HYPERLINK(AE223,"before"))</f>
+        <f>IF(AE223="","",HYPERLINK(IFERROR(LEFT(AE223,FIND(";",AE223)-1),AE223),"before"))</f>
         <v/>
       </c>
       <c r="AM223">
-        <f>IF(AF223="","",HYPERLINK(AF223,"after"))</f>
+        <f>IF(AF223="","",HYPERLINK(IFERROR(LEFT(AF223,FIND(";",AF223)-1),AF223),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8773,11 +8773,11 @@
         <v/>
       </c>
       <c r="AL224">
-        <f>IF(AE224="","",HYPERLINK(AE224,"before"))</f>
+        <f>IF(AE224="","",HYPERLINK(IFERROR(LEFT(AE224,FIND(";",AE224)-1),AE224),"before"))</f>
         <v/>
       </c>
       <c r="AM224">
-        <f>IF(AF224="","",HYPERLINK(AF224,"after"))</f>
+        <f>IF(AF224="","",HYPERLINK(IFERROR(LEFT(AF224,FIND(";",AF224)-1),AF224),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8809,11 +8809,11 @@
         <v/>
       </c>
       <c r="AL225">
-        <f>IF(AE225="","",HYPERLINK(AE225,"before"))</f>
+        <f>IF(AE225="","",HYPERLINK(IFERROR(LEFT(AE225,FIND(";",AE225)-1),AE225),"before"))</f>
         <v/>
       </c>
       <c r="AM225">
-        <f>IF(AF225="","",HYPERLINK(AF225,"after"))</f>
+        <f>IF(AF225="","",HYPERLINK(IFERROR(LEFT(AF225,FIND(";",AF225)-1),AF225),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8845,11 +8845,11 @@
         <v/>
       </c>
       <c r="AL226">
-        <f>IF(AE226="","",HYPERLINK(AE226,"before"))</f>
+        <f>IF(AE226="","",HYPERLINK(IFERROR(LEFT(AE226,FIND(";",AE226)-1),AE226),"before"))</f>
         <v/>
       </c>
       <c r="AM226">
-        <f>IF(AF226="","",HYPERLINK(AF226,"after"))</f>
+        <f>IF(AF226="","",HYPERLINK(IFERROR(LEFT(AF226,FIND(";",AF226)-1),AF226),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8881,11 +8881,11 @@
         <v/>
       </c>
       <c r="AL227">
-        <f>IF(AE227="","",HYPERLINK(AE227,"before"))</f>
+        <f>IF(AE227="","",HYPERLINK(IFERROR(LEFT(AE227,FIND(";",AE227)-1),AE227),"before"))</f>
         <v/>
       </c>
       <c r="AM227">
-        <f>IF(AF227="","",HYPERLINK(AF227,"after"))</f>
+        <f>IF(AF227="","",HYPERLINK(IFERROR(LEFT(AF227,FIND(";",AF227)-1),AF227),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8917,11 +8917,11 @@
         <v/>
       </c>
       <c r="AL228">
-        <f>IF(AE228="","",HYPERLINK(AE228,"before"))</f>
+        <f>IF(AE228="","",HYPERLINK(IFERROR(LEFT(AE228,FIND(";",AE228)-1),AE228),"before"))</f>
         <v/>
       </c>
       <c r="AM228">
-        <f>IF(AF228="","",HYPERLINK(AF228,"after"))</f>
+        <f>IF(AF228="","",HYPERLINK(IFERROR(LEFT(AF228,FIND(";",AF228)-1),AF228),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8953,11 +8953,11 @@
         <v/>
       </c>
       <c r="AL229">
-        <f>IF(AE229="","",HYPERLINK(AE229,"before"))</f>
+        <f>IF(AE229="","",HYPERLINK(IFERROR(LEFT(AE229,FIND(";",AE229)-1),AE229),"before"))</f>
         <v/>
       </c>
       <c r="AM229">
-        <f>IF(AF229="","",HYPERLINK(AF229,"after"))</f>
+        <f>IF(AF229="","",HYPERLINK(IFERROR(LEFT(AF229,FIND(";",AF229)-1),AF229),"after"))</f>
         <v/>
       </c>
     </row>
@@ -8989,11 +8989,11 @@
         <v/>
       </c>
       <c r="AL230">
-        <f>IF(AE230="","",HYPERLINK(AE230,"before"))</f>
+        <f>IF(AE230="","",HYPERLINK(IFERROR(LEFT(AE230,FIND(";",AE230)-1),AE230),"before"))</f>
         <v/>
       </c>
       <c r="AM230">
-        <f>IF(AF230="","",HYPERLINK(AF230,"after"))</f>
+        <f>IF(AF230="","",HYPERLINK(IFERROR(LEFT(AF230,FIND(";",AF230)-1),AF230),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9025,11 +9025,11 @@
         <v/>
       </c>
       <c r="AL231">
-        <f>IF(AE231="","",HYPERLINK(AE231,"before"))</f>
+        <f>IF(AE231="","",HYPERLINK(IFERROR(LEFT(AE231,FIND(";",AE231)-1),AE231),"before"))</f>
         <v/>
       </c>
       <c r="AM231">
-        <f>IF(AF231="","",HYPERLINK(AF231,"after"))</f>
+        <f>IF(AF231="","",HYPERLINK(IFERROR(LEFT(AF231,FIND(";",AF231)-1),AF231),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9061,11 +9061,11 @@
         <v/>
       </c>
       <c r="AL232">
-        <f>IF(AE232="","",HYPERLINK(AE232,"before"))</f>
+        <f>IF(AE232="","",HYPERLINK(IFERROR(LEFT(AE232,FIND(";",AE232)-1),AE232),"before"))</f>
         <v/>
       </c>
       <c r="AM232">
-        <f>IF(AF232="","",HYPERLINK(AF232,"after"))</f>
+        <f>IF(AF232="","",HYPERLINK(IFERROR(LEFT(AF232,FIND(";",AF232)-1),AF232),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9097,11 +9097,11 @@
         <v/>
       </c>
       <c r="AL233">
-        <f>IF(AE233="","",HYPERLINK(AE233,"before"))</f>
+        <f>IF(AE233="","",HYPERLINK(IFERROR(LEFT(AE233,FIND(";",AE233)-1),AE233),"before"))</f>
         <v/>
       </c>
       <c r="AM233">
-        <f>IF(AF233="","",HYPERLINK(AF233,"after"))</f>
+        <f>IF(AF233="","",HYPERLINK(IFERROR(LEFT(AF233,FIND(";",AF233)-1),AF233),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9133,11 +9133,11 @@
         <v/>
       </c>
       <c r="AL234">
-        <f>IF(AE234="","",HYPERLINK(AE234,"before"))</f>
+        <f>IF(AE234="","",HYPERLINK(IFERROR(LEFT(AE234,FIND(";",AE234)-1),AE234),"before"))</f>
         <v/>
       </c>
       <c r="AM234">
-        <f>IF(AF234="","",HYPERLINK(AF234,"after"))</f>
+        <f>IF(AF234="","",HYPERLINK(IFERROR(LEFT(AF234,FIND(";",AF234)-1),AF234),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9169,11 +9169,11 @@
         <v/>
       </c>
       <c r="AL235">
-        <f>IF(AE235="","",HYPERLINK(AE235,"before"))</f>
+        <f>IF(AE235="","",HYPERLINK(IFERROR(LEFT(AE235,FIND(";",AE235)-1),AE235),"before"))</f>
         <v/>
       </c>
       <c r="AM235">
-        <f>IF(AF235="","",HYPERLINK(AF235,"after"))</f>
+        <f>IF(AF235="","",HYPERLINK(IFERROR(LEFT(AF235,FIND(";",AF235)-1),AF235),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9205,11 +9205,11 @@
         <v/>
       </c>
       <c r="AL236">
-        <f>IF(AE236="","",HYPERLINK(AE236,"before"))</f>
+        <f>IF(AE236="","",HYPERLINK(IFERROR(LEFT(AE236,FIND(";",AE236)-1),AE236),"before"))</f>
         <v/>
       </c>
       <c r="AM236">
-        <f>IF(AF236="","",HYPERLINK(AF236,"after"))</f>
+        <f>IF(AF236="","",HYPERLINK(IFERROR(LEFT(AF236,FIND(";",AF236)-1),AF236),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9241,11 +9241,11 @@
         <v/>
       </c>
       <c r="AL237">
-        <f>IF(AE237="","",HYPERLINK(AE237,"before"))</f>
+        <f>IF(AE237="","",HYPERLINK(IFERROR(LEFT(AE237,FIND(";",AE237)-1),AE237),"before"))</f>
         <v/>
       </c>
       <c r="AM237">
-        <f>IF(AF237="","",HYPERLINK(AF237,"after"))</f>
+        <f>IF(AF237="","",HYPERLINK(IFERROR(LEFT(AF237,FIND(";",AF237)-1),AF237),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9277,11 +9277,11 @@
         <v/>
       </c>
       <c r="AL238">
-        <f>IF(AE238="","",HYPERLINK(AE238,"before"))</f>
+        <f>IF(AE238="","",HYPERLINK(IFERROR(LEFT(AE238,FIND(";",AE238)-1),AE238),"before"))</f>
         <v/>
       </c>
       <c r="AM238">
-        <f>IF(AF238="","",HYPERLINK(AF238,"after"))</f>
+        <f>IF(AF238="","",HYPERLINK(IFERROR(LEFT(AF238,FIND(";",AF238)-1),AF238),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9313,11 +9313,11 @@
         <v/>
       </c>
       <c r="AL239">
-        <f>IF(AE239="","",HYPERLINK(AE239,"before"))</f>
+        <f>IF(AE239="","",HYPERLINK(IFERROR(LEFT(AE239,FIND(";",AE239)-1),AE239),"before"))</f>
         <v/>
       </c>
       <c r="AM239">
-        <f>IF(AF239="","",HYPERLINK(AF239,"after"))</f>
+        <f>IF(AF239="","",HYPERLINK(IFERROR(LEFT(AF239,FIND(";",AF239)-1),AF239),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9349,11 +9349,11 @@
         <v/>
       </c>
       <c r="AL240">
-        <f>IF(AE240="","",HYPERLINK(AE240,"before"))</f>
+        <f>IF(AE240="","",HYPERLINK(IFERROR(LEFT(AE240,FIND(";",AE240)-1),AE240),"before"))</f>
         <v/>
       </c>
       <c r="AM240">
-        <f>IF(AF240="","",HYPERLINK(AF240,"after"))</f>
+        <f>IF(AF240="","",HYPERLINK(IFERROR(LEFT(AF240,FIND(";",AF240)-1),AF240),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9385,11 +9385,11 @@
         <v/>
       </c>
       <c r="AL241">
-        <f>IF(AE241="","",HYPERLINK(AE241,"before"))</f>
+        <f>IF(AE241="","",HYPERLINK(IFERROR(LEFT(AE241,FIND(";",AE241)-1),AE241),"before"))</f>
         <v/>
       </c>
       <c r="AM241">
-        <f>IF(AF241="","",HYPERLINK(AF241,"after"))</f>
+        <f>IF(AF241="","",HYPERLINK(IFERROR(LEFT(AF241,FIND(";",AF241)-1),AF241),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9421,11 +9421,11 @@
         <v/>
       </c>
       <c r="AL242">
-        <f>IF(AE242="","",HYPERLINK(AE242,"before"))</f>
+        <f>IF(AE242="","",HYPERLINK(IFERROR(LEFT(AE242,FIND(";",AE242)-1),AE242),"before"))</f>
         <v/>
       </c>
       <c r="AM242">
-        <f>IF(AF242="","",HYPERLINK(AF242,"after"))</f>
+        <f>IF(AF242="","",HYPERLINK(IFERROR(LEFT(AF242,FIND(";",AF242)-1),AF242),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9457,11 +9457,11 @@
         <v/>
       </c>
       <c r="AL243">
-        <f>IF(AE243="","",HYPERLINK(AE243,"before"))</f>
+        <f>IF(AE243="","",HYPERLINK(IFERROR(LEFT(AE243,FIND(";",AE243)-1),AE243),"before"))</f>
         <v/>
       </c>
       <c r="AM243">
-        <f>IF(AF243="","",HYPERLINK(AF243,"after"))</f>
+        <f>IF(AF243="","",HYPERLINK(IFERROR(LEFT(AF243,FIND(";",AF243)-1),AF243),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9493,11 +9493,11 @@
         <v/>
       </c>
       <c r="AL244">
-        <f>IF(AE244="","",HYPERLINK(AE244,"before"))</f>
+        <f>IF(AE244="","",HYPERLINK(IFERROR(LEFT(AE244,FIND(";",AE244)-1),AE244),"before"))</f>
         <v/>
       </c>
       <c r="AM244">
-        <f>IF(AF244="","",HYPERLINK(AF244,"after"))</f>
+        <f>IF(AF244="","",HYPERLINK(IFERROR(LEFT(AF244,FIND(";",AF244)-1),AF244),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9529,11 +9529,11 @@
         <v/>
       </c>
       <c r="AL245">
-        <f>IF(AE245="","",HYPERLINK(AE245,"before"))</f>
+        <f>IF(AE245="","",HYPERLINK(IFERROR(LEFT(AE245,FIND(";",AE245)-1),AE245),"before"))</f>
         <v/>
       </c>
       <c r="AM245">
-        <f>IF(AF245="","",HYPERLINK(AF245,"after"))</f>
+        <f>IF(AF245="","",HYPERLINK(IFERROR(LEFT(AF245,FIND(";",AF245)-1),AF245),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9565,11 +9565,11 @@
         <v/>
       </c>
       <c r="AL246">
-        <f>IF(AE246="","",HYPERLINK(AE246,"before"))</f>
+        <f>IF(AE246="","",HYPERLINK(IFERROR(LEFT(AE246,FIND(";",AE246)-1),AE246),"before"))</f>
         <v/>
       </c>
       <c r="AM246">
-        <f>IF(AF246="","",HYPERLINK(AF246,"after"))</f>
+        <f>IF(AF246="","",HYPERLINK(IFERROR(LEFT(AF246,FIND(";",AF246)-1),AF246),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9601,11 +9601,11 @@
         <v/>
       </c>
       <c r="AL247">
-        <f>IF(AE247="","",HYPERLINK(AE247,"before"))</f>
+        <f>IF(AE247="","",HYPERLINK(IFERROR(LEFT(AE247,FIND(";",AE247)-1),AE247),"before"))</f>
         <v/>
       </c>
       <c r="AM247">
-        <f>IF(AF247="","",HYPERLINK(AF247,"after"))</f>
+        <f>IF(AF247="","",HYPERLINK(IFERROR(LEFT(AF247,FIND(";",AF247)-1),AF247),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9637,11 +9637,11 @@
         <v/>
       </c>
       <c r="AL248">
-        <f>IF(AE248="","",HYPERLINK(AE248,"before"))</f>
+        <f>IF(AE248="","",HYPERLINK(IFERROR(LEFT(AE248,FIND(";",AE248)-1),AE248),"before"))</f>
         <v/>
       </c>
       <c r="AM248">
-        <f>IF(AF248="","",HYPERLINK(AF248,"after"))</f>
+        <f>IF(AF248="","",HYPERLINK(IFERROR(LEFT(AF248,FIND(";",AF248)-1),AF248),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9673,11 +9673,11 @@
         <v/>
       </c>
       <c r="AL249">
-        <f>IF(AE249="","",HYPERLINK(AE249,"before"))</f>
+        <f>IF(AE249="","",HYPERLINK(IFERROR(LEFT(AE249,FIND(";",AE249)-1),AE249),"before"))</f>
         <v/>
       </c>
       <c r="AM249">
-        <f>IF(AF249="","",HYPERLINK(AF249,"after"))</f>
+        <f>IF(AF249="","",HYPERLINK(IFERROR(LEFT(AF249,FIND(";",AF249)-1),AF249),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9709,11 +9709,11 @@
         <v/>
       </c>
       <c r="AL250">
-        <f>IF(AE250="","",HYPERLINK(AE250,"before"))</f>
+        <f>IF(AE250="","",HYPERLINK(IFERROR(LEFT(AE250,FIND(";",AE250)-1),AE250),"before"))</f>
         <v/>
       </c>
       <c r="AM250">
-        <f>IF(AF250="","",HYPERLINK(AF250,"after"))</f>
+        <f>IF(AF250="","",HYPERLINK(IFERROR(LEFT(AF250,FIND(";",AF250)-1),AF250),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9745,11 +9745,11 @@
         <v/>
       </c>
       <c r="AL251">
-        <f>IF(AE251="","",HYPERLINK(AE251,"before"))</f>
+        <f>IF(AE251="","",HYPERLINK(IFERROR(LEFT(AE251,FIND(";",AE251)-1),AE251),"before"))</f>
         <v/>
       </c>
       <c r="AM251">
-        <f>IF(AF251="","",HYPERLINK(AF251,"after"))</f>
+        <f>IF(AF251="","",HYPERLINK(IFERROR(LEFT(AF251,FIND(";",AF251)-1),AF251),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9781,11 +9781,11 @@
         <v/>
       </c>
       <c r="AL252">
-        <f>IF(AE252="","",HYPERLINK(AE252,"before"))</f>
+        <f>IF(AE252="","",HYPERLINK(IFERROR(LEFT(AE252,FIND(";",AE252)-1),AE252),"before"))</f>
         <v/>
       </c>
       <c r="AM252">
-        <f>IF(AF252="","",HYPERLINK(AF252,"after"))</f>
+        <f>IF(AF252="","",HYPERLINK(IFERROR(LEFT(AF252,FIND(";",AF252)-1),AF252),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9817,11 +9817,11 @@
         <v/>
       </c>
       <c r="AL253">
-        <f>IF(AE253="","",HYPERLINK(AE253,"before"))</f>
+        <f>IF(AE253="","",HYPERLINK(IFERROR(LEFT(AE253,FIND(";",AE253)-1),AE253),"before"))</f>
         <v/>
       </c>
       <c r="AM253">
-        <f>IF(AF253="","",HYPERLINK(AF253,"after"))</f>
+        <f>IF(AF253="","",HYPERLINK(IFERROR(LEFT(AF253,FIND(";",AF253)-1),AF253),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9853,11 +9853,11 @@
         <v/>
       </c>
       <c r="AL254">
-        <f>IF(AE254="","",HYPERLINK(AE254,"before"))</f>
+        <f>IF(AE254="","",HYPERLINK(IFERROR(LEFT(AE254,FIND(";",AE254)-1),AE254),"before"))</f>
         <v/>
       </c>
       <c r="AM254">
-        <f>IF(AF254="","",HYPERLINK(AF254,"after"))</f>
+        <f>IF(AF254="","",HYPERLINK(IFERROR(LEFT(AF254,FIND(";",AF254)-1),AF254),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9889,11 +9889,11 @@
         <v/>
       </c>
       <c r="AL255">
-        <f>IF(AE255="","",HYPERLINK(AE255,"before"))</f>
+        <f>IF(AE255="","",HYPERLINK(IFERROR(LEFT(AE255,FIND(";",AE255)-1),AE255),"before"))</f>
         <v/>
       </c>
       <c r="AM255">
-        <f>IF(AF255="","",HYPERLINK(AF255,"after"))</f>
+        <f>IF(AF255="","",HYPERLINK(IFERROR(LEFT(AF255,FIND(";",AF255)-1),AF255),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9925,11 +9925,11 @@
         <v/>
       </c>
       <c r="AL256">
-        <f>IF(AE256="","",HYPERLINK(AE256,"before"))</f>
+        <f>IF(AE256="","",HYPERLINK(IFERROR(LEFT(AE256,FIND(";",AE256)-1),AE256),"before"))</f>
         <v/>
       </c>
       <c r="AM256">
-        <f>IF(AF256="","",HYPERLINK(AF256,"after"))</f>
+        <f>IF(AF256="","",HYPERLINK(IFERROR(LEFT(AF256,FIND(";",AF256)-1),AF256),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9961,11 +9961,11 @@
         <v/>
       </c>
       <c r="AL257">
-        <f>IF(AE257="","",HYPERLINK(AE257,"before"))</f>
+        <f>IF(AE257="","",HYPERLINK(IFERROR(LEFT(AE257,FIND(";",AE257)-1),AE257),"before"))</f>
         <v/>
       </c>
       <c r="AM257">
-        <f>IF(AF257="","",HYPERLINK(AF257,"after"))</f>
+        <f>IF(AF257="","",HYPERLINK(IFERROR(LEFT(AF257,FIND(";",AF257)-1),AF257),"after"))</f>
         <v/>
       </c>
     </row>
@@ -9997,11 +9997,11 @@
         <v/>
       </c>
       <c r="AL258">
-        <f>IF(AE258="","",HYPERLINK(AE258,"before"))</f>
+        <f>IF(AE258="","",HYPERLINK(IFERROR(LEFT(AE258,FIND(";",AE258)-1),AE258),"before"))</f>
         <v/>
       </c>
       <c r="AM258">
-        <f>IF(AF258="","",HYPERLINK(AF258,"after"))</f>
+        <f>IF(AF258="","",HYPERLINK(IFERROR(LEFT(AF258,FIND(";",AF258)-1),AF258),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10033,11 +10033,11 @@
         <v/>
       </c>
       <c r="AL259">
-        <f>IF(AE259="","",HYPERLINK(AE259,"before"))</f>
+        <f>IF(AE259="","",HYPERLINK(IFERROR(LEFT(AE259,FIND(";",AE259)-1),AE259),"before"))</f>
         <v/>
       </c>
       <c r="AM259">
-        <f>IF(AF259="","",HYPERLINK(AF259,"after"))</f>
+        <f>IF(AF259="","",HYPERLINK(IFERROR(LEFT(AF259,FIND(";",AF259)-1),AF259),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10069,11 +10069,11 @@
         <v/>
       </c>
       <c r="AL260">
-        <f>IF(AE260="","",HYPERLINK(AE260,"before"))</f>
+        <f>IF(AE260="","",HYPERLINK(IFERROR(LEFT(AE260,FIND(";",AE260)-1),AE260),"before"))</f>
         <v/>
       </c>
       <c r="AM260">
-        <f>IF(AF260="","",HYPERLINK(AF260,"after"))</f>
+        <f>IF(AF260="","",HYPERLINK(IFERROR(LEFT(AF260,FIND(";",AF260)-1),AF260),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10105,11 +10105,11 @@
         <v/>
       </c>
       <c r="AL261">
-        <f>IF(AE261="","",HYPERLINK(AE261,"before"))</f>
+        <f>IF(AE261="","",HYPERLINK(IFERROR(LEFT(AE261,FIND(";",AE261)-1),AE261),"before"))</f>
         <v/>
       </c>
       <c r="AM261">
-        <f>IF(AF261="","",HYPERLINK(AF261,"after"))</f>
+        <f>IF(AF261="","",HYPERLINK(IFERROR(LEFT(AF261,FIND(";",AF261)-1),AF261),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10141,11 +10141,11 @@
         <v/>
       </c>
       <c r="AL262">
-        <f>IF(AE262="","",HYPERLINK(AE262,"before"))</f>
+        <f>IF(AE262="","",HYPERLINK(IFERROR(LEFT(AE262,FIND(";",AE262)-1),AE262),"before"))</f>
         <v/>
       </c>
       <c r="AM262">
-        <f>IF(AF262="","",HYPERLINK(AF262,"after"))</f>
+        <f>IF(AF262="","",HYPERLINK(IFERROR(LEFT(AF262,FIND(";",AF262)-1),AF262),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10177,11 +10177,11 @@
         <v/>
       </c>
       <c r="AL263">
-        <f>IF(AE263="","",HYPERLINK(AE263,"before"))</f>
+        <f>IF(AE263="","",HYPERLINK(IFERROR(LEFT(AE263,FIND(";",AE263)-1),AE263),"before"))</f>
         <v/>
       </c>
       <c r="AM263">
-        <f>IF(AF263="","",HYPERLINK(AF263,"after"))</f>
+        <f>IF(AF263="","",HYPERLINK(IFERROR(LEFT(AF263,FIND(";",AF263)-1),AF263),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10213,11 +10213,11 @@
         <v/>
       </c>
       <c r="AL264">
-        <f>IF(AE264="","",HYPERLINK(AE264,"before"))</f>
+        <f>IF(AE264="","",HYPERLINK(IFERROR(LEFT(AE264,FIND(";",AE264)-1),AE264),"before"))</f>
         <v/>
       </c>
       <c r="AM264">
-        <f>IF(AF264="","",HYPERLINK(AF264,"after"))</f>
+        <f>IF(AF264="","",HYPERLINK(IFERROR(LEFT(AF264,FIND(";",AF264)-1),AF264),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10249,11 +10249,11 @@
         <v/>
       </c>
       <c r="AL265">
-        <f>IF(AE265="","",HYPERLINK(AE265,"before"))</f>
+        <f>IF(AE265="","",HYPERLINK(IFERROR(LEFT(AE265,FIND(";",AE265)-1),AE265),"before"))</f>
         <v/>
       </c>
       <c r="AM265">
-        <f>IF(AF265="","",HYPERLINK(AF265,"after"))</f>
+        <f>IF(AF265="","",HYPERLINK(IFERROR(LEFT(AF265,FIND(";",AF265)-1),AF265),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10285,11 +10285,11 @@
         <v/>
       </c>
       <c r="AL266">
-        <f>IF(AE266="","",HYPERLINK(AE266,"before"))</f>
+        <f>IF(AE266="","",HYPERLINK(IFERROR(LEFT(AE266,FIND(";",AE266)-1),AE266),"before"))</f>
         <v/>
       </c>
       <c r="AM266">
-        <f>IF(AF266="","",HYPERLINK(AF266,"after"))</f>
+        <f>IF(AF266="","",HYPERLINK(IFERROR(LEFT(AF266,FIND(";",AF266)-1),AF266),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10321,11 +10321,11 @@
         <v/>
       </c>
       <c r="AL267">
-        <f>IF(AE267="","",HYPERLINK(AE267,"before"))</f>
+        <f>IF(AE267="","",HYPERLINK(IFERROR(LEFT(AE267,FIND(";",AE267)-1),AE267),"before"))</f>
         <v/>
       </c>
       <c r="AM267">
-        <f>IF(AF267="","",HYPERLINK(AF267,"after"))</f>
+        <f>IF(AF267="","",HYPERLINK(IFERROR(LEFT(AF267,FIND(";",AF267)-1),AF267),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10357,11 +10357,11 @@
         <v/>
       </c>
       <c r="AL268">
-        <f>IF(AE268="","",HYPERLINK(AE268,"before"))</f>
+        <f>IF(AE268="","",HYPERLINK(IFERROR(LEFT(AE268,FIND(";",AE268)-1),AE268),"before"))</f>
         <v/>
       </c>
       <c r="AM268">
-        <f>IF(AF268="","",HYPERLINK(AF268,"after"))</f>
+        <f>IF(AF268="","",HYPERLINK(IFERROR(LEFT(AF268,FIND(";",AF268)-1),AF268),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10393,11 +10393,11 @@
         <v/>
       </c>
       <c r="AL269">
-        <f>IF(AE269="","",HYPERLINK(AE269,"before"))</f>
+        <f>IF(AE269="","",HYPERLINK(IFERROR(LEFT(AE269,FIND(";",AE269)-1),AE269),"before"))</f>
         <v/>
       </c>
       <c r="AM269">
-        <f>IF(AF269="","",HYPERLINK(AF269,"after"))</f>
+        <f>IF(AF269="","",HYPERLINK(IFERROR(LEFT(AF269,FIND(";",AF269)-1),AF269),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10429,11 +10429,11 @@
         <v/>
       </c>
       <c r="AL270">
-        <f>IF(AE270="","",HYPERLINK(AE270,"before"))</f>
+        <f>IF(AE270="","",HYPERLINK(IFERROR(LEFT(AE270,FIND(";",AE270)-1),AE270),"before"))</f>
         <v/>
       </c>
       <c r="AM270">
-        <f>IF(AF270="","",HYPERLINK(AF270,"after"))</f>
+        <f>IF(AF270="","",HYPERLINK(IFERROR(LEFT(AF270,FIND(";",AF270)-1),AF270),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10465,11 +10465,11 @@
         <v/>
       </c>
       <c r="AL271">
-        <f>IF(AE271="","",HYPERLINK(AE271,"before"))</f>
+        <f>IF(AE271="","",HYPERLINK(IFERROR(LEFT(AE271,FIND(";",AE271)-1),AE271),"before"))</f>
         <v/>
       </c>
       <c r="AM271">
-        <f>IF(AF271="","",HYPERLINK(AF271,"after"))</f>
+        <f>IF(AF271="","",HYPERLINK(IFERROR(LEFT(AF271,FIND(";",AF271)-1),AF271),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10501,11 +10501,11 @@
         <v/>
       </c>
       <c r="AL272">
-        <f>IF(AE272="","",HYPERLINK(AE272,"before"))</f>
+        <f>IF(AE272="","",HYPERLINK(IFERROR(LEFT(AE272,FIND(";",AE272)-1),AE272),"before"))</f>
         <v/>
       </c>
       <c r="AM272">
-        <f>IF(AF272="","",HYPERLINK(AF272,"after"))</f>
+        <f>IF(AF272="","",HYPERLINK(IFERROR(LEFT(AF272,FIND(";",AF272)-1),AF272),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10537,11 +10537,11 @@
         <v/>
       </c>
       <c r="AL273">
-        <f>IF(AE273="","",HYPERLINK(AE273,"before"))</f>
+        <f>IF(AE273="","",HYPERLINK(IFERROR(LEFT(AE273,FIND(";",AE273)-1),AE273),"before"))</f>
         <v/>
       </c>
       <c r="AM273">
-        <f>IF(AF273="","",HYPERLINK(AF273,"after"))</f>
+        <f>IF(AF273="","",HYPERLINK(IFERROR(LEFT(AF273,FIND(";",AF273)-1),AF273),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10573,11 +10573,11 @@
         <v/>
       </c>
       <c r="AL274">
-        <f>IF(AE274="","",HYPERLINK(AE274,"before"))</f>
+        <f>IF(AE274="","",HYPERLINK(IFERROR(LEFT(AE274,FIND(";",AE274)-1),AE274),"before"))</f>
         <v/>
       </c>
       <c r="AM274">
-        <f>IF(AF274="","",HYPERLINK(AF274,"after"))</f>
+        <f>IF(AF274="","",HYPERLINK(IFERROR(LEFT(AF274,FIND(";",AF274)-1),AF274),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10609,11 +10609,11 @@
         <v/>
       </c>
       <c r="AL275">
-        <f>IF(AE275="","",HYPERLINK(AE275,"before"))</f>
+        <f>IF(AE275="","",HYPERLINK(IFERROR(LEFT(AE275,FIND(";",AE275)-1),AE275),"before"))</f>
         <v/>
       </c>
       <c r="AM275">
-        <f>IF(AF275="","",HYPERLINK(AF275,"after"))</f>
+        <f>IF(AF275="","",HYPERLINK(IFERROR(LEFT(AF275,FIND(";",AF275)-1),AF275),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10645,11 +10645,11 @@
         <v/>
       </c>
       <c r="AL276">
-        <f>IF(AE276="","",HYPERLINK(AE276,"before"))</f>
+        <f>IF(AE276="","",HYPERLINK(IFERROR(LEFT(AE276,FIND(";",AE276)-1),AE276),"before"))</f>
         <v/>
       </c>
       <c r="AM276">
-        <f>IF(AF276="","",HYPERLINK(AF276,"after"))</f>
+        <f>IF(AF276="","",HYPERLINK(IFERROR(LEFT(AF276,FIND(";",AF276)-1),AF276),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10681,11 +10681,11 @@
         <v/>
       </c>
       <c r="AL277">
-        <f>IF(AE277="","",HYPERLINK(AE277,"before"))</f>
+        <f>IF(AE277="","",HYPERLINK(IFERROR(LEFT(AE277,FIND(";",AE277)-1),AE277),"before"))</f>
         <v/>
       </c>
       <c r="AM277">
-        <f>IF(AF277="","",HYPERLINK(AF277,"after"))</f>
+        <f>IF(AF277="","",HYPERLINK(IFERROR(LEFT(AF277,FIND(";",AF277)-1),AF277),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10717,11 +10717,11 @@
         <v/>
       </c>
       <c r="AL278">
-        <f>IF(AE278="","",HYPERLINK(AE278,"before"))</f>
+        <f>IF(AE278="","",HYPERLINK(IFERROR(LEFT(AE278,FIND(";",AE278)-1),AE278),"before"))</f>
         <v/>
       </c>
       <c r="AM278">
-        <f>IF(AF278="","",HYPERLINK(AF278,"after"))</f>
+        <f>IF(AF278="","",HYPERLINK(IFERROR(LEFT(AF278,FIND(";",AF278)-1),AF278),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10753,11 +10753,11 @@
         <v/>
       </c>
       <c r="AL279">
-        <f>IF(AE279="","",HYPERLINK(AE279,"before"))</f>
+        <f>IF(AE279="","",HYPERLINK(IFERROR(LEFT(AE279,FIND(";",AE279)-1),AE279),"before"))</f>
         <v/>
       </c>
       <c r="AM279">
-        <f>IF(AF279="","",HYPERLINK(AF279,"after"))</f>
+        <f>IF(AF279="","",HYPERLINK(IFERROR(LEFT(AF279,FIND(";",AF279)-1),AF279),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10789,11 +10789,11 @@
         <v/>
       </c>
       <c r="AL280">
-        <f>IF(AE280="","",HYPERLINK(AE280,"before"))</f>
+        <f>IF(AE280="","",HYPERLINK(IFERROR(LEFT(AE280,FIND(";",AE280)-1),AE280),"before"))</f>
         <v/>
       </c>
       <c r="AM280">
-        <f>IF(AF280="","",HYPERLINK(AF280,"after"))</f>
+        <f>IF(AF280="","",HYPERLINK(IFERROR(LEFT(AF280,FIND(";",AF280)-1),AF280),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10825,11 +10825,11 @@
         <v/>
       </c>
       <c r="AL281">
-        <f>IF(AE281="","",HYPERLINK(AE281,"before"))</f>
+        <f>IF(AE281="","",HYPERLINK(IFERROR(LEFT(AE281,FIND(";",AE281)-1),AE281),"before"))</f>
         <v/>
       </c>
       <c r="AM281">
-        <f>IF(AF281="","",HYPERLINK(AF281,"after"))</f>
+        <f>IF(AF281="","",HYPERLINK(IFERROR(LEFT(AF281,FIND(";",AF281)-1),AF281),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10861,11 +10861,11 @@
         <v/>
       </c>
       <c r="AL282">
-        <f>IF(AE282="","",HYPERLINK(AE282,"before"))</f>
+        <f>IF(AE282="","",HYPERLINK(IFERROR(LEFT(AE282,FIND(";",AE282)-1),AE282),"before"))</f>
         <v/>
       </c>
       <c r="AM282">
-        <f>IF(AF282="","",HYPERLINK(AF282,"after"))</f>
+        <f>IF(AF282="","",HYPERLINK(IFERROR(LEFT(AF282,FIND(";",AF282)-1),AF282),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10897,11 +10897,11 @@
         <v/>
       </c>
       <c r="AL283">
-        <f>IF(AE283="","",HYPERLINK(AE283,"before"))</f>
+        <f>IF(AE283="","",HYPERLINK(IFERROR(LEFT(AE283,FIND(";",AE283)-1),AE283),"before"))</f>
         <v/>
       </c>
       <c r="AM283">
-        <f>IF(AF283="","",HYPERLINK(AF283,"after"))</f>
+        <f>IF(AF283="","",HYPERLINK(IFERROR(LEFT(AF283,FIND(";",AF283)-1),AF283),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10933,11 +10933,11 @@
         <v/>
       </c>
       <c r="AL284">
-        <f>IF(AE284="","",HYPERLINK(AE284,"before"))</f>
+        <f>IF(AE284="","",HYPERLINK(IFERROR(LEFT(AE284,FIND(";",AE284)-1),AE284),"before"))</f>
         <v/>
       </c>
       <c r="AM284">
-        <f>IF(AF284="","",HYPERLINK(AF284,"after"))</f>
+        <f>IF(AF284="","",HYPERLINK(IFERROR(LEFT(AF284,FIND(";",AF284)-1),AF284),"after"))</f>
         <v/>
       </c>
     </row>
@@ -10969,11 +10969,11 @@
         <v/>
       </c>
       <c r="AL285">
-        <f>IF(AE285="","",HYPERLINK(AE285,"before"))</f>
+        <f>IF(AE285="","",HYPERLINK(IFERROR(LEFT(AE285,FIND(";",AE285)-1),AE285),"before"))</f>
         <v/>
       </c>
       <c r="AM285">
-        <f>IF(AF285="","",HYPERLINK(AF285,"after"))</f>
+        <f>IF(AF285="","",HYPERLINK(IFERROR(LEFT(AF285,FIND(";",AF285)-1),AF285),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11005,11 +11005,11 @@
         <v/>
       </c>
       <c r="AL286">
-        <f>IF(AE286="","",HYPERLINK(AE286,"before"))</f>
+        <f>IF(AE286="","",HYPERLINK(IFERROR(LEFT(AE286,FIND(";",AE286)-1),AE286),"before"))</f>
         <v/>
       </c>
       <c r="AM286">
-        <f>IF(AF286="","",HYPERLINK(AF286,"after"))</f>
+        <f>IF(AF286="","",HYPERLINK(IFERROR(LEFT(AF286,FIND(";",AF286)-1),AF286),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11041,11 +11041,11 @@
         <v/>
       </c>
       <c r="AL287">
-        <f>IF(AE287="","",HYPERLINK(AE287,"before"))</f>
+        <f>IF(AE287="","",HYPERLINK(IFERROR(LEFT(AE287,FIND(";",AE287)-1),AE287),"before"))</f>
         <v/>
       </c>
       <c r="AM287">
-        <f>IF(AF287="","",HYPERLINK(AF287,"after"))</f>
+        <f>IF(AF287="","",HYPERLINK(IFERROR(LEFT(AF287,FIND(";",AF287)-1),AF287),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11077,11 +11077,11 @@
         <v/>
       </c>
       <c r="AL288">
-        <f>IF(AE288="","",HYPERLINK(AE288,"before"))</f>
+        <f>IF(AE288="","",HYPERLINK(IFERROR(LEFT(AE288,FIND(";",AE288)-1),AE288),"before"))</f>
         <v/>
       </c>
       <c r="AM288">
-        <f>IF(AF288="","",HYPERLINK(AF288,"after"))</f>
+        <f>IF(AF288="","",HYPERLINK(IFERROR(LEFT(AF288,FIND(";",AF288)-1),AF288),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11113,11 +11113,11 @@
         <v/>
       </c>
       <c r="AL289">
-        <f>IF(AE289="","",HYPERLINK(AE289,"before"))</f>
+        <f>IF(AE289="","",HYPERLINK(IFERROR(LEFT(AE289,FIND(";",AE289)-1),AE289),"before"))</f>
         <v/>
       </c>
       <c r="AM289">
-        <f>IF(AF289="","",HYPERLINK(AF289,"after"))</f>
+        <f>IF(AF289="","",HYPERLINK(IFERROR(LEFT(AF289,FIND(";",AF289)-1),AF289),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11149,11 +11149,11 @@
         <v/>
       </c>
       <c r="AL290">
-        <f>IF(AE290="","",HYPERLINK(AE290,"before"))</f>
+        <f>IF(AE290="","",HYPERLINK(IFERROR(LEFT(AE290,FIND(";",AE290)-1),AE290),"before"))</f>
         <v/>
       </c>
       <c r="AM290">
-        <f>IF(AF290="","",HYPERLINK(AF290,"after"))</f>
+        <f>IF(AF290="","",HYPERLINK(IFERROR(LEFT(AF290,FIND(";",AF290)-1),AF290),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11185,11 +11185,11 @@
         <v/>
       </c>
       <c r="AL291">
-        <f>IF(AE291="","",HYPERLINK(AE291,"before"))</f>
+        <f>IF(AE291="","",HYPERLINK(IFERROR(LEFT(AE291,FIND(";",AE291)-1),AE291),"before"))</f>
         <v/>
       </c>
       <c r="AM291">
-        <f>IF(AF291="","",HYPERLINK(AF291,"after"))</f>
+        <f>IF(AF291="","",HYPERLINK(IFERROR(LEFT(AF291,FIND(";",AF291)-1),AF291),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11221,11 +11221,11 @@
         <v/>
       </c>
       <c r="AL292">
-        <f>IF(AE292="","",HYPERLINK(AE292,"before"))</f>
+        <f>IF(AE292="","",HYPERLINK(IFERROR(LEFT(AE292,FIND(";",AE292)-1),AE292),"before"))</f>
         <v/>
       </c>
       <c r="AM292">
-        <f>IF(AF292="","",HYPERLINK(AF292,"after"))</f>
+        <f>IF(AF292="","",HYPERLINK(IFERROR(LEFT(AF292,FIND(";",AF292)-1),AF292),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11257,11 +11257,11 @@
         <v/>
       </c>
       <c r="AL293">
-        <f>IF(AE293="","",HYPERLINK(AE293,"before"))</f>
+        <f>IF(AE293="","",HYPERLINK(IFERROR(LEFT(AE293,FIND(";",AE293)-1),AE293),"before"))</f>
         <v/>
       </c>
       <c r="AM293">
-        <f>IF(AF293="","",HYPERLINK(AF293,"after"))</f>
+        <f>IF(AF293="","",HYPERLINK(IFERROR(LEFT(AF293,FIND(";",AF293)-1),AF293),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11293,11 +11293,11 @@
         <v/>
       </c>
       <c r="AL294">
-        <f>IF(AE294="","",HYPERLINK(AE294,"before"))</f>
+        <f>IF(AE294="","",HYPERLINK(IFERROR(LEFT(AE294,FIND(";",AE294)-1),AE294),"before"))</f>
         <v/>
       </c>
       <c r="AM294">
-        <f>IF(AF294="","",HYPERLINK(AF294,"after"))</f>
+        <f>IF(AF294="","",HYPERLINK(IFERROR(LEFT(AF294,FIND(";",AF294)-1),AF294),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11329,11 +11329,11 @@
         <v/>
       </c>
       <c r="AL295">
-        <f>IF(AE295="","",HYPERLINK(AE295,"before"))</f>
+        <f>IF(AE295="","",HYPERLINK(IFERROR(LEFT(AE295,FIND(";",AE295)-1),AE295),"before"))</f>
         <v/>
       </c>
       <c r="AM295">
-        <f>IF(AF295="","",HYPERLINK(AF295,"after"))</f>
+        <f>IF(AF295="","",HYPERLINK(IFERROR(LEFT(AF295,FIND(";",AF295)-1),AF295),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11365,11 +11365,11 @@
         <v/>
       </c>
       <c r="AL296">
-        <f>IF(AE296="","",HYPERLINK(AE296,"before"))</f>
+        <f>IF(AE296="","",HYPERLINK(IFERROR(LEFT(AE296,FIND(";",AE296)-1),AE296),"before"))</f>
         <v/>
       </c>
       <c r="AM296">
-        <f>IF(AF296="","",HYPERLINK(AF296,"after"))</f>
+        <f>IF(AF296="","",HYPERLINK(IFERROR(LEFT(AF296,FIND(";",AF296)-1),AF296),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11401,11 +11401,11 @@
         <v/>
       </c>
       <c r="AL297">
-        <f>IF(AE297="","",HYPERLINK(AE297,"before"))</f>
+        <f>IF(AE297="","",HYPERLINK(IFERROR(LEFT(AE297,FIND(";",AE297)-1),AE297),"before"))</f>
         <v/>
       </c>
       <c r="AM297">
-        <f>IF(AF297="","",HYPERLINK(AF297,"after"))</f>
+        <f>IF(AF297="","",HYPERLINK(IFERROR(LEFT(AF297,FIND(";",AF297)-1),AF297),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11437,11 +11437,11 @@
         <v/>
       </c>
       <c r="AL298">
-        <f>IF(AE298="","",HYPERLINK(AE298,"before"))</f>
+        <f>IF(AE298="","",HYPERLINK(IFERROR(LEFT(AE298,FIND(";",AE298)-1),AE298),"before"))</f>
         <v/>
       </c>
       <c r="AM298">
-        <f>IF(AF298="","",HYPERLINK(AF298,"after"))</f>
+        <f>IF(AF298="","",HYPERLINK(IFERROR(LEFT(AF298,FIND(";",AF298)-1),AF298),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11473,11 +11473,11 @@
         <v/>
       </c>
       <c r="AL299">
-        <f>IF(AE299="","",HYPERLINK(AE299,"before"))</f>
+        <f>IF(AE299="","",HYPERLINK(IFERROR(LEFT(AE299,FIND(";",AE299)-1),AE299),"before"))</f>
         <v/>
       </c>
       <c r="AM299">
-        <f>IF(AF299="","",HYPERLINK(AF299,"after"))</f>
+        <f>IF(AF299="","",HYPERLINK(IFERROR(LEFT(AF299,FIND(";",AF299)-1),AF299),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11509,11 +11509,11 @@
         <v/>
       </c>
       <c r="AL300">
-        <f>IF(AE300="","",HYPERLINK(AE300,"before"))</f>
+        <f>IF(AE300="","",HYPERLINK(IFERROR(LEFT(AE300,FIND(";",AE300)-1),AE300),"before"))</f>
         <v/>
       </c>
       <c r="AM300">
-        <f>IF(AF300="","",HYPERLINK(AF300,"after"))</f>
+        <f>IF(AF300="","",HYPERLINK(IFERROR(LEFT(AF300,FIND(";",AF300)-1),AF300),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11545,11 +11545,11 @@
         <v/>
       </c>
       <c r="AL301">
-        <f>IF(AE301="","",HYPERLINK(AE301,"before"))</f>
+        <f>IF(AE301="","",HYPERLINK(IFERROR(LEFT(AE301,FIND(";",AE301)-1),AE301),"before"))</f>
         <v/>
       </c>
       <c r="AM301">
-        <f>IF(AF301="","",HYPERLINK(AF301,"after"))</f>
+        <f>IF(AF301="","",HYPERLINK(IFERROR(LEFT(AF301,FIND(";",AF301)-1),AF301),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11581,11 +11581,11 @@
         <v/>
       </c>
       <c r="AL302">
-        <f>IF(AE302="","",HYPERLINK(AE302,"before"))</f>
+        <f>IF(AE302="","",HYPERLINK(IFERROR(LEFT(AE302,FIND(";",AE302)-1),AE302),"before"))</f>
         <v/>
       </c>
       <c r="AM302">
-        <f>IF(AF302="","",HYPERLINK(AF302,"after"))</f>
+        <f>IF(AF302="","",HYPERLINK(IFERROR(LEFT(AF302,FIND(";",AF302)-1),AF302),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11617,11 +11617,11 @@
         <v/>
       </c>
       <c r="AL303">
-        <f>IF(AE303="","",HYPERLINK(AE303,"before"))</f>
+        <f>IF(AE303="","",HYPERLINK(IFERROR(LEFT(AE303,FIND(";",AE303)-1),AE303),"before"))</f>
         <v/>
       </c>
       <c r="AM303">
-        <f>IF(AF303="","",HYPERLINK(AF303,"after"))</f>
+        <f>IF(AF303="","",HYPERLINK(IFERROR(LEFT(AF303,FIND(";",AF303)-1),AF303),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11653,11 +11653,11 @@
         <v/>
       </c>
       <c r="AL304">
-        <f>IF(AE304="","",HYPERLINK(AE304,"before"))</f>
+        <f>IF(AE304="","",HYPERLINK(IFERROR(LEFT(AE304,FIND(";",AE304)-1),AE304),"before"))</f>
         <v/>
       </c>
       <c r="AM304">
-        <f>IF(AF304="","",HYPERLINK(AF304,"after"))</f>
+        <f>IF(AF304="","",HYPERLINK(IFERROR(LEFT(AF304,FIND(";",AF304)-1),AF304),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11689,11 +11689,11 @@
         <v/>
       </c>
       <c r="AL305">
-        <f>IF(AE305="","",HYPERLINK(AE305,"before"))</f>
+        <f>IF(AE305="","",HYPERLINK(IFERROR(LEFT(AE305,FIND(";",AE305)-1),AE305),"before"))</f>
         <v/>
       </c>
       <c r="AM305">
-        <f>IF(AF305="","",HYPERLINK(AF305,"after"))</f>
+        <f>IF(AF305="","",HYPERLINK(IFERROR(LEFT(AF305,FIND(";",AF305)-1),AF305),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11725,11 +11725,11 @@
         <v/>
       </c>
       <c r="AL306">
-        <f>IF(AE306="","",HYPERLINK(AE306,"before"))</f>
+        <f>IF(AE306="","",HYPERLINK(IFERROR(LEFT(AE306,FIND(";",AE306)-1),AE306),"before"))</f>
         <v/>
       </c>
       <c r="AM306">
-        <f>IF(AF306="","",HYPERLINK(AF306,"after"))</f>
+        <f>IF(AF306="","",HYPERLINK(IFERROR(LEFT(AF306,FIND(";",AF306)-1),AF306),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11761,11 +11761,11 @@
         <v/>
       </c>
       <c r="AL307">
-        <f>IF(AE307="","",HYPERLINK(AE307,"before"))</f>
+        <f>IF(AE307="","",HYPERLINK(IFERROR(LEFT(AE307,FIND(";",AE307)-1),AE307),"before"))</f>
         <v/>
       </c>
       <c r="AM307">
-        <f>IF(AF307="","",HYPERLINK(AF307,"after"))</f>
+        <f>IF(AF307="","",HYPERLINK(IFERROR(LEFT(AF307,FIND(";",AF307)-1),AF307),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11797,11 +11797,11 @@
         <v/>
       </c>
       <c r="AL308">
-        <f>IF(AE308="","",HYPERLINK(AE308,"before"))</f>
+        <f>IF(AE308="","",HYPERLINK(IFERROR(LEFT(AE308,FIND(";",AE308)-1),AE308),"before"))</f>
         <v/>
       </c>
       <c r="AM308">
-        <f>IF(AF308="","",HYPERLINK(AF308,"after"))</f>
+        <f>IF(AF308="","",HYPERLINK(IFERROR(LEFT(AF308,FIND(";",AF308)-1),AF308),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11833,11 +11833,11 @@
         <v/>
       </c>
       <c r="AL309">
-        <f>IF(AE309="","",HYPERLINK(AE309,"before"))</f>
+        <f>IF(AE309="","",HYPERLINK(IFERROR(LEFT(AE309,FIND(";",AE309)-1),AE309),"before"))</f>
         <v/>
       </c>
       <c r="AM309">
-        <f>IF(AF309="","",HYPERLINK(AF309,"after"))</f>
+        <f>IF(AF309="","",HYPERLINK(IFERROR(LEFT(AF309,FIND(";",AF309)-1),AF309),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11869,11 +11869,11 @@
         <v/>
       </c>
       <c r="AL310">
-        <f>IF(AE310="","",HYPERLINK(AE310,"before"))</f>
+        <f>IF(AE310="","",HYPERLINK(IFERROR(LEFT(AE310,FIND(";",AE310)-1),AE310),"before"))</f>
         <v/>
       </c>
       <c r="AM310">
-        <f>IF(AF310="","",HYPERLINK(AF310,"after"))</f>
+        <f>IF(AF310="","",HYPERLINK(IFERROR(LEFT(AF310,FIND(";",AF310)-1),AF310),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11905,11 +11905,11 @@
         <v/>
       </c>
       <c r="AL311">
-        <f>IF(AE311="","",HYPERLINK(AE311,"before"))</f>
+        <f>IF(AE311="","",HYPERLINK(IFERROR(LEFT(AE311,FIND(";",AE311)-1),AE311),"before"))</f>
         <v/>
       </c>
       <c r="AM311">
-        <f>IF(AF311="","",HYPERLINK(AF311,"after"))</f>
+        <f>IF(AF311="","",HYPERLINK(IFERROR(LEFT(AF311,FIND(";",AF311)-1),AF311),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11941,11 +11941,11 @@
         <v/>
       </c>
       <c r="AL312">
-        <f>IF(AE312="","",HYPERLINK(AE312,"before"))</f>
+        <f>IF(AE312="","",HYPERLINK(IFERROR(LEFT(AE312,FIND(";",AE312)-1),AE312),"before"))</f>
         <v/>
       </c>
       <c r="AM312">
-        <f>IF(AF312="","",HYPERLINK(AF312,"after"))</f>
+        <f>IF(AF312="","",HYPERLINK(IFERROR(LEFT(AF312,FIND(";",AF312)-1),AF312),"after"))</f>
         <v/>
       </c>
     </row>
@@ -11977,11 +11977,11 @@
         <v/>
       </c>
       <c r="AL313">
-        <f>IF(AE313="","",HYPERLINK(AE313,"before"))</f>
+        <f>IF(AE313="","",HYPERLINK(IFERROR(LEFT(AE313,FIND(";",AE313)-1),AE313),"before"))</f>
         <v/>
       </c>
       <c r="AM313">
-        <f>IF(AF313="","",HYPERLINK(AF313,"after"))</f>
+        <f>IF(AF313="","",HYPERLINK(IFERROR(LEFT(AF313,FIND(";",AF313)-1),AF313),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12013,11 +12013,11 @@
         <v/>
       </c>
       <c r="AL314">
-        <f>IF(AE314="","",HYPERLINK(AE314,"before"))</f>
+        <f>IF(AE314="","",HYPERLINK(IFERROR(LEFT(AE314,FIND(";",AE314)-1),AE314),"before"))</f>
         <v/>
       </c>
       <c r="AM314">
-        <f>IF(AF314="","",HYPERLINK(AF314,"after"))</f>
+        <f>IF(AF314="","",HYPERLINK(IFERROR(LEFT(AF314,FIND(";",AF314)-1),AF314),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12049,11 +12049,11 @@
         <v/>
       </c>
       <c r="AL315">
-        <f>IF(AE315="","",HYPERLINK(AE315,"before"))</f>
+        <f>IF(AE315="","",HYPERLINK(IFERROR(LEFT(AE315,FIND(";",AE315)-1),AE315),"before"))</f>
         <v/>
       </c>
       <c r="AM315">
-        <f>IF(AF315="","",HYPERLINK(AF315,"after"))</f>
+        <f>IF(AF315="","",HYPERLINK(IFERROR(LEFT(AF315,FIND(";",AF315)-1),AF315),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12085,11 +12085,11 @@
         <v/>
       </c>
       <c r="AL316">
-        <f>IF(AE316="","",HYPERLINK(AE316,"before"))</f>
+        <f>IF(AE316="","",HYPERLINK(IFERROR(LEFT(AE316,FIND(";",AE316)-1),AE316),"before"))</f>
         <v/>
       </c>
       <c r="AM316">
-        <f>IF(AF316="","",HYPERLINK(AF316,"after"))</f>
+        <f>IF(AF316="","",HYPERLINK(IFERROR(LEFT(AF316,FIND(";",AF316)-1),AF316),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12121,11 +12121,11 @@
         <v/>
       </c>
       <c r="AL317">
-        <f>IF(AE317="","",HYPERLINK(AE317,"before"))</f>
+        <f>IF(AE317="","",HYPERLINK(IFERROR(LEFT(AE317,FIND(";",AE317)-1),AE317),"before"))</f>
         <v/>
       </c>
       <c r="AM317">
-        <f>IF(AF317="","",HYPERLINK(AF317,"after"))</f>
+        <f>IF(AF317="","",HYPERLINK(IFERROR(LEFT(AF317,FIND(";",AF317)-1),AF317),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12157,11 +12157,11 @@
         <v/>
       </c>
       <c r="AL318">
-        <f>IF(AE318="","",HYPERLINK(AE318,"before"))</f>
+        <f>IF(AE318="","",HYPERLINK(IFERROR(LEFT(AE318,FIND(";",AE318)-1),AE318),"before"))</f>
         <v/>
       </c>
       <c r="AM318">
-        <f>IF(AF318="","",HYPERLINK(AF318,"after"))</f>
+        <f>IF(AF318="","",HYPERLINK(IFERROR(LEFT(AF318,FIND(";",AF318)-1),AF318),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12193,11 +12193,11 @@
         <v/>
       </c>
       <c r="AL319">
-        <f>IF(AE319="","",HYPERLINK(AE319,"before"))</f>
+        <f>IF(AE319="","",HYPERLINK(IFERROR(LEFT(AE319,FIND(";",AE319)-1),AE319),"before"))</f>
         <v/>
       </c>
       <c r="AM319">
-        <f>IF(AF319="","",HYPERLINK(AF319,"after"))</f>
+        <f>IF(AF319="","",HYPERLINK(IFERROR(LEFT(AF319,FIND(";",AF319)-1),AF319),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12229,11 +12229,11 @@
         <v/>
       </c>
       <c r="AL320">
-        <f>IF(AE320="","",HYPERLINK(AE320,"before"))</f>
+        <f>IF(AE320="","",HYPERLINK(IFERROR(LEFT(AE320,FIND(";",AE320)-1),AE320),"before"))</f>
         <v/>
       </c>
       <c r="AM320">
-        <f>IF(AF320="","",HYPERLINK(AF320,"after"))</f>
+        <f>IF(AF320="","",HYPERLINK(IFERROR(LEFT(AF320,FIND(";",AF320)-1),AF320),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12265,11 +12265,11 @@
         <v/>
       </c>
       <c r="AL321">
-        <f>IF(AE321="","",HYPERLINK(AE321,"before"))</f>
+        <f>IF(AE321="","",HYPERLINK(IFERROR(LEFT(AE321,FIND(";",AE321)-1),AE321),"before"))</f>
         <v/>
       </c>
       <c r="AM321">
-        <f>IF(AF321="","",HYPERLINK(AF321,"after"))</f>
+        <f>IF(AF321="","",HYPERLINK(IFERROR(LEFT(AF321,FIND(";",AF321)-1),AF321),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12301,11 +12301,11 @@
         <v/>
       </c>
       <c r="AL322">
-        <f>IF(AE322="","",HYPERLINK(AE322,"before"))</f>
+        <f>IF(AE322="","",HYPERLINK(IFERROR(LEFT(AE322,FIND(";",AE322)-1),AE322),"before"))</f>
         <v/>
       </c>
       <c r="AM322">
-        <f>IF(AF322="","",HYPERLINK(AF322,"after"))</f>
+        <f>IF(AF322="","",HYPERLINK(IFERROR(LEFT(AF322,FIND(";",AF322)-1),AF322),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12337,11 +12337,11 @@
         <v/>
       </c>
       <c r="AL323">
-        <f>IF(AE323="","",HYPERLINK(AE323,"before"))</f>
+        <f>IF(AE323="","",HYPERLINK(IFERROR(LEFT(AE323,FIND(";",AE323)-1),AE323),"before"))</f>
         <v/>
       </c>
       <c r="AM323">
-        <f>IF(AF323="","",HYPERLINK(AF323,"after"))</f>
+        <f>IF(AF323="","",HYPERLINK(IFERROR(LEFT(AF323,FIND(";",AF323)-1),AF323),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12373,11 +12373,11 @@
         <v/>
       </c>
       <c r="AL324">
-        <f>IF(AE324="","",HYPERLINK(AE324,"before"))</f>
+        <f>IF(AE324="","",HYPERLINK(IFERROR(LEFT(AE324,FIND(";",AE324)-1),AE324),"before"))</f>
         <v/>
       </c>
       <c r="AM324">
-        <f>IF(AF324="","",HYPERLINK(AF324,"after"))</f>
+        <f>IF(AF324="","",HYPERLINK(IFERROR(LEFT(AF324,FIND(";",AF324)-1),AF324),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12409,11 +12409,11 @@
         <v/>
       </c>
       <c r="AL325">
-        <f>IF(AE325="","",HYPERLINK(AE325,"before"))</f>
+        <f>IF(AE325="","",HYPERLINK(IFERROR(LEFT(AE325,FIND(";",AE325)-1),AE325),"before"))</f>
         <v/>
       </c>
       <c r="AM325">
-        <f>IF(AF325="","",HYPERLINK(AF325,"after"))</f>
+        <f>IF(AF325="","",HYPERLINK(IFERROR(LEFT(AF325,FIND(";",AF325)-1),AF325),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12445,11 +12445,11 @@
         <v/>
       </c>
       <c r="AL326">
-        <f>IF(AE326="","",HYPERLINK(AE326,"before"))</f>
+        <f>IF(AE326="","",HYPERLINK(IFERROR(LEFT(AE326,FIND(";",AE326)-1),AE326),"before"))</f>
         <v/>
       </c>
       <c r="AM326">
-        <f>IF(AF326="","",HYPERLINK(AF326,"after"))</f>
+        <f>IF(AF326="","",HYPERLINK(IFERROR(LEFT(AF326,FIND(";",AF326)-1),AF326),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12481,11 +12481,11 @@
         <v/>
       </c>
       <c r="AL327">
-        <f>IF(AE327="","",HYPERLINK(AE327,"before"))</f>
+        <f>IF(AE327="","",HYPERLINK(IFERROR(LEFT(AE327,FIND(";",AE327)-1),AE327),"before"))</f>
         <v/>
       </c>
       <c r="AM327">
-        <f>IF(AF327="","",HYPERLINK(AF327,"after"))</f>
+        <f>IF(AF327="","",HYPERLINK(IFERROR(LEFT(AF327,FIND(";",AF327)-1),AF327),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12517,11 +12517,11 @@
         <v/>
       </c>
       <c r="AL328">
-        <f>IF(AE328="","",HYPERLINK(AE328,"before"))</f>
+        <f>IF(AE328="","",HYPERLINK(IFERROR(LEFT(AE328,FIND(";",AE328)-1),AE328),"before"))</f>
         <v/>
       </c>
       <c r="AM328">
-        <f>IF(AF328="","",HYPERLINK(AF328,"after"))</f>
+        <f>IF(AF328="","",HYPERLINK(IFERROR(LEFT(AF328,FIND(";",AF328)-1),AF328),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12553,11 +12553,11 @@
         <v/>
       </c>
       <c r="AL329">
-        <f>IF(AE329="","",HYPERLINK(AE329,"before"))</f>
+        <f>IF(AE329="","",HYPERLINK(IFERROR(LEFT(AE329,FIND(";",AE329)-1),AE329),"before"))</f>
         <v/>
       </c>
       <c r="AM329">
-        <f>IF(AF329="","",HYPERLINK(AF329,"after"))</f>
+        <f>IF(AF329="","",HYPERLINK(IFERROR(LEFT(AF329,FIND(";",AF329)-1),AF329),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12589,11 +12589,11 @@
         <v/>
       </c>
       <c r="AL330">
-        <f>IF(AE330="","",HYPERLINK(AE330,"before"))</f>
+        <f>IF(AE330="","",HYPERLINK(IFERROR(LEFT(AE330,FIND(";",AE330)-1),AE330),"before"))</f>
         <v/>
       </c>
       <c r="AM330">
-        <f>IF(AF330="","",HYPERLINK(AF330,"after"))</f>
+        <f>IF(AF330="","",HYPERLINK(IFERROR(LEFT(AF330,FIND(";",AF330)-1),AF330),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12625,11 +12625,11 @@
         <v/>
       </c>
       <c r="AL331">
-        <f>IF(AE331="","",HYPERLINK(AE331,"before"))</f>
+        <f>IF(AE331="","",HYPERLINK(IFERROR(LEFT(AE331,FIND(";",AE331)-1),AE331),"before"))</f>
         <v/>
       </c>
       <c r="AM331">
-        <f>IF(AF331="","",HYPERLINK(AF331,"after"))</f>
+        <f>IF(AF331="","",HYPERLINK(IFERROR(LEFT(AF331,FIND(";",AF331)-1),AF331),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12661,11 +12661,11 @@
         <v/>
       </c>
       <c r="AL332">
-        <f>IF(AE332="","",HYPERLINK(AE332,"before"))</f>
+        <f>IF(AE332="","",HYPERLINK(IFERROR(LEFT(AE332,FIND(";",AE332)-1),AE332),"before"))</f>
         <v/>
       </c>
       <c r="AM332">
-        <f>IF(AF332="","",HYPERLINK(AF332,"after"))</f>
+        <f>IF(AF332="","",HYPERLINK(IFERROR(LEFT(AF332,FIND(";",AF332)-1),AF332),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12697,11 +12697,11 @@
         <v/>
       </c>
       <c r="AL333">
-        <f>IF(AE333="","",HYPERLINK(AE333,"before"))</f>
+        <f>IF(AE333="","",HYPERLINK(IFERROR(LEFT(AE333,FIND(";",AE333)-1),AE333),"before"))</f>
         <v/>
       </c>
       <c r="AM333">
-        <f>IF(AF333="","",HYPERLINK(AF333,"after"))</f>
+        <f>IF(AF333="","",HYPERLINK(IFERROR(LEFT(AF333,FIND(";",AF333)-1),AF333),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12733,11 +12733,11 @@
         <v/>
       </c>
       <c r="AL334">
-        <f>IF(AE334="","",HYPERLINK(AE334,"before"))</f>
+        <f>IF(AE334="","",HYPERLINK(IFERROR(LEFT(AE334,FIND(";",AE334)-1),AE334),"before"))</f>
         <v/>
       </c>
       <c r="AM334">
-        <f>IF(AF334="","",HYPERLINK(AF334,"after"))</f>
+        <f>IF(AF334="","",HYPERLINK(IFERROR(LEFT(AF334,FIND(";",AF334)-1),AF334),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12769,11 +12769,11 @@
         <v/>
       </c>
       <c r="AL335">
-        <f>IF(AE335="","",HYPERLINK(AE335,"before"))</f>
+        <f>IF(AE335="","",HYPERLINK(IFERROR(LEFT(AE335,FIND(";",AE335)-1),AE335),"before"))</f>
         <v/>
       </c>
       <c r="AM335">
-        <f>IF(AF335="","",HYPERLINK(AF335,"after"))</f>
+        <f>IF(AF335="","",HYPERLINK(IFERROR(LEFT(AF335,FIND(";",AF335)-1),AF335),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12805,11 +12805,11 @@
         <v/>
       </c>
       <c r="AL336">
-        <f>IF(AE336="","",HYPERLINK(AE336,"before"))</f>
+        <f>IF(AE336="","",HYPERLINK(IFERROR(LEFT(AE336,FIND(";",AE336)-1),AE336),"before"))</f>
         <v/>
       </c>
       <c r="AM336">
-        <f>IF(AF336="","",HYPERLINK(AF336,"after"))</f>
+        <f>IF(AF336="","",HYPERLINK(IFERROR(LEFT(AF336,FIND(";",AF336)-1),AF336),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12841,11 +12841,11 @@
         <v/>
       </c>
       <c r="AL337">
-        <f>IF(AE337="","",HYPERLINK(AE337,"before"))</f>
+        <f>IF(AE337="","",HYPERLINK(IFERROR(LEFT(AE337,FIND(";",AE337)-1),AE337),"before"))</f>
         <v/>
       </c>
       <c r="AM337">
-        <f>IF(AF337="","",HYPERLINK(AF337,"after"))</f>
+        <f>IF(AF337="","",HYPERLINK(IFERROR(LEFT(AF337,FIND(";",AF337)-1),AF337),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12877,11 +12877,11 @@
         <v/>
       </c>
       <c r="AL338">
-        <f>IF(AE338="","",HYPERLINK(AE338,"before"))</f>
+        <f>IF(AE338="","",HYPERLINK(IFERROR(LEFT(AE338,FIND(";",AE338)-1),AE338),"before"))</f>
         <v/>
       </c>
       <c r="AM338">
-        <f>IF(AF338="","",HYPERLINK(AF338,"after"))</f>
+        <f>IF(AF338="","",HYPERLINK(IFERROR(LEFT(AF338,FIND(";",AF338)-1),AF338),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12913,11 +12913,11 @@
         <v/>
       </c>
       <c r="AL339">
-        <f>IF(AE339="","",HYPERLINK(AE339,"before"))</f>
+        <f>IF(AE339="","",HYPERLINK(IFERROR(LEFT(AE339,FIND(";",AE339)-1),AE339),"before"))</f>
         <v/>
       </c>
       <c r="AM339">
-        <f>IF(AF339="","",HYPERLINK(AF339,"after"))</f>
+        <f>IF(AF339="","",HYPERLINK(IFERROR(LEFT(AF339,FIND(";",AF339)-1),AF339),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12949,11 +12949,11 @@
         <v/>
       </c>
       <c r="AL340">
-        <f>IF(AE340="","",HYPERLINK(AE340,"before"))</f>
+        <f>IF(AE340="","",HYPERLINK(IFERROR(LEFT(AE340,FIND(";",AE340)-1),AE340),"before"))</f>
         <v/>
       </c>
       <c r="AM340">
-        <f>IF(AF340="","",HYPERLINK(AF340,"after"))</f>
+        <f>IF(AF340="","",HYPERLINK(IFERROR(LEFT(AF340,FIND(";",AF340)-1),AF340),"after"))</f>
         <v/>
       </c>
     </row>
@@ -12985,11 +12985,11 @@
         <v/>
       </c>
       <c r="AL341">
-        <f>IF(AE341="","",HYPERLINK(AE341,"before"))</f>
+        <f>IF(AE341="","",HYPERLINK(IFERROR(LEFT(AE341,FIND(";",AE341)-1),AE341),"before"))</f>
         <v/>
       </c>
       <c r="AM341">
-        <f>IF(AF341="","",HYPERLINK(AF341,"after"))</f>
+        <f>IF(AF341="","",HYPERLINK(IFERROR(LEFT(AF341,FIND(";",AF341)-1),AF341),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13021,11 +13021,11 @@
         <v/>
       </c>
       <c r="AL342">
-        <f>IF(AE342="","",HYPERLINK(AE342,"before"))</f>
+        <f>IF(AE342="","",HYPERLINK(IFERROR(LEFT(AE342,FIND(";",AE342)-1),AE342),"before"))</f>
         <v/>
       </c>
       <c r="AM342">
-        <f>IF(AF342="","",HYPERLINK(AF342,"after"))</f>
+        <f>IF(AF342="","",HYPERLINK(IFERROR(LEFT(AF342,FIND(";",AF342)-1),AF342),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13057,11 +13057,11 @@
         <v/>
       </c>
       <c r="AL343">
-        <f>IF(AE343="","",HYPERLINK(AE343,"before"))</f>
+        <f>IF(AE343="","",HYPERLINK(IFERROR(LEFT(AE343,FIND(";",AE343)-1),AE343),"before"))</f>
         <v/>
       </c>
       <c r="AM343">
-        <f>IF(AF343="","",HYPERLINK(AF343,"after"))</f>
+        <f>IF(AF343="","",HYPERLINK(IFERROR(LEFT(AF343,FIND(";",AF343)-1),AF343),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13093,11 +13093,11 @@
         <v/>
       </c>
       <c r="AL344">
-        <f>IF(AE344="","",HYPERLINK(AE344,"before"))</f>
+        <f>IF(AE344="","",HYPERLINK(IFERROR(LEFT(AE344,FIND(";",AE344)-1),AE344),"before"))</f>
         <v/>
       </c>
       <c r="AM344">
-        <f>IF(AF344="","",HYPERLINK(AF344,"after"))</f>
+        <f>IF(AF344="","",HYPERLINK(IFERROR(LEFT(AF344,FIND(";",AF344)-1),AF344),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13129,11 +13129,11 @@
         <v/>
       </c>
       <c r="AL345">
-        <f>IF(AE345="","",HYPERLINK(AE345,"before"))</f>
+        <f>IF(AE345="","",HYPERLINK(IFERROR(LEFT(AE345,FIND(";",AE345)-1),AE345),"before"))</f>
         <v/>
       </c>
       <c r="AM345">
-        <f>IF(AF345="","",HYPERLINK(AF345,"after"))</f>
+        <f>IF(AF345="","",HYPERLINK(IFERROR(LEFT(AF345,FIND(";",AF345)-1),AF345),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13165,11 +13165,11 @@
         <v/>
       </c>
       <c r="AL346">
-        <f>IF(AE346="","",HYPERLINK(AE346,"before"))</f>
+        <f>IF(AE346="","",HYPERLINK(IFERROR(LEFT(AE346,FIND(";",AE346)-1),AE346),"before"))</f>
         <v/>
       </c>
       <c r="AM346">
-        <f>IF(AF346="","",HYPERLINK(AF346,"after"))</f>
+        <f>IF(AF346="","",HYPERLINK(IFERROR(LEFT(AF346,FIND(";",AF346)-1),AF346),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13201,11 +13201,11 @@
         <v/>
       </c>
       <c r="AL347">
-        <f>IF(AE347="","",HYPERLINK(AE347,"before"))</f>
+        <f>IF(AE347="","",HYPERLINK(IFERROR(LEFT(AE347,FIND(";",AE347)-1),AE347),"before"))</f>
         <v/>
       </c>
       <c r="AM347">
-        <f>IF(AF347="","",HYPERLINK(AF347,"after"))</f>
+        <f>IF(AF347="","",HYPERLINK(IFERROR(LEFT(AF347,FIND(";",AF347)-1),AF347),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13237,11 +13237,11 @@
         <v/>
       </c>
       <c r="AL348">
-        <f>IF(AE348="","",HYPERLINK(AE348,"before"))</f>
+        <f>IF(AE348="","",HYPERLINK(IFERROR(LEFT(AE348,FIND(";",AE348)-1),AE348),"before"))</f>
         <v/>
       </c>
       <c r="AM348">
-        <f>IF(AF348="","",HYPERLINK(AF348,"after"))</f>
+        <f>IF(AF348="","",HYPERLINK(IFERROR(LEFT(AF348,FIND(";",AF348)-1),AF348),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13273,11 +13273,11 @@
         <v/>
       </c>
       <c r="AL349">
-        <f>IF(AE349="","",HYPERLINK(AE349,"before"))</f>
+        <f>IF(AE349="","",HYPERLINK(IFERROR(LEFT(AE349,FIND(";",AE349)-1),AE349),"before"))</f>
         <v/>
       </c>
       <c r="AM349">
-        <f>IF(AF349="","",HYPERLINK(AF349,"after"))</f>
+        <f>IF(AF349="","",HYPERLINK(IFERROR(LEFT(AF349,FIND(";",AF349)-1),AF349),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13309,11 +13309,11 @@
         <v/>
       </c>
       <c r="AL350">
-        <f>IF(AE350="","",HYPERLINK(AE350,"before"))</f>
+        <f>IF(AE350="","",HYPERLINK(IFERROR(LEFT(AE350,FIND(";",AE350)-1),AE350),"before"))</f>
         <v/>
       </c>
       <c r="AM350">
-        <f>IF(AF350="","",HYPERLINK(AF350,"after"))</f>
+        <f>IF(AF350="","",HYPERLINK(IFERROR(LEFT(AF350,FIND(";",AF350)-1),AF350),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13345,11 +13345,11 @@
         <v/>
       </c>
       <c r="AL351">
-        <f>IF(AE351="","",HYPERLINK(AE351,"before"))</f>
+        <f>IF(AE351="","",HYPERLINK(IFERROR(LEFT(AE351,FIND(";",AE351)-1),AE351),"before"))</f>
         <v/>
       </c>
       <c r="AM351">
-        <f>IF(AF351="","",HYPERLINK(AF351,"after"))</f>
+        <f>IF(AF351="","",HYPERLINK(IFERROR(LEFT(AF351,FIND(";",AF351)-1),AF351),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13381,11 +13381,11 @@
         <v/>
       </c>
       <c r="AL352">
-        <f>IF(AE352="","",HYPERLINK(AE352,"before"))</f>
+        <f>IF(AE352="","",HYPERLINK(IFERROR(LEFT(AE352,FIND(";",AE352)-1),AE352),"before"))</f>
         <v/>
       </c>
       <c r="AM352">
-        <f>IF(AF352="","",HYPERLINK(AF352,"after"))</f>
+        <f>IF(AF352="","",HYPERLINK(IFERROR(LEFT(AF352,FIND(";",AF352)-1),AF352),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13417,11 +13417,11 @@
         <v/>
       </c>
       <c r="AL353">
-        <f>IF(AE353="","",HYPERLINK(AE353,"before"))</f>
+        <f>IF(AE353="","",HYPERLINK(IFERROR(LEFT(AE353,FIND(";",AE353)-1),AE353),"before"))</f>
         <v/>
       </c>
       <c r="AM353">
-        <f>IF(AF353="","",HYPERLINK(AF353,"after"))</f>
+        <f>IF(AF353="","",HYPERLINK(IFERROR(LEFT(AF353,FIND(";",AF353)-1),AF353),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13453,11 +13453,11 @@
         <v/>
       </c>
       <c r="AL354">
-        <f>IF(AE354="","",HYPERLINK(AE354,"before"))</f>
+        <f>IF(AE354="","",HYPERLINK(IFERROR(LEFT(AE354,FIND(";",AE354)-1),AE354),"before"))</f>
         <v/>
       </c>
       <c r="AM354">
-        <f>IF(AF354="","",HYPERLINK(AF354,"after"))</f>
+        <f>IF(AF354="","",HYPERLINK(IFERROR(LEFT(AF354,FIND(";",AF354)-1),AF354),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13489,11 +13489,11 @@
         <v/>
       </c>
       <c r="AL355">
-        <f>IF(AE355="","",HYPERLINK(AE355,"before"))</f>
+        <f>IF(AE355="","",HYPERLINK(IFERROR(LEFT(AE355,FIND(";",AE355)-1),AE355),"before"))</f>
         <v/>
       </c>
       <c r="AM355">
-        <f>IF(AF355="","",HYPERLINK(AF355,"after"))</f>
+        <f>IF(AF355="","",HYPERLINK(IFERROR(LEFT(AF355,FIND(";",AF355)-1),AF355),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13525,11 +13525,11 @@
         <v/>
       </c>
       <c r="AL356">
-        <f>IF(AE356="","",HYPERLINK(AE356,"before"))</f>
+        <f>IF(AE356="","",HYPERLINK(IFERROR(LEFT(AE356,FIND(";",AE356)-1),AE356),"before"))</f>
         <v/>
       </c>
       <c r="AM356">
-        <f>IF(AF356="","",HYPERLINK(AF356,"after"))</f>
+        <f>IF(AF356="","",HYPERLINK(IFERROR(LEFT(AF356,FIND(";",AF356)-1),AF356),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13561,11 +13561,11 @@
         <v/>
       </c>
       <c r="AL357">
-        <f>IF(AE357="","",HYPERLINK(AE357,"before"))</f>
+        <f>IF(AE357="","",HYPERLINK(IFERROR(LEFT(AE357,FIND(";",AE357)-1),AE357),"before"))</f>
         <v/>
       </c>
       <c r="AM357">
-        <f>IF(AF357="","",HYPERLINK(AF357,"after"))</f>
+        <f>IF(AF357="","",HYPERLINK(IFERROR(LEFT(AF357,FIND(";",AF357)-1),AF357),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13597,11 +13597,11 @@
         <v/>
       </c>
       <c r="AL358">
-        <f>IF(AE358="","",HYPERLINK(AE358,"before"))</f>
+        <f>IF(AE358="","",HYPERLINK(IFERROR(LEFT(AE358,FIND(";",AE358)-1),AE358),"before"))</f>
         <v/>
       </c>
       <c r="AM358">
-        <f>IF(AF358="","",HYPERLINK(AF358,"after"))</f>
+        <f>IF(AF358="","",HYPERLINK(IFERROR(LEFT(AF358,FIND(";",AF358)-1),AF358),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13633,11 +13633,11 @@
         <v/>
       </c>
       <c r="AL359">
-        <f>IF(AE359="","",HYPERLINK(AE359,"before"))</f>
+        <f>IF(AE359="","",HYPERLINK(IFERROR(LEFT(AE359,FIND(";",AE359)-1),AE359),"before"))</f>
         <v/>
       </c>
       <c r="AM359">
-        <f>IF(AF359="","",HYPERLINK(AF359,"after"))</f>
+        <f>IF(AF359="","",HYPERLINK(IFERROR(LEFT(AF359,FIND(";",AF359)-1),AF359),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13669,11 +13669,11 @@
         <v/>
       </c>
       <c r="AL360">
-        <f>IF(AE360="","",HYPERLINK(AE360,"before"))</f>
+        <f>IF(AE360="","",HYPERLINK(IFERROR(LEFT(AE360,FIND(";",AE360)-1),AE360),"before"))</f>
         <v/>
       </c>
       <c r="AM360">
-        <f>IF(AF360="","",HYPERLINK(AF360,"after"))</f>
+        <f>IF(AF360="","",HYPERLINK(IFERROR(LEFT(AF360,FIND(";",AF360)-1),AF360),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13705,11 +13705,11 @@
         <v/>
       </c>
       <c r="AL361">
-        <f>IF(AE361="","",HYPERLINK(AE361,"before"))</f>
+        <f>IF(AE361="","",HYPERLINK(IFERROR(LEFT(AE361,FIND(";",AE361)-1),AE361),"before"))</f>
         <v/>
       </c>
       <c r="AM361">
-        <f>IF(AF361="","",HYPERLINK(AF361,"after"))</f>
+        <f>IF(AF361="","",HYPERLINK(IFERROR(LEFT(AF361,FIND(";",AF361)-1),AF361),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13741,11 +13741,11 @@
         <v/>
       </c>
       <c r="AL362">
-        <f>IF(AE362="","",HYPERLINK(AE362,"before"))</f>
+        <f>IF(AE362="","",HYPERLINK(IFERROR(LEFT(AE362,FIND(";",AE362)-1),AE362),"before"))</f>
         <v/>
       </c>
       <c r="AM362">
-        <f>IF(AF362="","",HYPERLINK(AF362,"after"))</f>
+        <f>IF(AF362="","",HYPERLINK(IFERROR(LEFT(AF362,FIND(";",AF362)-1),AF362),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13777,11 +13777,11 @@
         <v/>
       </c>
       <c r="AL363">
-        <f>IF(AE363="","",HYPERLINK(AE363,"before"))</f>
+        <f>IF(AE363="","",HYPERLINK(IFERROR(LEFT(AE363,FIND(";",AE363)-1),AE363),"before"))</f>
         <v/>
       </c>
       <c r="AM363">
-        <f>IF(AF363="","",HYPERLINK(AF363,"after"))</f>
+        <f>IF(AF363="","",HYPERLINK(IFERROR(LEFT(AF363,FIND(";",AF363)-1),AF363),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13813,11 +13813,11 @@
         <v/>
       </c>
       <c r="AL364">
-        <f>IF(AE364="","",HYPERLINK(AE364,"before"))</f>
+        <f>IF(AE364="","",HYPERLINK(IFERROR(LEFT(AE364,FIND(";",AE364)-1),AE364),"before"))</f>
         <v/>
       </c>
       <c r="AM364">
-        <f>IF(AF364="","",HYPERLINK(AF364,"after"))</f>
+        <f>IF(AF364="","",HYPERLINK(IFERROR(LEFT(AF364,FIND(";",AF364)-1),AF364),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13849,11 +13849,11 @@
         <v/>
       </c>
       <c r="AL365">
-        <f>IF(AE365="","",HYPERLINK(AE365,"before"))</f>
+        <f>IF(AE365="","",HYPERLINK(IFERROR(LEFT(AE365,FIND(";",AE365)-1),AE365),"before"))</f>
         <v/>
       </c>
       <c r="AM365">
-        <f>IF(AF365="","",HYPERLINK(AF365,"after"))</f>
+        <f>IF(AF365="","",HYPERLINK(IFERROR(LEFT(AF365,FIND(";",AF365)-1),AF365),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13885,11 +13885,11 @@
         <v/>
       </c>
       <c r="AL366">
-        <f>IF(AE366="","",HYPERLINK(AE366,"before"))</f>
+        <f>IF(AE366="","",HYPERLINK(IFERROR(LEFT(AE366,FIND(";",AE366)-1),AE366),"before"))</f>
         <v/>
       </c>
       <c r="AM366">
-        <f>IF(AF366="","",HYPERLINK(AF366,"after"))</f>
+        <f>IF(AF366="","",HYPERLINK(IFERROR(LEFT(AF366,FIND(";",AF366)-1),AF366),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13921,11 +13921,11 @@
         <v/>
       </c>
       <c r="AL367">
-        <f>IF(AE367="","",HYPERLINK(AE367,"before"))</f>
+        <f>IF(AE367="","",HYPERLINK(IFERROR(LEFT(AE367,FIND(";",AE367)-1),AE367),"before"))</f>
         <v/>
       </c>
       <c r="AM367">
-        <f>IF(AF367="","",HYPERLINK(AF367,"after"))</f>
+        <f>IF(AF367="","",HYPERLINK(IFERROR(LEFT(AF367,FIND(";",AF367)-1),AF367),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13957,11 +13957,11 @@
         <v/>
       </c>
       <c r="AL368">
-        <f>IF(AE368="","",HYPERLINK(AE368,"before"))</f>
+        <f>IF(AE368="","",HYPERLINK(IFERROR(LEFT(AE368,FIND(";",AE368)-1),AE368),"before"))</f>
         <v/>
       </c>
       <c r="AM368">
-        <f>IF(AF368="","",HYPERLINK(AF368,"after"))</f>
+        <f>IF(AF368="","",HYPERLINK(IFERROR(LEFT(AF368,FIND(";",AF368)-1),AF368),"after"))</f>
         <v/>
       </c>
     </row>
@@ -13993,11 +13993,11 @@
         <v/>
       </c>
       <c r="AL369">
-        <f>IF(AE369="","",HYPERLINK(AE369,"before"))</f>
+        <f>IF(AE369="","",HYPERLINK(IFERROR(LEFT(AE369,FIND(";",AE369)-1),AE369),"before"))</f>
         <v/>
       </c>
       <c r="AM369">
-        <f>IF(AF369="","",HYPERLINK(AF369,"after"))</f>
+        <f>IF(AF369="","",HYPERLINK(IFERROR(LEFT(AF369,FIND(";",AF369)-1),AF369),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14029,11 +14029,11 @@
         <v/>
       </c>
       <c r="AL370">
-        <f>IF(AE370="","",HYPERLINK(AE370,"before"))</f>
+        <f>IF(AE370="","",HYPERLINK(IFERROR(LEFT(AE370,FIND(";",AE370)-1),AE370),"before"))</f>
         <v/>
       </c>
       <c r="AM370">
-        <f>IF(AF370="","",HYPERLINK(AF370,"after"))</f>
+        <f>IF(AF370="","",HYPERLINK(IFERROR(LEFT(AF370,FIND(";",AF370)-1),AF370),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14065,11 +14065,11 @@
         <v/>
       </c>
       <c r="AL371">
-        <f>IF(AE371="","",HYPERLINK(AE371,"before"))</f>
+        <f>IF(AE371="","",HYPERLINK(IFERROR(LEFT(AE371,FIND(";",AE371)-1),AE371),"before"))</f>
         <v/>
       </c>
       <c r="AM371">
-        <f>IF(AF371="","",HYPERLINK(AF371,"after"))</f>
+        <f>IF(AF371="","",HYPERLINK(IFERROR(LEFT(AF371,FIND(";",AF371)-1),AF371),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14101,11 +14101,11 @@
         <v/>
       </c>
       <c r="AL372">
-        <f>IF(AE372="","",HYPERLINK(AE372,"before"))</f>
+        <f>IF(AE372="","",HYPERLINK(IFERROR(LEFT(AE372,FIND(";",AE372)-1),AE372),"before"))</f>
         <v/>
       </c>
       <c r="AM372">
-        <f>IF(AF372="","",HYPERLINK(AF372,"after"))</f>
+        <f>IF(AF372="","",HYPERLINK(IFERROR(LEFT(AF372,FIND(";",AF372)-1),AF372),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14137,11 +14137,11 @@
         <v/>
       </c>
       <c r="AL373">
-        <f>IF(AE373="","",HYPERLINK(AE373,"before"))</f>
+        <f>IF(AE373="","",HYPERLINK(IFERROR(LEFT(AE373,FIND(";",AE373)-1),AE373),"before"))</f>
         <v/>
       </c>
       <c r="AM373">
-        <f>IF(AF373="","",HYPERLINK(AF373,"after"))</f>
+        <f>IF(AF373="","",HYPERLINK(IFERROR(LEFT(AF373,FIND(";",AF373)-1),AF373),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14173,11 +14173,11 @@
         <v/>
       </c>
       <c r="AL374">
-        <f>IF(AE374="","",HYPERLINK(AE374,"before"))</f>
+        <f>IF(AE374="","",HYPERLINK(IFERROR(LEFT(AE374,FIND(";",AE374)-1),AE374),"before"))</f>
         <v/>
       </c>
       <c r="AM374">
-        <f>IF(AF374="","",HYPERLINK(AF374,"after"))</f>
+        <f>IF(AF374="","",HYPERLINK(IFERROR(LEFT(AF374,FIND(";",AF374)-1),AF374),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14209,11 +14209,11 @@
         <v/>
       </c>
       <c r="AL375">
-        <f>IF(AE375="","",HYPERLINK(AE375,"before"))</f>
+        <f>IF(AE375="","",HYPERLINK(IFERROR(LEFT(AE375,FIND(";",AE375)-1),AE375),"before"))</f>
         <v/>
       </c>
       <c r="AM375">
-        <f>IF(AF375="","",HYPERLINK(AF375,"after"))</f>
+        <f>IF(AF375="","",HYPERLINK(IFERROR(LEFT(AF375,FIND(";",AF375)-1),AF375),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14245,11 +14245,11 @@
         <v/>
       </c>
       <c r="AL376">
-        <f>IF(AE376="","",HYPERLINK(AE376,"before"))</f>
+        <f>IF(AE376="","",HYPERLINK(IFERROR(LEFT(AE376,FIND(";",AE376)-1),AE376),"before"))</f>
         <v/>
       </c>
       <c r="AM376">
-        <f>IF(AF376="","",HYPERLINK(AF376,"after"))</f>
+        <f>IF(AF376="","",HYPERLINK(IFERROR(LEFT(AF376,FIND(";",AF376)-1),AF376),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14281,11 +14281,11 @@
         <v/>
       </c>
       <c r="AL377">
-        <f>IF(AE377="","",HYPERLINK(AE377,"before"))</f>
+        <f>IF(AE377="","",HYPERLINK(IFERROR(LEFT(AE377,FIND(";",AE377)-1),AE377),"before"))</f>
         <v/>
       </c>
       <c r="AM377">
-        <f>IF(AF377="","",HYPERLINK(AF377,"after"))</f>
+        <f>IF(AF377="","",HYPERLINK(IFERROR(LEFT(AF377,FIND(";",AF377)-1),AF377),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14317,11 +14317,11 @@
         <v/>
       </c>
       <c r="AL378">
-        <f>IF(AE378="","",HYPERLINK(AE378,"before"))</f>
+        <f>IF(AE378="","",HYPERLINK(IFERROR(LEFT(AE378,FIND(";",AE378)-1),AE378),"before"))</f>
         <v/>
       </c>
       <c r="AM378">
-        <f>IF(AF378="","",HYPERLINK(AF378,"after"))</f>
+        <f>IF(AF378="","",HYPERLINK(IFERROR(LEFT(AF378,FIND(";",AF378)-1),AF378),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14353,11 +14353,11 @@
         <v/>
       </c>
       <c r="AL379">
-        <f>IF(AE379="","",HYPERLINK(AE379,"before"))</f>
+        <f>IF(AE379="","",HYPERLINK(IFERROR(LEFT(AE379,FIND(";",AE379)-1),AE379),"before"))</f>
         <v/>
       </c>
       <c r="AM379">
-        <f>IF(AF379="","",HYPERLINK(AF379,"after"))</f>
+        <f>IF(AF379="","",HYPERLINK(IFERROR(LEFT(AF379,FIND(";",AF379)-1),AF379),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14389,11 +14389,11 @@
         <v/>
       </c>
       <c r="AL380">
-        <f>IF(AE380="","",HYPERLINK(AE380,"before"))</f>
+        <f>IF(AE380="","",HYPERLINK(IFERROR(LEFT(AE380,FIND(";",AE380)-1),AE380),"before"))</f>
         <v/>
       </c>
       <c r="AM380">
-        <f>IF(AF380="","",HYPERLINK(AF380,"after"))</f>
+        <f>IF(AF380="","",HYPERLINK(IFERROR(LEFT(AF380,FIND(";",AF380)-1),AF380),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14425,11 +14425,11 @@
         <v/>
       </c>
       <c r="AL381">
-        <f>IF(AE381="","",HYPERLINK(AE381,"before"))</f>
+        <f>IF(AE381="","",HYPERLINK(IFERROR(LEFT(AE381,FIND(";",AE381)-1),AE381),"before"))</f>
         <v/>
       </c>
       <c r="AM381">
-        <f>IF(AF381="","",HYPERLINK(AF381,"after"))</f>
+        <f>IF(AF381="","",HYPERLINK(IFERROR(LEFT(AF381,FIND(";",AF381)-1),AF381),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14461,11 +14461,11 @@
         <v/>
       </c>
       <c r="AL382">
-        <f>IF(AE382="","",HYPERLINK(AE382,"before"))</f>
+        <f>IF(AE382="","",HYPERLINK(IFERROR(LEFT(AE382,FIND(";",AE382)-1),AE382),"before"))</f>
         <v/>
       </c>
       <c r="AM382">
-        <f>IF(AF382="","",HYPERLINK(AF382,"after"))</f>
+        <f>IF(AF382="","",HYPERLINK(IFERROR(LEFT(AF382,FIND(";",AF382)-1),AF382),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14497,11 +14497,11 @@
         <v/>
       </c>
       <c r="AL383">
-        <f>IF(AE383="","",HYPERLINK(AE383,"before"))</f>
+        <f>IF(AE383="","",HYPERLINK(IFERROR(LEFT(AE383,FIND(";",AE383)-1),AE383),"before"))</f>
         <v/>
       </c>
       <c r="AM383">
-        <f>IF(AF383="","",HYPERLINK(AF383,"after"))</f>
+        <f>IF(AF383="","",HYPERLINK(IFERROR(LEFT(AF383,FIND(";",AF383)-1),AF383),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14533,11 +14533,11 @@
         <v/>
       </c>
       <c r="AL384">
-        <f>IF(AE384="","",HYPERLINK(AE384,"before"))</f>
+        <f>IF(AE384="","",HYPERLINK(IFERROR(LEFT(AE384,FIND(";",AE384)-1),AE384),"before"))</f>
         <v/>
       </c>
       <c r="AM384">
-        <f>IF(AF384="","",HYPERLINK(AF384,"after"))</f>
+        <f>IF(AF384="","",HYPERLINK(IFERROR(LEFT(AF384,FIND(";",AF384)-1),AF384),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14569,11 +14569,11 @@
         <v/>
       </c>
       <c r="AL385">
-        <f>IF(AE385="","",HYPERLINK(AE385,"before"))</f>
+        <f>IF(AE385="","",HYPERLINK(IFERROR(LEFT(AE385,FIND(";",AE385)-1),AE385),"before"))</f>
         <v/>
       </c>
       <c r="AM385">
-        <f>IF(AF385="","",HYPERLINK(AF385,"after"))</f>
+        <f>IF(AF385="","",HYPERLINK(IFERROR(LEFT(AF385,FIND(";",AF385)-1),AF385),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14605,11 +14605,11 @@
         <v/>
       </c>
       <c r="AL386">
-        <f>IF(AE386="","",HYPERLINK(AE386,"before"))</f>
+        <f>IF(AE386="","",HYPERLINK(IFERROR(LEFT(AE386,FIND(";",AE386)-1),AE386),"before"))</f>
         <v/>
       </c>
       <c r="AM386">
-        <f>IF(AF386="","",HYPERLINK(AF386,"after"))</f>
+        <f>IF(AF386="","",HYPERLINK(IFERROR(LEFT(AF386,FIND(";",AF386)-1),AF386),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14641,11 +14641,11 @@
         <v/>
       </c>
       <c r="AL387">
-        <f>IF(AE387="","",HYPERLINK(AE387,"before"))</f>
+        <f>IF(AE387="","",HYPERLINK(IFERROR(LEFT(AE387,FIND(";",AE387)-1),AE387),"before"))</f>
         <v/>
       </c>
       <c r="AM387">
-        <f>IF(AF387="","",HYPERLINK(AF387,"after"))</f>
+        <f>IF(AF387="","",HYPERLINK(IFERROR(LEFT(AF387,FIND(";",AF387)-1),AF387),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14677,11 +14677,11 @@
         <v/>
       </c>
       <c r="AL388">
-        <f>IF(AE388="","",HYPERLINK(AE388,"before"))</f>
+        <f>IF(AE388="","",HYPERLINK(IFERROR(LEFT(AE388,FIND(";",AE388)-1),AE388),"before"))</f>
         <v/>
       </c>
       <c r="AM388">
-        <f>IF(AF388="","",HYPERLINK(AF388,"after"))</f>
+        <f>IF(AF388="","",HYPERLINK(IFERROR(LEFT(AF388,FIND(";",AF388)-1),AF388),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14713,11 +14713,11 @@
         <v/>
       </c>
       <c r="AL389">
-        <f>IF(AE389="","",HYPERLINK(AE389,"before"))</f>
+        <f>IF(AE389="","",HYPERLINK(IFERROR(LEFT(AE389,FIND(";",AE389)-1),AE389),"before"))</f>
         <v/>
       </c>
       <c r="AM389">
-        <f>IF(AF389="","",HYPERLINK(AF389,"after"))</f>
+        <f>IF(AF389="","",HYPERLINK(IFERROR(LEFT(AF389,FIND(";",AF389)-1),AF389),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14749,11 +14749,11 @@
         <v/>
       </c>
       <c r="AL390">
-        <f>IF(AE390="","",HYPERLINK(AE390,"before"))</f>
+        <f>IF(AE390="","",HYPERLINK(IFERROR(LEFT(AE390,FIND(";",AE390)-1),AE390),"before"))</f>
         <v/>
       </c>
       <c r="AM390">
-        <f>IF(AF390="","",HYPERLINK(AF390,"after"))</f>
+        <f>IF(AF390="","",HYPERLINK(IFERROR(LEFT(AF390,FIND(";",AF390)-1),AF390),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14785,11 +14785,11 @@
         <v/>
       </c>
       <c r="AL391">
-        <f>IF(AE391="","",HYPERLINK(AE391,"before"))</f>
+        <f>IF(AE391="","",HYPERLINK(IFERROR(LEFT(AE391,FIND(";",AE391)-1),AE391),"before"))</f>
         <v/>
       </c>
       <c r="AM391">
-        <f>IF(AF391="","",HYPERLINK(AF391,"after"))</f>
+        <f>IF(AF391="","",HYPERLINK(IFERROR(LEFT(AF391,FIND(";",AF391)-1),AF391),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14821,11 +14821,11 @@
         <v/>
       </c>
       <c r="AL392">
-        <f>IF(AE392="","",HYPERLINK(AE392,"before"))</f>
+        <f>IF(AE392="","",HYPERLINK(IFERROR(LEFT(AE392,FIND(";",AE392)-1),AE392),"before"))</f>
         <v/>
       </c>
       <c r="AM392">
-        <f>IF(AF392="","",HYPERLINK(AF392,"after"))</f>
+        <f>IF(AF392="","",HYPERLINK(IFERROR(LEFT(AF392,FIND(";",AF392)-1),AF392),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14857,11 +14857,11 @@
         <v/>
       </c>
       <c r="AL393">
-        <f>IF(AE393="","",HYPERLINK(AE393,"before"))</f>
+        <f>IF(AE393="","",HYPERLINK(IFERROR(LEFT(AE393,FIND(";",AE393)-1),AE393),"before"))</f>
         <v/>
       </c>
       <c r="AM393">
-        <f>IF(AF393="","",HYPERLINK(AF393,"after"))</f>
+        <f>IF(AF393="","",HYPERLINK(IFERROR(LEFT(AF393,FIND(";",AF393)-1),AF393),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14893,11 +14893,11 @@
         <v/>
       </c>
       <c r="AL394">
-        <f>IF(AE394="","",HYPERLINK(AE394,"before"))</f>
+        <f>IF(AE394="","",HYPERLINK(IFERROR(LEFT(AE394,FIND(";",AE394)-1),AE394),"before"))</f>
         <v/>
       </c>
       <c r="AM394">
-        <f>IF(AF394="","",HYPERLINK(AF394,"after"))</f>
+        <f>IF(AF394="","",HYPERLINK(IFERROR(LEFT(AF394,FIND(";",AF394)-1),AF394),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14929,11 +14929,11 @@
         <v/>
       </c>
       <c r="AL395">
-        <f>IF(AE395="","",HYPERLINK(AE395,"before"))</f>
+        <f>IF(AE395="","",HYPERLINK(IFERROR(LEFT(AE395,FIND(";",AE395)-1),AE395),"before"))</f>
         <v/>
       </c>
       <c r="AM395">
-        <f>IF(AF395="","",HYPERLINK(AF395,"after"))</f>
+        <f>IF(AF395="","",HYPERLINK(IFERROR(LEFT(AF395,FIND(";",AF395)-1),AF395),"after"))</f>
         <v/>
       </c>
     </row>
@@ -14965,11 +14965,11 @@
         <v/>
       </c>
       <c r="AL396">
-        <f>IF(AE396="","",HYPERLINK(AE396,"before"))</f>
+        <f>IF(AE396="","",HYPERLINK(IFERROR(LEFT(AE396,FIND(";",AE396)-1),AE396),"before"))</f>
         <v/>
       </c>
       <c r="AM396">
-        <f>IF(AF396="","",HYPERLINK(AF396,"after"))</f>
+        <f>IF(AF396="","",HYPERLINK(IFERROR(LEFT(AF396,FIND(";",AF396)-1),AF396),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15001,11 +15001,11 @@
         <v/>
       </c>
       <c r="AL397">
-        <f>IF(AE397="","",HYPERLINK(AE397,"before"))</f>
+        <f>IF(AE397="","",HYPERLINK(IFERROR(LEFT(AE397,FIND(";",AE397)-1),AE397),"before"))</f>
         <v/>
       </c>
       <c r="AM397">
-        <f>IF(AF397="","",HYPERLINK(AF397,"after"))</f>
+        <f>IF(AF397="","",HYPERLINK(IFERROR(LEFT(AF397,FIND(";",AF397)-1),AF397),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15037,11 +15037,11 @@
         <v/>
       </c>
       <c r="AL398">
-        <f>IF(AE398="","",HYPERLINK(AE398,"before"))</f>
+        <f>IF(AE398="","",HYPERLINK(IFERROR(LEFT(AE398,FIND(";",AE398)-1),AE398),"before"))</f>
         <v/>
       </c>
       <c r="AM398">
-        <f>IF(AF398="","",HYPERLINK(AF398,"after"))</f>
+        <f>IF(AF398="","",HYPERLINK(IFERROR(LEFT(AF398,FIND(";",AF398)-1),AF398),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15073,11 +15073,11 @@
         <v/>
       </c>
       <c r="AL399">
-        <f>IF(AE399="","",HYPERLINK(AE399,"before"))</f>
+        <f>IF(AE399="","",HYPERLINK(IFERROR(LEFT(AE399,FIND(";",AE399)-1),AE399),"before"))</f>
         <v/>
       </c>
       <c r="AM399">
-        <f>IF(AF399="","",HYPERLINK(AF399,"after"))</f>
+        <f>IF(AF399="","",HYPERLINK(IFERROR(LEFT(AF399,FIND(";",AF399)-1),AF399),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15109,11 +15109,11 @@
         <v/>
       </c>
       <c r="AL400">
-        <f>IF(AE400="","",HYPERLINK(AE400,"before"))</f>
+        <f>IF(AE400="","",HYPERLINK(IFERROR(LEFT(AE400,FIND(";",AE400)-1),AE400),"before"))</f>
         <v/>
       </c>
       <c r="AM400">
-        <f>IF(AF400="","",HYPERLINK(AF400,"after"))</f>
+        <f>IF(AF400="","",HYPERLINK(IFERROR(LEFT(AF400,FIND(";",AF400)-1),AF400),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15145,11 +15145,11 @@
         <v/>
       </c>
       <c r="AL401">
-        <f>IF(AE401="","",HYPERLINK(AE401,"before"))</f>
+        <f>IF(AE401="","",HYPERLINK(IFERROR(LEFT(AE401,FIND(";",AE401)-1),AE401),"before"))</f>
         <v/>
       </c>
       <c r="AM401">
-        <f>IF(AF401="","",HYPERLINK(AF401,"after"))</f>
+        <f>IF(AF401="","",HYPERLINK(IFERROR(LEFT(AF401,FIND(";",AF401)-1),AF401),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15181,11 +15181,11 @@
         <v/>
       </c>
       <c r="AL402">
-        <f>IF(AE402="","",HYPERLINK(AE402,"before"))</f>
+        <f>IF(AE402="","",HYPERLINK(IFERROR(LEFT(AE402,FIND(";",AE402)-1),AE402),"before"))</f>
         <v/>
       </c>
       <c r="AM402">
-        <f>IF(AF402="","",HYPERLINK(AF402,"after"))</f>
+        <f>IF(AF402="","",HYPERLINK(IFERROR(LEFT(AF402,FIND(";",AF402)-1),AF402),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15217,11 +15217,11 @@
         <v/>
       </c>
       <c r="AL403">
-        <f>IF(AE403="","",HYPERLINK(AE403,"before"))</f>
+        <f>IF(AE403="","",HYPERLINK(IFERROR(LEFT(AE403,FIND(";",AE403)-1),AE403),"before"))</f>
         <v/>
       </c>
       <c r="AM403">
-        <f>IF(AF403="","",HYPERLINK(AF403,"after"))</f>
+        <f>IF(AF403="","",HYPERLINK(IFERROR(LEFT(AF403,FIND(";",AF403)-1),AF403),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15253,11 +15253,11 @@
         <v/>
       </c>
       <c r="AL404">
-        <f>IF(AE404="","",HYPERLINK(AE404,"before"))</f>
+        <f>IF(AE404="","",HYPERLINK(IFERROR(LEFT(AE404,FIND(";",AE404)-1),AE404),"before"))</f>
         <v/>
       </c>
       <c r="AM404">
-        <f>IF(AF404="","",HYPERLINK(AF404,"after"))</f>
+        <f>IF(AF404="","",HYPERLINK(IFERROR(LEFT(AF404,FIND(";",AF404)-1),AF404),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15289,11 +15289,11 @@
         <v/>
       </c>
       <c r="AL405">
-        <f>IF(AE405="","",HYPERLINK(AE405,"before"))</f>
+        <f>IF(AE405="","",HYPERLINK(IFERROR(LEFT(AE405,FIND(";",AE405)-1),AE405),"before"))</f>
         <v/>
       </c>
       <c r="AM405">
-        <f>IF(AF405="","",HYPERLINK(AF405,"after"))</f>
+        <f>IF(AF405="","",HYPERLINK(IFERROR(LEFT(AF405,FIND(";",AF405)-1),AF405),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15325,11 +15325,11 @@
         <v/>
       </c>
       <c r="AL406">
-        <f>IF(AE406="","",HYPERLINK(AE406,"before"))</f>
+        <f>IF(AE406="","",HYPERLINK(IFERROR(LEFT(AE406,FIND(";",AE406)-1),AE406),"before"))</f>
         <v/>
       </c>
       <c r="AM406">
-        <f>IF(AF406="","",HYPERLINK(AF406,"after"))</f>
+        <f>IF(AF406="","",HYPERLINK(IFERROR(LEFT(AF406,FIND(";",AF406)-1),AF406),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15361,11 +15361,11 @@
         <v/>
       </c>
       <c r="AL407">
-        <f>IF(AE407="","",HYPERLINK(AE407,"before"))</f>
+        <f>IF(AE407="","",HYPERLINK(IFERROR(LEFT(AE407,FIND(";",AE407)-1),AE407),"before"))</f>
         <v/>
       </c>
       <c r="AM407">
-        <f>IF(AF407="","",HYPERLINK(AF407,"after"))</f>
+        <f>IF(AF407="","",HYPERLINK(IFERROR(LEFT(AF407,FIND(";",AF407)-1),AF407),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15397,11 +15397,11 @@
         <v/>
       </c>
       <c r="AL408">
-        <f>IF(AE408="","",HYPERLINK(AE408,"before"))</f>
+        <f>IF(AE408="","",HYPERLINK(IFERROR(LEFT(AE408,FIND(";",AE408)-1),AE408),"before"))</f>
         <v/>
       </c>
       <c r="AM408">
-        <f>IF(AF408="","",HYPERLINK(AF408,"after"))</f>
+        <f>IF(AF408="","",HYPERLINK(IFERROR(LEFT(AF408,FIND(";",AF408)-1),AF408),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15433,11 +15433,11 @@
         <v/>
       </c>
       <c r="AL409">
-        <f>IF(AE409="","",HYPERLINK(AE409,"before"))</f>
+        <f>IF(AE409="","",HYPERLINK(IFERROR(LEFT(AE409,FIND(";",AE409)-1),AE409),"before"))</f>
         <v/>
       </c>
       <c r="AM409">
-        <f>IF(AF409="","",HYPERLINK(AF409,"after"))</f>
+        <f>IF(AF409="","",HYPERLINK(IFERROR(LEFT(AF409,FIND(";",AF409)-1),AF409),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15469,11 +15469,11 @@
         <v/>
       </c>
       <c r="AL410">
-        <f>IF(AE410="","",HYPERLINK(AE410,"before"))</f>
+        <f>IF(AE410="","",HYPERLINK(IFERROR(LEFT(AE410,FIND(";",AE410)-1),AE410),"before"))</f>
         <v/>
       </c>
       <c r="AM410">
-        <f>IF(AF410="","",HYPERLINK(AF410,"after"))</f>
+        <f>IF(AF410="","",HYPERLINK(IFERROR(LEFT(AF410,FIND(";",AF410)-1),AF410),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15505,11 +15505,11 @@
         <v/>
       </c>
       <c r="AL411">
-        <f>IF(AE411="","",HYPERLINK(AE411,"before"))</f>
+        <f>IF(AE411="","",HYPERLINK(IFERROR(LEFT(AE411,FIND(";",AE411)-1),AE411),"before"))</f>
         <v/>
       </c>
       <c r="AM411">
-        <f>IF(AF411="","",HYPERLINK(AF411,"after"))</f>
+        <f>IF(AF411="","",HYPERLINK(IFERROR(LEFT(AF411,FIND(";",AF411)-1),AF411),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15541,11 +15541,11 @@
         <v/>
       </c>
       <c r="AL412">
-        <f>IF(AE412="","",HYPERLINK(AE412,"before"))</f>
+        <f>IF(AE412="","",HYPERLINK(IFERROR(LEFT(AE412,FIND(";",AE412)-1),AE412),"before"))</f>
         <v/>
       </c>
       <c r="AM412">
-        <f>IF(AF412="","",HYPERLINK(AF412,"after"))</f>
+        <f>IF(AF412="","",HYPERLINK(IFERROR(LEFT(AF412,FIND(";",AF412)-1),AF412),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15577,11 +15577,11 @@
         <v/>
       </c>
       <c r="AL413">
-        <f>IF(AE413="","",HYPERLINK(AE413,"before"))</f>
+        <f>IF(AE413="","",HYPERLINK(IFERROR(LEFT(AE413,FIND(";",AE413)-1),AE413),"before"))</f>
         <v/>
       </c>
       <c r="AM413">
-        <f>IF(AF413="","",HYPERLINK(AF413,"after"))</f>
+        <f>IF(AF413="","",HYPERLINK(IFERROR(LEFT(AF413,FIND(";",AF413)-1),AF413),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15613,11 +15613,11 @@
         <v/>
       </c>
       <c r="AL414">
-        <f>IF(AE414="","",HYPERLINK(AE414,"before"))</f>
+        <f>IF(AE414="","",HYPERLINK(IFERROR(LEFT(AE414,FIND(";",AE414)-1),AE414),"before"))</f>
         <v/>
       </c>
       <c r="AM414">
-        <f>IF(AF414="","",HYPERLINK(AF414,"after"))</f>
+        <f>IF(AF414="","",HYPERLINK(IFERROR(LEFT(AF414,FIND(";",AF414)-1),AF414),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15649,11 +15649,11 @@
         <v/>
       </c>
       <c r="AL415">
-        <f>IF(AE415="","",HYPERLINK(AE415,"before"))</f>
+        <f>IF(AE415="","",HYPERLINK(IFERROR(LEFT(AE415,FIND(";",AE415)-1),AE415),"before"))</f>
         <v/>
       </c>
       <c r="AM415">
-        <f>IF(AF415="","",HYPERLINK(AF415,"after"))</f>
+        <f>IF(AF415="","",HYPERLINK(IFERROR(LEFT(AF415,FIND(";",AF415)-1),AF415),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15685,11 +15685,11 @@
         <v/>
       </c>
       <c r="AL416">
-        <f>IF(AE416="","",HYPERLINK(AE416,"before"))</f>
+        <f>IF(AE416="","",HYPERLINK(IFERROR(LEFT(AE416,FIND(";",AE416)-1),AE416),"before"))</f>
         <v/>
       </c>
       <c r="AM416">
-        <f>IF(AF416="","",HYPERLINK(AF416,"after"))</f>
+        <f>IF(AF416="","",HYPERLINK(IFERROR(LEFT(AF416,FIND(";",AF416)-1),AF416),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15721,11 +15721,11 @@
         <v/>
       </c>
       <c r="AL417">
-        <f>IF(AE417="","",HYPERLINK(AE417,"before"))</f>
+        <f>IF(AE417="","",HYPERLINK(IFERROR(LEFT(AE417,FIND(";",AE417)-1),AE417),"before"))</f>
         <v/>
       </c>
       <c r="AM417">
-        <f>IF(AF417="","",HYPERLINK(AF417,"after"))</f>
+        <f>IF(AF417="","",HYPERLINK(IFERROR(LEFT(AF417,FIND(";",AF417)-1),AF417),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15757,11 +15757,11 @@
         <v/>
       </c>
       <c r="AL418">
-        <f>IF(AE418="","",HYPERLINK(AE418,"before"))</f>
+        <f>IF(AE418="","",HYPERLINK(IFERROR(LEFT(AE418,FIND(";",AE418)-1),AE418),"before"))</f>
         <v/>
       </c>
       <c r="AM418">
-        <f>IF(AF418="","",HYPERLINK(AF418,"after"))</f>
+        <f>IF(AF418="","",HYPERLINK(IFERROR(LEFT(AF418,FIND(";",AF418)-1),AF418),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15793,11 +15793,11 @@
         <v/>
       </c>
       <c r="AL419">
-        <f>IF(AE419="","",HYPERLINK(AE419,"before"))</f>
+        <f>IF(AE419="","",HYPERLINK(IFERROR(LEFT(AE419,FIND(";",AE419)-1),AE419),"before"))</f>
         <v/>
       </c>
       <c r="AM419">
-        <f>IF(AF419="","",HYPERLINK(AF419,"after"))</f>
+        <f>IF(AF419="","",HYPERLINK(IFERROR(LEFT(AF419,FIND(";",AF419)-1),AF419),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15829,11 +15829,11 @@
         <v/>
       </c>
       <c r="AL420">
-        <f>IF(AE420="","",HYPERLINK(AE420,"before"))</f>
+        <f>IF(AE420="","",HYPERLINK(IFERROR(LEFT(AE420,FIND(";",AE420)-1),AE420),"before"))</f>
         <v/>
       </c>
       <c r="AM420">
-        <f>IF(AF420="","",HYPERLINK(AF420,"after"))</f>
+        <f>IF(AF420="","",HYPERLINK(IFERROR(LEFT(AF420,FIND(";",AF420)-1),AF420),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15865,11 +15865,11 @@
         <v/>
       </c>
       <c r="AL421">
-        <f>IF(AE421="","",HYPERLINK(AE421,"before"))</f>
+        <f>IF(AE421="","",HYPERLINK(IFERROR(LEFT(AE421,FIND(";",AE421)-1),AE421),"before"))</f>
         <v/>
       </c>
       <c r="AM421">
-        <f>IF(AF421="","",HYPERLINK(AF421,"after"))</f>
+        <f>IF(AF421="","",HYPERLINK(IFERROR(LEFT(AF421,FIND(";",AF421)-1),AF421),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15901,11 +15901,11 @@
         <v/>
       </c>
       <c r="AL422">
-        <f>IF(AE422="","",HYPERLINK(AE422,"before"))</f>
+        <f>IF(AE422="","",HYPERLINK(IFERROR(LEFT(AE422,FIND(";",AE422)-1),AE422),"before"))</f>
         <v/>
       </c>
       <c r="AM422">
-        <f>IF(AF422="","",HYPERLINK(AF422,"after"))</f>
+        <f>IF(AF422="","",HYPERLINK(IFERROR(LEFT(AF422,FIND(";",AF422)-1),AF422),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15937,11 +15937,11 @@
         <v/>
       </c>
       <c r="AL423">
-        <f>IF(AE423="","",HYPERLINK(AE423,"before"))</f>
+        <f>IF(AE423="","",HYPERLINK(IFERROR(LEFT(AE423,FIND(";",AE423)-1),AE423),"before"))</f>
         <v/>
       </c>
       <c r="AM423">
-        <f>IF(AF423="","",HYPERLINK(AF423,"after"))</f>
+        <f>IF(AF423="","",HYPERLINK(IFERROR(LEFT(AF423,FIND(";",AF423)-1),AF423),"after"))</f>
         <v/>
       </c>
     </row>
@@ -15973,11 +15973,11 @@
         <v/>
       </c>
       <c r="AL424">
-        <f>IF(AE424="","",HYPERLINK(AE424,"before"))</f>
+        <f>IF(AE424="","",HYPERLINK(IFERROR(LEFT(AE424,FIND(";",AE424)-1),AE424),"before"))</f>
         <v/>
       </c>
       <c r="AM424">
-        <f>IF(AF424="","",HYPERLINK(AF424,"after"))</f>
+        <f>IF(AF424="","",HYPERLINK(IFERROR(LEFT(AF424,FIND(";",AF424)-1),AF424),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16009,11 +16009,11 @@
         <v/>
       </c>
       <c r="AL425">
-        <f>IF(AE425="","",HYPERLINK(AE425,"before"))</f>
+        <f>IF(AE425="","",HYPERLINK(IFERROR(LEFT(AE425,FIND(";",AE425)-1),AE425),"before"))</f>
         <v/>
       </c>
       <c r="AM425">
-        <f>IF(AF425="","",HYPERLINK(AF425,"after"))</f>
+        <f>IF(AF425="","",HYPERLINK(IFERROR(LEFT(AF425,FIND(";",AF425)-1),AF425),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16045,11 +16045,11 @@
         <v/>
       </c>
       <c r="AL426">
-        <f>IF(AE426="","",HYPERLINK(AE426,"before"))</f>
+        <f>IF(AE426="","",HYPERLINK(IFERROR(LEFT(AE426,FIND(";",AE426)-1),AE426),"before"))</f>
         <v/>
       </c>
       <c r="AM426">
-        <f>IF(AF426="","",HYPERLINK(AF426,"after"))</f>
+        <f>IF(AF426="","",HYPERLINK(IFERROR(LEFT(AF426,FIND(";",AF426)-1),AF426),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16081,11 +16081,11 @@
         <v/>
       </c>
       <c r="AL427">
-        <f>IF(AE427="","",HYPERLINK(AE427,"before"))</f>
+        <f>IF(AE427="","",HYPERLINK(IFERROR(LEFT(AE427,FIND(";",AE427)-1),AE427),"before"))</f>
         <v/>
       </c>
       <c r="AM427">
-        <f>IF(AF427="","",HYPERLINK(AF427,"after"))</f>
+        <f>IF(AF427="","",HYPERLINK(IFERROR(LEFT(AF427,FIND(";",AF427)-1),AF427),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16117,11 +16117,11 @@
         <v/>
       </c>
       <c r="AL428">
-        <f>IF(AE428="","",HYPERLINK(AE428,"before"))</f>
+        <f>IF(AE428="","",HYPERLINK(IFERROR(LEFT(AE428,FIND(";",AE428)-1),AE428),"before"))</f>
         <v/>
       </c>
       <c r="AM428">
-        <f>IF(AF428="","",HYPERLINK(AF428,"after"))</f>
+        <f>IF(AF428="","",HYPERLINK(IFERROR(LEFT(AF428,FIND(";",AF428)-1),AF428),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16153,11 +16153,11 @@
         <v/>
       </c>
       <c r="AL429">
-        <f>IF(AE429="","",HYPERLINK(AE429,"before"))</f>
+        <f>IF(AE429="","",HYPERLINK(IFERROR(LEFT(AE429,FIND(";",AE429)-1),AE429),"before"))</f>
         <v/>
       </c>
       <c r="AM429">
-        <f>IF(AF429="","",HYPERLINK(AF429,"after"))</f>
+        <f>IF(AF429="","",HYPERLINK(IFERROR(LEFT(AF429,FIND(";",AF429)-1),AF429),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16189,11 +16189,11 @@
         <v/>
       </c>
       <c r="AL430">
-        <f>IF(AE430="","",HYPERLINK(AE430,"before"))</f>
+        <f>IF(AE430="","",HYPERLINK(IFERROR(LEFT(AE430,FIND(";",AE430)-1),AE430),"before"))</f>
         <v/>
       </c>
       <c r="AM430">
-        <f>IF(AF430="","",HYPERLINK(AF430,"after"))</f>
+        <f>IF(AF430="","",HYPERLINK(IFERROR(LEFT(AF430,FIND(";",AF430)-1),AF430),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16225,11 +16225,11 @@
         <v/>
       </c>
       <c r="AL431">
-        <f>IF(AE431="","",HYPERLINK(AE431,"before"))</f>
+        <f>IF(AE431="","",HYPERLINK(IFERROR(LEFT(AE431,FIND(";",AE431)-1),AE431),"before"))</f>
         <v/>
       </c>
       <c r="AM431">
-        <f>IF(AF431="","",HYPERLINK(AF431,"after"))</f>
+        <f>IF(AF431="","",HYPERLINK(IFERROR(LEFT(AF431,FIND(";",AF431)-1),AF431),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16261,11 +16261,11 @@
         <v/>
       </c>
       <c r="AL432">
-        <f>IF(AE432="","",HYPERLINK(AE432,"before"))</f>
+        <f>IF(AE432="","",HYPERLINK(IFERROR(LEFT(AE432,FIND(";",AE432)-1),AE432),"before"))</f>
         <v/>
       </c>
       <c r="AM432">
-        <f>IF(AF432="","",HYPERLINK(AF432,"after"))</f>
+        <f>IF(AF432="","",HYPERLINK(IFERROR(LEFT(AF432,FIND(";",AF432)-1),AF432),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16297,11 +16297,11 @@
         <v/>
       </c>
       <c r="AL433">
-        <f>IF(AE433="","",HYPERLINK(AE433,"before"))</f>
+        <f>IF(AE433="","",HYPERLINK(IFERROR(LEFT(AE433,FIND(";",AE433)-1),AE433),"before"))</f>
         <v/>
       </c>
       <c r="AM433">
-        <f>IF(AF433="","",HYPERLINK(AF433,"after"))</f>
+        <f>IF(AF433="","",HYPERLINK(IFERROR(LEFT(AF433,FIND(";",AF433)-1),AF433),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16333,11 +16333,11 @@
         <v/>
       </c>
       <c r="AL434">
-        <f>IF(AE434="","",HYPERLINK(AE434,"before"))</f>
+        <f>IF(AE434="","",HYPERLINK(IFERROR(LEFT(AE434,FIND(";",AE434)-1),AE434),"before"))</f>
         <v/>
       </c>
       <c r="AM434">
-        <f>IF(AF434="","",HYPERLINK(AF434,"after"))</f>
+        <f>IF(AF434="","",HYPERLINK(IFERROR(LEFT(AF434,FIND(";",AF434)-1),AF434),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16369,11 +16369,11 @@
         <v/>
       </c>
       <c r="AL435">
-        <f>IF(AE435="","",HYPERLINK(AE435,"before"))</f>
+        <f>IF(AE435="","",HYPERLINK(IFERROR(LEFT(AE435,FIND(";",AE435)-1),AE435),"before"))</f>
         <v/>
       </c>
       <c r="AM435">
-        <f>IF(AF435="","",HYPERLINK(AF435,"after"))</f>
+        <f>IF(AF435="","",HYPERLINK(IFERROR(LEFT(AF435,FIND(";",AF435)-1),AF435),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16405,11 +16405,11 @@
         <v/>
       </c>
       <c r="AL436">
-        <f>IF(AE436="","",HYPERLINK(AE436,"before"))</f>
+        <f>IF(AE436="","",HYPERLINK(IFERROR(LEFT(AE436,FIND(";",AE436)-1),AE436),"before"))</f>
         <v/>
       </c>
       <c r="AM436">
-        <f>IF(AF436="","",HYPERLINK(AF436,"after"))</f>
+        <f>IF(AF436="","",HYPERLINK(IFERROR(LEFT(AF436,FIND(";",AF436)-1),AF436),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16441,11 +16441,11 @@
         <v/>
       </c>
       <c r="AL437">
-        <f>IF(AE437="","",HYPERLINK(AE437,"before"))</f>
+        <f>IF(AE437="","",HYPERLINK(IFERROR(LEFT(AE437,FIND(";",AE437)-1),AE437),"before"))</f>
         <v/>
       </c>
       <c r="AM437">
-        <f>IF(AF437="","",HYPERLINK(AF437,"after"))</f>
+        <f>IF(AF437="","",HYPERLINK(IFERROR(LEFT(AF437,FIND(";",AF437)-1),AF437),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16477,11 +16477,11 @@
         <v/>
       </c>
       <c r="AL438">
-        <f>IF(AE438="","",HYPERLINK(AE438,"before"))</f>
+        <f>IF(AE438="","",HYPERLINK(IFERROR(LEFT(AE438,FIND(";",AE438)-1),AE438),"before"))</f>
         <v/>
       </c>
       <c r="AM438">
-        <f>IF(AF438="","",HYPERLINK(AF438,"after"))</f>
+        <f>IF(AF438="","",HYPERLINK(IFERROR(LEFT(AF438,FIND(";",AF438)-1),AF438),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16513,11 +16513,11 @@
         <v/>
       </c>
       <c r="AL439">
-        <f>IF(AE439="","",HYPERLINK(AE439,"before"))</f>
+        <f>IF(AE439="","",HYPERLINK(IFERROR(LEFT(AE439,FIND(";",AE439)-1),AE439),"before"))</f>
         <v/>
       </c>
       <c r="AM439">
-        <f>IF(AF439="","",HYPERLINK(AF439,"after"))</f>
+        <f>IF(AF439="","",HYPERLINK(IFERROR(LEFT(AF439,FIND(";",AF439)-1),AF439),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16549,11 +16549,11 @@
         <v/>
       </c>
       <c r="AL440">
-        <f>IF(AE440="","",HYPERLINK(AE440,"before"))</f>
+        <f>IF(AE440="","",HYPERLINK(IFERROR(LEFT(AE440,FIND(";",AE440)-1),AE440),"before"))</f>
         <v/>
       </c>
       <c r="AM440">
-        <f>IF(AF440="","",HYPERLINK(AF440,"after"))</f>
+        <f>IF(AF440="","",HYPERLINK(IFERROR(LEFT(AF440,FIND(";",AF440)-1),AF440),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16585,11 +16585,11 @@
         <v/>
       </c>
       <c r="AL441">
-        <f>IF(AE441="","",HYPERLINK(AE441,"before"))</f>
+        <f>IF(AE441="","",HYPERLINK(IFERROR(LEFT(AE441,FIND(";",AE441)-1),AE441),"before"))</f>
         <v/>
       </c>
       <c r="AM441">
-        <f>IF(AF441="","",HYPERLINK(AF441,"after"))</f>
+        <f>IF(AF441="","",HYPERLINK(IFERROR(LEFT(AF441,FIND(";",AF441)-1),AF441),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16621,11 +16621,11 @@
         <v/>
       </c>
       <c r="AL442">
-        <f>IF(AE442="","",HYPERLINK(AE442,"before"))</f>
+        <f>IF(AE442="","",HYPERLINK(IFERROR(LEFT(AE442,FIND(";",AE442)-1),AE442),"before"))</f>
         <v/>
       </c>
       <c r="AM442">
-        <f>IF(AF442="","",HYPERLINK(AF442,"after"))</f>
+        <f>IF(AF442="","",HYPERLINK(IFERROR(LEFT(AF442,FIND(";",AF442)-1),AF442),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16657,11 +16657,11 @@
         <v/>
       </c>
       <c r="AL443">
-        <f>IF(AE443="","",HYPERLINK(AE443,"before"))</f>
+        <f>IF(AE443="","",HYPERLINK(IFERROR(LEFT(AE443,FIND(";",AE443)-1),AE443),"before"))</f>
         <v/>
       </c>
       <c r="AM443">
-        <f>IF(AF443="","",HYPERLINK(AF443,"after"))</f>
+        <f>IF(AF443="","",HYPERLINK(IFERROR(LEFT(AF443,FIND(";",AF443)-1),AF443),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16693,11 +16693,11 @@
         <v/>
       </c>
       <c r="AL444">
-        <f>IF(AE444="","",HYPERLINK(AE444,"before"))</f>
+        <f>IF(AE444="","",HYPERLINK(IFERROR(LEFT(AE444,FIND(";",AE444)-1),AE444),"before"))</f>
         <v/>
       </c>
       <c r="AM444">
-        <f>IF(AF444="","",HYPERLINK(AF444,"after"))</f>
+        <f>IF(AF444="","",HYPERLINK(IFERROR(LEFT(AF444,FIND(";",AF444)-1),AF444),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16729,11 +16729,11 @@
         <v/>
       </c>
       <c r="AL445">
-        <f>IF(AE445="","",HYPERLINK(AE445,"before"))</f>
+        <f>IF(AE445="","",HYPERLINK(IFERROR(LEFT(AE445,FIND(";",AE445)-1),AE445),"before"))</f>
         <v/>
       </c>
       <c r="AM445">
-        <f>IF(AF445="","",HYPERLINK(AF445,"after"))</f>
+        <f>IF(AF445="","",HYPERLINK(IFERROR(LEFT(AF445,FIND(";",AF445)-1),AF445),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16765,11 +16765,11 @@
         <v/>
       </c>
       <c r="AL446">
-        <f>IF(AE446="","",HYPERLINK(AE446,"before"))</f>
+        <f>IF(AE446="","",HYPERLINK(IFERROR(LEFT(AE446,FIND(";",AE446)-1),AE446),"before"))</f>
         <v/>
       </c>
       <c r="AM446">
-        <f>IF(AF446="","",HYPERLINK(AF446,"after"))</f>
+        <f>IF(AF446="","",HYPERLINK(IFERROR(LEFT(AF446,FIND(";",AF446)-1),AF446),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16801,11 +16801,11 @@
         <v/>
       </c>
       <c r="AL447">
-        <f>IF(AE447="","",HYPERLINK(AE447,"before"))</f>
+        <f>IF(AE447="","",HYPERLINK(IFERROR(LEFT(AE447,FIND(";",AE447)-1),AE447),"before"))</f>
         <v/>
       </c>
       <c r="AM447">
-        <f>IF(AF447="","",HYPERLINK(AF447,"after"))</f>
+        <f>IF(AF447="","",HYPERLINK(IFERROR(LEFT(AF447,FIND(";",AF447)-1),AF447),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16837,11 +16837,11 @@
         <v/>
       </c>
       <c r="AL448">
-        <f>IF(AE448="","",HYPERLINK(AE448,"before"))</f>
+        <f>IF(AE448="","",HYPERLINK(IFERROR(LEFT(AE448,FIND(";",AE448)-1),AE448),"before"))</f>
         <v/>
       </c>
       <c r="AM448">
-        <f>IF(AF448="","",HYPERLINK(AF448,"after"))</f>
+        <f>IF(AF448="","",HYPERLINK(IFERROR(LEFT(AF448,FIND(";",AF448)-1),AF448),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16873,11 +16873,11 @@
         <v/>
       </c>
       <c r="AL449">
-        <f>IF(AE449="","",HYPERLINK(AE449,"before"))</f>
+        <f>IF(AE449="","",HYPERLINK(IFERROR(LEFT(AE449,FIND(";",AE449)-1),AE449),"before"))</f>
         <v/>
       </c>
       <c r="AM449">
-        <f>IF(AF449="","",HYPERLINK(AF449,"after"))</f>
+        <f>IF(AF449="","",HYPERLINK(IFERROR(LEFT(AF449,FIND(";",AF449)-1),AF449),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16909,11 +16909,11 @@
         <v/>
       </c>
       <c r="AL450">
-        <f>IF(AE450="","",HYPERLINK(AE450,"before"))</f>
+        <f>IF(AE450="","",HYPERLINK(IFERROR(LEFT(AE450,FIND(";",AE450)-1),AE450),"before"))</f>
         <v/>
       </c>
       <c r="AM450">
-        <f>IF(AF450="","",HYPERLINK(AF450,"after"))</f>
+        <f>IF(AF450="","",HYPERLINK(IFERROR(LEFT(AF450,FIND(";",AF450)-1),AF450),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16945,11 +16945,11 @@
         <v/>
       </c>
       <c r="AL451">
-        <f>IF(AE451="","",HYPERLINK(AE451,"before"))</f>
+        <f>IF(AE451="","",HYPERLINK(IFERROR(LEFT(AE451,FIND(";",AE451)-1),AE451),"before"))</f>
         <v/>
       </c>
       <c r="AM451">
-        <f>IF(AF451="","",HYPERLINK(AF451,"after"))</f>
+        <f>IF(AF451="","",HYPERLINK(IFERROR(LEFT(AF451,FIND(";",AF451)-1),AF451),"after"))</f>
         <v/>
       </c>
     </row>
@@ -16981,11 +16981,11 @@
         <v/>
       </c>
       <c r="AL452">
-        <f>IF(AE452="","",HYPERLINK(AE452,"before"))</f>
+        <f>IF(AE452="","",HYPERLINK(IFERROR(LEFT(AE452,FIND(";",AE452)-1),AE452),"before"))</f>
         <v/>
       </c>
       <c r="AM452">
-        <f>IF(AF452="","",HYPERLINK(AF452,"after"))</f>
+        <f>IF(AF452="","",HYPERLINK(IFERROR(LEFT(AF452,FIND(";",AF452)-1),AF452),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17017,11 +17017,11 @@
         <v/>
       </c>
       <c r="AL453">
-        <f>IF(AE453="","",HYPERLINK(AE453,"before"))</f>
+        <f>IF(AE453="","",HYPERLINK(IFERROR(LEFT(AE453,FIND(";",AE453)-1),AE453),"before"))</f>
         <v/>
       </c>
       <c r="AM453">
-        <f>IF(AF453="","",HYPERLINK(AF453,"after"))</f>
+        <f>IF(AF453="","",HYPERLINK(IFERROR(LEFT(AF453,FIND(";",AF453)-1),AF453),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17053,11 +17053,11 @@
         <v/>
       </c>
       <c r="AL454">
-        <f>IF(AE454="","",HYPERLINK(AE454,"before"))</f>
+        <f>IF(AE454="","",HYPERLINK(IFERROR(LEFT(AE454,FIND(";",AE454)-1),AE454),"before"))</f>
         <v/>
       </c>
       <c r="AM454">
-        <f>IF(AF454="","",HYPERLINK(AF454,"after"))</f>
+        <f>IF(AF454="","",HYPERLINK(IFERROR(LEFT(AF454,FIND(";",AF454)-1),AF454),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17089,11 +17089,11 @@
         <v/>
       </c>
       <c r="AL455">
-        <f>IF(AE455="","",HYPERLINK(AE455,"before"))</f>
+        <f>IF(AE455="","",HYPERLINK(IFERROR(LEFT(AE455,FIND(";",AE455)-1),AE455),"before"))</f>
         <v/>
       </c>
       <c r="AM455">
-        <f>IF(AF455="","",HYPERLINK(AF455,"after"))</f>
+        <f>IF(AF455="","",HYPERLINK(IFERROR(LEFT(AF455,FIND(";",AF455)-1),AF455),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17125,11 +17125,11 @@
         <v/>
       </c>
       <c r="AL456">
-        <f>IF(AE456="","",HYPERLINK(AE456,"before"))</f>
+        <f>IF(AE456="","",HYPERLINK(IFERROR(LEFT(AE456,FIND(";",AE456)-1),AE456),"before"))</f>
         <v/>
       </c>
       <c r="AM456">
-        <f>IF(AF456="","",HYPERLINK(AF456,"after"))</f>
+        <f>IF(AF456="","",HYPERLINK(IFERROR(LEFT(AF456,FIND(";",AF456)-1),AF456),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17161,11 +17161,11 @@
         <v/>
       </c>
       <c r="AL457">
-        <f>IF(AE457="","",HYPERLINK(AE457,"before"))</f>
+        <f>IF(AE457="","",HYPERLINK(IFERROR(LEFT(AE457,FIND(";",AE457)-1),AE457),"before"))</f>
         <v/>
       </c>
       <c r="AM457">
-        <f>IF(AF457="","",HYPERLINK(AF457,"after"))</f>
+        <f>IF(AF457="","",HYPERLINK(IFERROR(LEFT(AF457,FIND(";",AF457)-1),AF457),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17197,11 +17197,11 @@
         <v/>
       </c>
       <c r="AL458">
-        <f>IF(AE458="","",HYPERLINK(AE458,"before"))</f>
+        <f>IF(AE458="","",HYPERLINK(IFERROR(LEFT(AE458,FIND(";",AE458)-1),AE458),"before"))</f>
         <v/>
       </c>
       <c r="AM458">
-        <f>IF(AF458="","",HYPERLINK(AF458,"after"))</f>
+        <f>IF(AF458="","",HYPERLINK(IFERROR(LEFT(AF458,FIND(";",AF458)-1),AF458),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17233,11 +17233,11 @@
         <v/>
       </c>
       <c r="AL459">
-        <f>IF(AE459="","",HYPERLINK(AE459,"before"))</f>
+        <f>IF(AE459="","",HYPERLINK(IFERROR(LEFT(AE459,FIND(";",AE459)-1),AE459),"before"))</f>
         <v/>
       </c>
       <c r="AM459">
-        <f>IF(AF459="","",HYPERLINK(AF459,"after"))</f>
+        <f>IF(AF459="","",HYPERLINK(IFERROR(LEFT(AF459,FIND(";",AF459)-1),AF459),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17269,11 +17269,11 @@
         <v/>
       </c>
       <c r="AL460">
-        <f>IF(AE460="","",HYPERLINK(AE460,"before"))</f>
+        <f>IF(AE460="","",HYPERLINK(IFERROR(LEFT(AE460,FIND(";",AE460)-1),AE460),"before"))</f>
         <v/>
       </c>
       <c r="AM460">
-        <f>IF(AF460="","",HYPERLINK(AF460,"after"))</f>
+        <f>IF(AF460="","",HYPERLINK(IFERROR(LEFT(AF460,FIND(";",AF460)-1),AF460),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17305,11 +17305,11 @@
         <v/>
       </c>
       <c r="AL461">
-        <f>IF(AE461="","",HYPERLINK(AE461,"before"))</f>
+        <f>IF(AE461="","",HYPERLINK(IFERROR(LEFT(AE461,FIND(";",AE461)-1),AE461),"before"))</f>
         <v/>
       </c>
       <c r="AM461">
-        <f>IF(AF461="","",HYPERLINK(AF461,"after"))</f>
+        <f>IF(AF461="","",HYPERLINK(IFERROR(LEFT(AF461,FIND(";",AF461)-1),AF461),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17341,11 +17341,11 @@
         <v/>
       </c>
       <c r="AL462">
-        <f>IF(AE462="","",HYPERLINK(AE462,"before"))</f>
+        <f>IF(AE462="","",HYPERLINK(IFERROR(LEFT(AE462,FIND(";",AE462)-1),AE462),"before"))</f>
         <v/>
       </c>
       <c r="AM462">
-        <f>IF(AF462="","",HYPERLINK(AF462,"after"))</f>
+        <f>IF(AF462="","",HYPERLINK(IFERROR(LEFT(AF462,FIND(";",AF462)-1),AF462),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17377,11 +17377,11 @@
         <v/>
       </c>
       <c r="AL463">
-        <f>IF(AE463="","",HYPERLINK(AE463,"before"))</f>
+        <f>IF(AE463="","",HYPERLINK(IFERROR(LEFT(AE463,FIND(";",AE463)-1),AE463),"before"))</f>
         <v/>
       </c>
       <c r="AM463">
-        <f>IF(AF463="","",HYPERLINK(AF463,"after"))</f>
+        <f>IF(AF463="","",HYPERLINK(IFERROR(LEFT(AF463,FIND(";",AF463)-1),AF463),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17413,11 +17413,11 @@
         <v/>
       </c>
       <c r="AL464">
-        <f>IF(AE464="","",HYPERLINK(AE464,"before"))</f>
+        <f>IF(AE464="","",HYPERLINK(IFERROR(LEFT(AE464,FIND(";",AE464)-1),AE464),"before"))</f>
         <v/>
       </c>
       <c r="AM464">
-        <f>IF(AF464="","",HYPERLINK(AF464,"after"))</f>
+        <f>IF(AF464="","",HYPERLINK(IFERROR(LEFT(AF464,FIND(";",AF464)-1),AF464),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17449,11 +17449,11 @@
         <v/>
       </c>
       <c r="AL465">
-        <f>IF(AE465="","",HYPERLINK(AE465,"before"))</f>
+        <f>IF(AE465="","",HYPERLINK(IFERROR(LEFT(AE465,FIND(";",AE465)-1),AE465),"before"))</f>
         <v/>
       </c>
       <c r="AM465">
-        <f>IF(AF465="","",HYPERLINK(AF465,"after"))</f>
+        <f>IF(AF465="","",HYPERLINK(IFERROR(LEFT(AF465,FIND(";",AF465)-1),AF465),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17485,11 +17485,11 @@
         <v/>
       </c>
       <c r="AL466">
-        <f>IF(AE466="","",HYPERLINK(AE466,"before"))</f>
+        <f>IF(AE466="","",HYPERLINK(IFERROR(LEFT(AE466,FIND(";",AE466)-1),AE466),"before"))</f>
         <v/>
       </c>
       <c r="AM466">
-        <f>IF(AF466="","",HYPERLINK(AF466,"after"))</f>
+        <f>IF(AF466="","",HYPERLINK(IFERROR(LEFT(AF466,FIND(";",AF466)-1),AF466),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17521,11 +17521,11 @@
         <v/>
       </c>
       <c r="AL467">
-        <f>IF(AE467="","",HYPERLINK(AE467,"before"))</f>
+        <f>IF(AE467="","",HYPERLINK(IFERROR(LEFT(AE467,FIND(";",AE467)-1),AE467),"before"))</f>
         <v/>
       </c>
       <c r="AM467">
-        <f>IF(AF467="","",HYPERLINK(AF467,"after"))</f>
+        <f>IF(AF467="","",HYPERLINK(IFERROR(LEFT(AF467,FIND(";",AF467)-1),AF467),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17557,11 +17557,11 @@
         <v/>
       </c>
       <c r="AL468">
-        <f>IF(AE468="","",HYPERLINK(AE468,"before"))</f>
+        <f>IF(AE468="","",HYPERLINK(IFERROR(LEFT(AE468,FIND(";",AE468)-1),AE468),"before"))</f>
         <v/>
       </c>
       <c r="AM468">
-        <f>IF(AF468="","",HYPERLINK(AF468,"after"))</f>
+        <f>IF(AF468="","",HYPERLINK(IFERROR(LEFT(AF468,FIND(";",AF468)-1),AF468),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17593,11 +17593,11 @@
         <v/>
       </c>
       <c r="AL469">
-        <f>IF(AE469="","",HYPERLINK(AE469,"before"))</f>
+        <f>IF(AE469="","",HYPERLINK(IFERROR(LEFT(AE469,FIND(";",AE469)-1),AE469),"before"))</f>
         <v/>
       </c>
       <c r="AM469">
-        <f>IF(AF469="","",HYPERLINK(AF469,"after"))</f>
+        <f>IF(AF469="","",HYPERLINK(IFERROR(LEFT(AF469,FIND(";",AF469)-1),AF469),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17629,11 +17629,11 @@
         <v/>
       </c>
       <c r="AL470">
-        <f>IF(AE470="","",HYPERLINK(AE470,"before"))</f>
+        <f>IF(AE470="","",HYPERLINK(IFERROR(LEFT(AE470,FIND(";",AE470)-1),AE470),"before"))</f>
         <v/>
       </c>
       <c r="AM470">
-        <f>IF(AF470="","",HYPERLINK(AF470,"after"))</f>
+        <f>IF(AF470="","",HYPERLINK(IFERROR(LEFT(AF470,FIND(";",AF470)-1),AF470),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17665,11 +17665,11 @@
         <v/>
       </c>
       <c r="AL471">
-        <f>IF(AE471="","",HYPERLINK(AE471,"before"))</f>
+        <f>IF(AE471="","",HYPERLINK(IFERROR(LEFT(AE471,FIND(";",AE471)-1),AE471),"before"))</f>
         <v/>
       </c>
       <c r="AM471">
-        <f>IF(AF471="","",HYPERLINK(AF471,"after"))</f>
+        <f>IF(AF471="","",HYPERLINK(IFERROR(LEFT(AF471,FIND(";",AF471)-1),AF471),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17701,11 +17701,11 @@
         <v/>
       </c>
       <c r="AL472">
-        <f>IF(AE472="","",HYPERLINK(AE472,"before"))</f>
+        <f>IF(AE472="","",HYPERLINK(IFERROR(LEFT(AE472,FIND(";",AE472)-1),AE472),"before"))</f>
         <v/>
       </c>
       <c r="AM472">
-        <f>IF(AF472="","",HYPERLINK(AF472,"after"))</f>
+        <f>IF(AF472="","",HYPERLINK(IFERROR(LEFT(AF472,FIND(";",AF472)-1),AF472),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17737,11 +17737,11 @@
         <v/>
       </c>
       <c r="AL473">
-        <f>IF(AE473="","",HYPERLINK(AE473,"before"))</f>
+        <f>IF(AE473="","",HYPERLINK(IFERROR(LEFT(AE473,FIND(";",AE473)-1),AE473),"before"))</f>
         <v/>
       </c>
       <c r="AM473">
-        <f>IF(AF473="","",HYPERLINK(AF473,"after"))</f>
+        <f>IF(AF473="","",HYPERLINK(IFERROR(LEFT(AF473,FIND(";",AF473)-1),AF473),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17773,11 +17773,11 @@
         <v/>
       </c>
       <c r="AL474">
-        <f>IF(AE474="","",HYPERLINK(AE474,"before"))</f>
+        <f>IF(AE474="","",HYPERLINK(IFERROR(LEFT(AE474,FIND(";",AE474)-1),AE474),"before"))</f>
         <v/>
       </c>
       <c r="AM474">
-        <f>IF(AF474="","",HYPERLINK(AF474,"after"))</f>
+        <f>IF(AF474="","",HYPERLINK(IFERROR(LEFT(AF474,FIND(";",AF474)-1),AF474),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17809,11 +17809,11 @@
         <v/>
       </c>
       <c r="AL475">
-        <f>IF(AE475="","",HYPERLINK(AE475,"before"))</f>
+        <f>IF(AE475="","",HYPERLINK(IFERROR(LEFT(AE475,FIND(";",AE475)-1),AE475),"before"))</f>
         <v/>
       </c>
       <c r="AM475">
-        <f>IF(AF475="","",HYPERLINK(AF475,"after"))</f>
+        <f>IF(AF475="","",HYPERLINK(IFERROR(LEFT(AF475,FIND(";",AF475)-1),AF475),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17845,11 +17845,11 @@
         <v/>
       </c>
       <c r="AL476">
-        <f>IF(AE476="","",HYPERLINK(AE476,"before"))</f>
+        <f>IF(AE476="","",HYPERLINK(IFERROR(LEFT(AE476,FIND(";",AE476)-1),AE476),"before"))</f>
         <v/>
       </c>
       <c r="AM476">
-        <f>IF(AF476="","",HYPERLINK(AF476,"after"))</f>
+        <f>IF(AF476="","",HYPERLINK(IFERROR(LEFT(AF476,FIND(";",AF476)-1),AF476),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17881,11 +17881,11 @@
         <v/>
       </c>
       <c r="AL477">
-        <f>IF(AE477="","",HYPERLINK(AE477,"before"))</f>
+        <f>IF(AE477="","",HYPERLINK(IFERROR(LEFT(AE477,FIND(";",AE477)-1),AE477),"before"))</f>
         <v/>
       </c>
       <c r="AM477">
-        <f>IF(AF477="","",HYPERLINK(AF477,"after"))</f>
+        <f>IF(AF477="","",HYPERLINK(IFERROR(LEFT(AF477,FIND(";",AF477)-1),AF477),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17917,11 +17917,11 @@
         <v/>
       </c>
       <c r="AL478">
-        <f>IF(AE478="","",HYPERLINK(AE478,"before"))</f>
+        <f>IF(AE478="","",HYPERLINK(IFERROR(LEFT(AE478,FIND(";",AE478)-1),AE478),"before"))</f>
         <v/>
       </c>
       <c r="AM478">
-        <f>IF(AF478="","",HYPERLINK(AF478,"after"))</f>
+        <f>IF(AF478="","",HYPERLINK(IFERROR(LEFT(AF478,FIND(";",AF478)-1),AF478),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17953,11 +17953,11 @@
         <v/>
       </c>
       <c r="AL479">
-        <f>IF(AE479="","",HYPERLINK(AE479,"before"))</f>
+        <f>IF(AE479="","",HYPERLINK(IFERROR(LEFT(AE479,FIND(";",AE479)-1),AE479),"before"))</f>
         <v/>
       </c>
       <c r="AM479">
-        <f>IF(AF479="","",HYPERLINK(AF479,"after"))</f>
+        <f>IF(AF479="","",HYPERLINK(IFERROR(LEFT(AF479,FIND(";",AF479)-1),AF479),"after"))</f>
         <v/>
       </c>
     </row>
@@ -17989,11 +17989,11 @@
         <v/>
       </c>
       <c r="AL480">
-        <f>IF(AE480="","",HYPERLINK(AE480,"before"))</f>
+        <f>IF(AE480="","",HYPERLINK(IFERROR(LEFT(AE480,FIND(";",AE480)-1),AE480),"before"))</f>
         <v/>
       </c>
       <c r="AM480">
-        <f>IF(AF480="","",HYPERLINK(AF480,"after"))</f>
+        <f>IF(AF480="","",HYPERLINK(IFERROR(LEFT(AF480,FIND(";",AF480)-1),AF480),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18025,11 +18025,11 @@
         <v/>
       </c>
       <c r="AL481">
-        <f>IF(AE481="","",HYPERLINK(AE481,"before"))</f>
+        <f>IF(AE481="","",HYPERLINK(IFERROR(LEFT(AE481,FIND(";",AE481)-1),AE481),"before"))</f>
         <v/>
       </c>
       <c r="AM481">
-        <f>IF(AF481="","",HYPERLINK(AF481,"after"))</f>
+        <f>IF(AF481="","",HYPERLINK(IFERROR(LEFT(AF481,FIND(";",AF481)-1),AF481),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18061,11 +18061,11 @@
         <v/>
       </c>
       <c r="AL482">
-        <f>IF(AE482="","",HYPERLINK(AE482,"before"))</f>
+        <f>IF(AE482="","",HYPERLINK(IFERROR(LEFT(AE482,FIND(";",AE482)-1),AE482),"before"))</f>
         <v/>
       </c>
       <c r="AM482">
-        <f>IF(AF482="","",HYPERLINK(AF482,"after"))</f>
+        <f>IF(AF482="","",HYPERLINK(IFERROR(LEFT(AF482,FIND(";",AF482)-1),AF482),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18097,11 +18097,11 @@
         <v/>
       </c>
       <c r="AL483">
-        <f>IF(AE483="","",HYPERLINK(AE483,"before"))</f>
+        <f>IF(AE483="","",HYPERLINK(IFERROR(LEFT(AE483,FIND(";",AE483)-1),AE483),"before"))</f>
         <v/>
       </c>
       <c r="AM483">
-        <f>IF(AF483="","",HYPERLINK(AF483,"after"))</f>
+        <f>IF(AF483="","",HYPERLINK(IFERROR(LEFT(AF483,FIND(";",AF483)-1),AF483),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18133,11 +18133,11 @@
         <v/>
       </c>
       <c r="AL484">
-        <f>IF(AE484="","",HYPERLINK(AE484,"before"))</f>
+        <f>IF(AE484="","",HYPERLINK(IFERROR(LEFT(AE484,FIND(";",AE484)-1),AE484),"before"))</f>
         <v/>
       </c>
       <c r="AM484">
-        <f>IF(AF484="","",HYPERLINK(AF484,"after"))</f>
+        <f>IF(AF484="","",HYPERLINK(IFERROR(LEFT(AF484,FIND(";",AF484)-1),AF484),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18169,11 +18169,11 @@
         <v/>
       </c>
       <c r="AL485">
-        <f>IF(AE485="","",HYPERLINK(AE485,"before"))</f>
+        <f>IF(AE485="","",HYPERLINK(IFERROR(LEFT(AE485,FIND(";",AE485)-1),AE485),"before"))</f>
         <v/>
       </c>
       <c r="AM485">
-        <f>IF(AF485="","",HYPERLINK(AF485,"after"))</f>
+        <f>IF(AF485="","",HYPERLINK(IFERROR(LEFT(AF485,FIND(";",AF485)-1),AF485),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18205,11 +18205,11 @@
         <v/>
       </c>
       <c r="AL486">
-        <f>IF(AE486="","",HYPERLINK(AE486,"before"))</f>
+        <f>IF(AE486="","",HYPERLINK(IFERROR(LEFT(AE486,FIND(";",AE486)-1),AE486),"before"))</f>
         <v/>
       </c>
       <c r="AM486">
-        <f>IF(AF486="","",HYPERLINK(AF486,"after"))</f>
+        <f>IF(AF486="","",HYPERLINK(IFERROR(LEFT(AF486,FIND(";",AF486)-1),AF486),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18241,11 +18241,11 @@
         <v/>
       </c>
       <c r="AL487">
-        <f>IF(AE487="","",HYPERLINK(AE487,"before"))</f>
+        <f>IF(AE487="","",HYPERLINK(IFERROR(LEFT(AE487,FIND(";",AE487)-1),AE487),"before"))</f>
         <v/>
       </c>
       <c r="AM487">
-        <f>IF(AF487="","",HYPERLINK(AF487,"after"))</f>
+        <f>IF(AF487="","",HYPERLINK(IFERROR(LEFT(AF487,FIND(";",AF487)-1),AF487),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18277,11 +18277,11 @@
         <v/>
       </c>
       <c r="AL488">
-        <f>IF(AE488="","",HYPERLINK(AE488,"before"))</f>
+        <f>IF(AE488="","",HYPERLINK(IFERROR(LEFT(AE488,FIND(";",AE488)-1),AE488),"before"))</f>
         <v/>
       </c>
       <c r="AM488">
-        <f>IF(AF488="","",HYPERLINK(AF488,"after"))</f>
+        <f>IF(AF488="","",HYPERLINK(IFERROR(LEFT(AF488,FIND(";",AF488)-1),AF488),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18313,11 +18313,11 @@
         <v/>
       </c>
       <c r="AL489">
-        <f>IF(AE489="","",HYPERLINK(AE489,"before"))</f>
+        <f>IF(AE489="","",HYPERLINK(IFERROR(LEFT(AE489,FIND(";",AE489)-1),AE489),"before"))</f>
         <v/>
       </c>
       <c r="AM489">
-        <f>IF(AF489="","",HYPERLINK(AF489,"after"))</f>
+        <f>IF(AF489="","",HYPERLINK(IFERROR(LEFT(AF489,FIND(";",AF489)-1),AF489),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18349,11 +18349,11 @@
         <v/>
       </c>
       <c r="AL490">
-        <f>IF(AE490="","",HYPERLINK(AE490,"before"))</f>
+        <f>IF(AE490="","",HYPERLINK(IFERROR(LEFT(AE490,FIND(";",AE490)-1),AE490),"before"))</f>
         <v/>
       </c>
       <c r="AM490">
-        <f>IF(AF490="","",HYPERLINK(AF490,"after"))</f>
+        <f>IF(AF490="","",HYPERLINK(IFERROR(LEFT(AF490,FIND(";",AF490)-1),AF490),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18385,11 +18385,11 @@
         <v/>
       </c>
       <c r="AL491">
-        <f>IF(AE491="","",HYPERLINK(AE491,"before"))</f>
+        <f>IF(AE491="","",HYPERLINK(IFERROR(LEFT(AE491,FIND(";",AE491)-1),AE491),"before"))</f>
         <v/>
       </c>
       <c r="AM491">
-        <f>IF(AF491="","",HYPERLINK(AF491,"after"))</f>
+        <f>IF(AF491="","",HYPERLINK(IFERROR(LEFT(AF491,FIND(";",AF491)-1),AF491),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18421,11 +18421,11 @@
         <v/>
       </c>
       <c r="AL492">
-        <f>IF(AE492="","",HYPERLINK(AE492,"before"))</f>
+        <f>IF(AE492="","",HYPERLINK(IFERROR(LEFT(AE492,FIND(";",AE492)-1),AE492),"before"))</f>
         <v/>
       </c>
       <c r="AM492">
-        <f>IF(AF492="","",HYPERLINK(AF492,"after"))</f>
+        <f>IF(AF492="","",HYPERLINK(IFERROR(LEFT(AF492,FIND(";",AF492)-1),AF492),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18457,11 +18457,11 @@
         <v/>
       </c>
       <c r="AL493">
-        <f>IF(AE493="","",HYPERLINK(AE493,"before"))</f>
+        <f>IF(AE493="","",HYPERLINK(IFERROR(LEFT(AE493,FIND(";",AE493)-1),AE493),"before"))</f>
         <v/>
       </c>
       <c r="AM493">
-        <f>IF(AF493="","",HYPERLINK(AF493,"after"))</f>
+        <f>IF(AF493="","",HYPERLINK(IFERROR(LEFT(AF493,FIND(";",AF493)-1),AF493),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18493,11 +18493,11 @@
         <v/>
       </c>
       <c r="AL494">
-        <f>IF(AE494="","",HYPERLINK(AE494,"before"))</f>
+        <f>IF(AE494="","",HYPERLINK(IFERROR(LEFT(AE494,FIND(";",AE494)-1),AE494),"before"))</f>
         <v/>
       </c>
       <c r="AM494">
-        <f>IF(AF494="","",HYPERLINK(AF494,"after"))</f>
+        <f>IF(AF494="","",HYPERLINK(IFERROR(LEFT(AF494,FIND(";",AF494)-1),AF494),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18529,11 +18529,11 @@
         <v/>
       </c>
       <c r="AL495">
-        <f>IF(AE495="","",HYPERLINK(AE495,"before"))</f>
+        <f>IF(AE495="","",HYPERLINK(IFERROR(LEFT(AE495,FIND(";",AE495)-1),AE495),"before"))</f>
         <v/>
       </c>
       <c r="AM495">
-        <f>IF(AF495="","",HYPERLINK(AF495,"after"))</f>
+        <f>IF(AF495="","",HYPERLINK(IFERROR(LEFT(AF495,FIND(";",AF495)-1),AF495),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18565,11 +18565,11 @@
         <v/>
       </c>
       <c r="AL496">
-        <f>IF(AE496="","",HYPERLINK(AE496,"before"))</f>
+        <f>IF(AE496="","",HYPERLINK(IFERROR(LEFT(AE496,FIND(";",AE496)-1),AE496),"before"))</f>
         <v/>
       </c>
       <c r="AM496">
-        <f>IF(AF496="","",HYPERLINK(AF496,"after"))</f>
+        <f>IF(AF496="","",HYPERLINK(IFERROR(LEFT(AF496,FIND(";",AF496)-1),AF496),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18601,11 +18601,11 @@
         <v/>
       </c>
       <c r="AL497">
-        <f>IF(AE497="","",HYPERLINK(AE497,"before"))</f>
+        <f>IF(AE497="","",HYPERLINK(IFERROR(LEFT(AE497,FIND(";",AE497)-1),AE497),"before"))</f>
         <v/>
       </c>
       <c r="AM497">
-        <f>IF(AF497="","",HYPERLINK(AF497,"after"))</f>
+        <f>IF(AF497="","",HYPERLINK(IFERROR(LEFT(AF497,FIND(";",AF497)-1),AF497),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18637,11 +18637,11 @@
         <v/>
       </c>
       <c r="AL498">
-        <f>IF(AE498="","",HYPERLINK(AE498,"before"))</f>
+        <f>IF(AE498="","",HYPERLINK(IFERROR(LEFT(AE498,FIND(";",AE498)-1),AE498),"before"))</f>
         <v/>
       </c>
       <c r="AM498">
-        <f>IF(AF498="","",HYPERLINK(AF498,"after"))</f>
+        <f>IF(AF498="","",HYPERLINK(IFERROR(LEFT(AF498,FIND(";",AF498)-1),AF498),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18673,11 +18673,11 @@
         <v/>
       </c>
       <c r="AL499">
-        <f>IF(AE499="","",HYPERLINK(AE499,"before"))</f>
+        <f>IF(AE499="","",HYPERLINK(IFERROR(LEFT(AE499,FIND(";",AE499)-1),AE499),"before"))</f>
         <v/>
       </c>
       <c r="AM499">
-        <f>IF(AF499="","",HYPERLINK(AF499,"after"))</f>
+        <f>IF(AF499="","",HYPERLINK(IFERROR(LEFT(AF499,FIND(";",AF499)-1),AF499),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18709,11 +18709,11 @@
         <v/>
       </c>
       <c r="AL500">
-        <f>IF(AE500="","",HYPERLINK(AE500,"before"))</f>
+        <f>IF(AE500="","",HYPERLINK(IFERROR(LEFT(AE500,FIND(";",AE500)-1),AE500),"before"))</f>
         <v/>
       </c>
       <c r="AM500">
-        <f>IF(AF500="","",HYPERLINK(AF500,"after"))</f>
+        <f>IF(AF500="","",HYPERLINK(IFERROR(LEFT(AF500,FIND(";",AF500)-1),AF500),"after"))</f>
         <v/>
       </c>
     </row>
@@ -18745,11 +18745,11 @@
         <v/>
       </c>
       <c r="AL501">
-        <f>IF(AE501="","",HYPERLINK(AE501,"before"))</f>
+        <f>IF(AE501="","",HYPERLINK(IFERROR(LEFT(AE501,FIND(";",AE501)-1),AE501),"before"))</f>
         <v/>
       </c>
       <c r="AM501">
-        <f>IF(AF501="","",HYPERLINK(AF501,"after"))</f>
+        <f>IF(AF501="","",HYPERLINK(IFERROR(LEFT(AF501,FIND(";",AF501)-1),AF501),"after"))</f>
         <v/>
       </c>
     </row>
@@ -19046,7 +19046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -19166,43 +19166,50 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>before_photo / after_photo hold the file names inside the Share bundle ZIP (sN_wM_before.jpg).</t>
+          <t>before_photo / after_photo list the file names inside the Share bundle ZIP, one per face, separated by '; '</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Unzip the bundle into a folder, save this workbook in that same folder, and before_link / after_link become clickable.</t>
+          <t xml:space="preserve">   e.g. s20_w5_before_f5.jpg; s20_w5_before_f6.jpg  (extra photos beyond the faces are _x1, _x2 ...).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">   For photos embedded in the sheet itself, run: python build_workbook.py &lt;bundle.zip&gt;  (see that script).</t>
+          <t xml:space="preserve">   Unzip the bundle into a folder, save this workbook in that same folder, and before_link / after_link become clickable.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">   For photos embedded in the sheet itself, run: python build_workbook.py &lt;bundle.zip&gt;  (see that script).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
           <t>rotation_viewed_from records the viewpoint that makes CW/CCW unambiguous (e.g. drive end).</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="10" t="inlineStr"/>
-    </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>Dropdown lists live on the Lists sheet. Add a value there and it appears in the dropdown.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="10" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Keep this file as the template. Save each shift's data as a copy.</t>
         </is>
